--- a/00_doc/axi_ahblite_bridge_vplan.xlsx
+++ b/00_doc/axi_ahblite_bridge_vplan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\axi_ahblite_bridge_vip\00_doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA4272E1-CE8E-4EED-871C-FB31105473C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70671146-75B4-43D3-9973-1B78C43021AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="571" activeTab="2" xr2:uid="{28AB2DFB-D835-4571-8270-76E94898C9BC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="571" activeTab="3" xr2:uid="{28AB2DFB-D835-4571-8270-76E94898C9BC}"/>
   </bookViews>
   <sheets>
     <sheet name="Vplan" sheetId="1" r:id="rId1"/>
@@ -2088,7 +2088,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2122,6 +2122,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF008000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF808080"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2168,7 +2176,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2189,6 +2197,9 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -6323,7 +6334,8 @@
   <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="34" customWidth="1"/>
+    <col min="1" max="1" width="32.77734375" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="62" customWidth="1"/>
     <col min="4" max="4" width="50" customWidth="1"/>
     <col min="5" max="5" width="35" customWidth="1"/>
@@ -6366,8 +6378,8 @@
       <c r="E2" s="4" t="s">
         <v>584</v>
       </c>
-      <c r="F2" s="6" t="s">
-        <v>15</v>
+      <c r="F2" s="8" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -6386,8 +6398,8 @@
       <c r="E3" s="4" t="s">
         <v>587</v>
       </c>
-      <c r="F3" s="6" t="s">
-        <v>15</v>
+      <c r="F3" s="8" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -6406,8 +6418,8 @@
       <c r="E4" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="F4" s="6" t="s">
-        <v>15</v>
+      <c r="F4" s="8" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -6426,7 +6438,7 @@
       <c r="E5" s="4" t="s">
         <v>388</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -6446,7 +6458,7 @@
       <c r="E6" s="4" t="s">
         <v>594</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -6466,7 +6478,7 @@
       <c r="E7" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -6486,7 +6498,7 @@
       <c r="E8" s="4" t="s">
         <v>599</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -6506,7 +6518,7 @@
       <c r="E9" s="4" t="s">
         <v>400</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -6526,7 +6538,7 @@
       <c r="E10" s="4" t="s">
         <v>604</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -6546,7 +6558,7 @@
       <c r="E11" s="4" t="s">
         <v>421</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -6566,7 +6578,7 @@
       <c r="E12" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -6586,7 +6598,7 @@
       <c r="E13" s="4" t="s">
         <v>404</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="F13" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -6606,7 +6618,7 @@
       <c r="E14" s="4" t="s">
         <v>613</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="F14" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -6626,7 +6638,7 @@
       <c r="E15" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="F15" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -6646,7 +6658,7 @@
       <c r="E16" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="F16" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -6666,7 +6678,7 @@
       <c r="E17" s="4" t="s">
         <v>620</v>
       </c>
-      <c r="F17" s="6" t="s">
+      <c r="F17" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -6686,7 +6698,7 @@
       <c r="E18" s="4" t="s">
         <v>623</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="F18" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -6706,7 +6718,7 @@
       <c r="E19" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="F19" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -6726,7 +6738,7 @@
       <c r="E20" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="F20" s="6" t="s">
+      <c r="F20" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -6746,7 +6758,7 @@
       <c r="E21" s="4" t="s">
         <v>484</v>
       </c>
-      <c r="F21" s="6" t="s">
+      <c r="F21" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -6766,7 +6778,7 @@
       <c r="E22" s="4" t="s">
         <v>632</v>
       </c>
-      <c r="F22" s="6" t="s">
+      <c r="F22" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -6786,7 +6798,7 @@
       <c r="E23" s="4" t="s">
         <v>635</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="F23" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -6806,7 +6818,7 @@
       <c r="E24" s="4" t="s">
         <v>490</v>
       </c>
-      <c r="F24" s="6" t="s">
+      <c r="F24" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -6826,7 +6838,7 @@
       <c r="E25" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="F25" s="6" t="s">
+      <c r="F25" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -6846,7 +6858,7 @@
       <c r="E26" s="4" t="s">
         <v>643</v>
       </c>
-      <c r="F26" s="6" t="s">
+      <c r="F26" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -6866,7 +6878,7 @@
       <c r="E27" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="F27" s="6" t="s">
+      <c r="F27" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -6886,7 +6898,7 @@
       <c r="E28" s="4" t="s">
         <v>648</v>
       </c>
-      <c r="F28" s="6" t="s">
+      <c r="F28" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -6906,7 +6918,7 @@
       <c r="E29" s="4" t="s">
         <v>358</v>
       </c>
-      <c r="F29" s="6" t="s">
+      <c r="F29" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -6926,7 +6938,7 @@
       <c r="E30" s="4" t="s">
         <v>364</v>
       </c>
-      <c r="F30" s="6" t="s">
+      <c r="F30" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -6938,6 +6950,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup fitToHeight="0" orientation="landscape"/>
+  <pageSetup fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
--- a/00_doc/axi_ahblite_bridge_vplan.xlsx
+++ b/00_doc/axi_ahblite_bridge_vplan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\axi_ahblite_bridge_vip\00_doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70671146-75B4-43D3-9973-1B78C43021AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9691DCE9-01E1-4D21-82FB-6D1C1BB83586}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="571" activeTab="3" xr2:uid="{28AB2DFB-D835-4571-8270-76E94898C9BC}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1324" uniqueCount="680">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1324" uniqueCount="681">
   <si>
     <t>ID</t>
   </si>
@@ -2082,6 +2082,9 @@
   </si>
   <si>
     <t>bridge_random_stress_seq</t>
+  </si>
+  <si>
+    <t>Excluded</t>
   </si>
 </sst>
 </file>
@@ -6439,7 +6442,7 @@
         <v>388</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -6459,7 +6462,7 @@
         <v>594</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -6479,7 +6482,7 @@
         <v>134</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -6499,7 +6502,7 @@
         <v>599</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -6519,7 +6522,7 @@
         <v>400</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -6939,7 +6942,7 @@
         <v>364</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>15</v>
+        <v>680</v>
       </c>
     </row>
   </sheetData>

--- a/00_doc/axi_ahblite_bridge_vplan.xlsx
+++ b/00_doc/axi_ahblite_bridge_vplan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\axi_ahblite_bridge_vip\00_doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9691DCE9-01E1-4D21-82FB-6D1C1BB83586}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BD4FC81-57E2-40F8-B2F1-A27652EC2E49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="571" activeTab="3" xr2:uid="{28AB2DFB-D835-4571-8270-76E94898C9BC}"/>
   </bookViews>
@@ -6522,7 +6522,7 @@
         <v>400</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">

--- a/00_doc/axi_ahblite_bridge_vplan.xlsx
+++ b/00_doc/axi_ahblite_bridge_vplan.xlsx
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1324" uniqueCount="681">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1473" uniqueCount="823">
   <si>
     <t>ID</t>
   </si>
@@ -2085,6 +2085,432 @@
   </si>
   <si>
     <t>Excluded</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidence / Gap (regression 2, 2026-09-17)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Complete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single clk drives the DUT, both agents and the SVA in bridge_tb_top; no clock-domain crossing. Verified by review.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No test. bridge_tb_top changes rst_n only on clock edges, so reset asserted away from an edge is not exercised.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALID_LOW_IN_RESET checks the power-on reset of every run; no mid-test reset is applied.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESET_DEFAULTS checks HTRANS=IDLE (and TB-driven HREADY/HRESP) during power-on reset only; HADDR/HBURST/HSIZE/HPROT reset values are not checked.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reset hooks exist (vip_env reset_state, driver/monitor flush, bridge_reset_req event) but no test triggers a mid-test reset.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Depends on BRG_RST_005.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regression 2 (2026-09-17): passes in bridge_sanity_test and bridge_incr_mapping_test, 0 scoreboard mismatches.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bridge_sanity_test; bridge_incr_mapping_test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regression 2: passes. Unwritten AHB memory returns address-derived data, so read data is checked beat by beat.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32-bit only (64-bit tracked by BRG_CFG_002). Checked by the scoreboard and by sequence read-back in all 7 tests; narrow lanes on the narrow build.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AXI IDs are randomized in every request and compared by the scoreboard. Only one outstanding transaction, so concurrent ID reuse is covered by BRG_UNS_002.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">all functional tests; planned bridge_id_test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">axi_transaction_matches; AXI driver/monitor unexpected-ID checks; B_WITH_REQUEST; R_WITH_REQUEST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lengths 1 to 256 exercised; 0 mismatches in regression 2.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">predictor beat expansion; AXI monitor WLAST/RLAST checks; WLAST_POSITION; RLAST_POSITION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs max_outstanding &gt; 1 stimulus. The predictor orders requests by monitor timestamp and publishes writes at WLAST; extend it before this test.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Depends on BRG_ARB_001.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bridge_incr_mapping_test (1B/2B/4B sizes) and bridge_burst_matrix_test; 0 mismatches.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full width, read and write; 0 mismatches.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lengths 2, 3, 5, 17, 256 at full width, read and write; 0 mismatches.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lengths 1, 16 and four random 2 to 15 per run; last-beat read-back.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Both wrap offsets, read and write; two SINGLE/NONSEQ transfers observed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every legal wrap offset at full width.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stimulus complete: 20 matrix entries x read/write with non-overlapping addresses (case_stride 0x400). Merged coverage not yet reviewed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INCR4/5/8/16 at full width, read and write.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INCR4/5/8/16 ending at offset 0x3FF, full width, read and write.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INCR4/5/8/16/256 crossings pass, but every crossing starts one beat before the boundary at full width; other crossing positions are not exercised.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Both directions at full width only; narrow sizes and the 64-bit multi-boundary 256-beat case are not exercised.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSIZE compared by the scoreboard on every beat of every test.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">all functional tests; planned bridge_size_mapping_test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The default build (narrow off) runs the full regression, and bridge_data_integrity_seq now fatals if narrow cases are requested on it. Gap: bridge_incr_mapping_test still sends single-beat 1B/2B requests (byte lane 0) on this build, outside the PG177 profile.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">default-build regression; planned bridge_narrow_disabled_test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narrow build: 8 single-beat 8/16-bit cases at byte lanes 0 to 3 pass. Narrow bursts (AxLEN &gt; 0) and 64-bit are not exercised.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bridge_data_integrity_test (narrow build); planned bridge_narrow_enabled_test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All 7 legal 32-bit patterns (0x1, 0x2, 0x4, 0x8, 0x3, 0xC, 0xF) are checked on the narrow build. 64-bit patterns are not exercised.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bridge_data_integrity_test (narrow build); planned bridge_single_wstrb_test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All stimulus uses aligned addresses; no unaligned read is sent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No negative-test policy or report catcher yet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NONCACHEABLE is active in every run, but AxCACHE is always 0, so cacheable requests are never presented.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">all functional tests; planned bridge_protection_mapping_test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The scoreboard compares HPROT, but every sequence drives AxCACHE = 0.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The scoreboard compares HPROT, but every sequence drives AxPROT = 0.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The RTL resets HPROT to 4'b0011, but no checker observes it: RESET_DEFAULTS does not check HPROT.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planned HPROT reset-value assertion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every regression transfer completes OKAY and is compared. Response coverage stays at 42.86% because ERROR is never injected.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">all functional tests; planned bridge_response_mapping_test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No AHB ERROR stimulus. BRESP_SUPPORTED/RRESP_SUPPORTED are active on OKAY traffic only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assertions implemented but never triggered: no ERROR responses in the regression.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PG177 does not define burst continuation after ERROR. The RTL continues the burst (write SLVERR sticky, read RRESP per beat) and the scoreboard models the same; confirm the oracle against the reference VHDL.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ready_delay_min/max are 0 in every test.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bready_delay_min/max are 0 in every test.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rready_delay_min/max are 0 in every test.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The default build has C_DPHASE_TIMEOUT = 0, but no long AHB wait is applied.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No timeout build in the Makefile; the predictor does not model timeout.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Depends on BRG_TMO_002.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32-bit data/address builds pass with narrow off and on. The compliance regression is still incomplete (ERROR, wait, timeout, HPROT).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No 64-bit build.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Environment-side checks only (vip_env_cfg.is_valid, transaction constructors, SVA $fatal). The DUT has no elaboration guards; no negative test.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legal traffic keeps AxLOCK low (SVA active). The RTL drives HMASTLOCK from AxLOCK; the intended behavior for lock requests is undecided and there is no negative test.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All tests run with one outstanding transaction; ordering under concurrent traffic is not exercised.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assertions active in every run, but only OKAY is observed; SLVERR paths (ERROR, timeout) are never exercised.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Built and connected in all 40 regression-2 runs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Predictor expands every AXI request; 0 mismatches in regression 2.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Includes read data; unwritten AHB memory returns address-derived data.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">check_phase requires empty queues. Gap: no check that at least one transaction was compared.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UCDB saved per run; merged report not reviewed. Unreachable bins (cp_lock.unsupported, cp_axi_status.unsupported, cp_resp.unsupported, cp_region) need waivers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Makefile failure gate for SVA/simulator errors (FAIL_REGEX) is not yet proven by fault injection.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conflict: the Tests sheet marks bridge_vhdl_equivalence_test as Excluded. Decide and align both sheets.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seeds only change AXI IDs and FIXED lengths; no constrained-random test exists.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fixed_single, incr_single, incr_undef, incr4, incr8, incr16, wrap2_single, wrap4, wrap8, wrap16 (unsupported = default)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no, yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Response mapping for both directions. cp_axi_status.unsupported (EXOKAY/DECERR) is unreachable by design; waive.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">axi4_mst_coverage.cg_control</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cp_dir, cp_burst, cp_size, cp_len, cp_lock, cp_id, cp_cache, cp_prot; cx_dir_burst, cx_dir_size, cx_dir_len</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lock normal/unsupported; len single..max; id zero/nonzero; all AxCACHE/AxPROT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AXI agent control coverage. cp_lock.unsupported is unreachable in the legal profile; waive.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRG_BST_001 to BRG_BST_011, BRG_UNS_001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">axi4_mst_coverage.cg_address</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cp_lane, cp_region, cp_aligned</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lanes 0-3; regions 0-15 (ADDR[31:28]); aligned, unaligned</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Address lane/region/alignment. cp_region does not follow a defined address map (all stimulus is below 0x1000_0000); review or waive.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reviewed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">axi4_mst_coverage.cg_response</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cp_dir, cp_resp, cx_dir_resp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">okay, slverr, unsupported</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AXI responses seen by the master. unsupported (EXOKAY/DECERR) is unreachable by design; waive.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRG_RSP_001, BRG_RSP_002, BRG_UNS_003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">axi4_mst_coverage.cg_write_strobe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cp_strb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">full, zero, partial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Write strobe shape per beat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ahb_slv_coverage.cg_transfer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cp_dir, cp_trans, cp_burst, cp_size, cp_resp, cp_wait, cp_lock, cp_prot, cp_lane; cx_dir_burst, cx_dir_size, cx_burst_resp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nonseq/seq; all HBURST; wait 0, 1-3, 4-15, 16+; lock normal/unsupported</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Completed AHB transfer coverage. cp_lock.unsupported is unreachable (NO_LOCK); waive.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRG_BST_001 to BRG_BST_010, BRG_WAI_001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ahb_slv_coverage.cg_bus_trans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cp_trans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">idle, busy, nonseq, seq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HTRANS sampled whenever HREADY is high. The RTL inserts BUSY between burst beats.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">During reset, HTRANS is IDLE, HREADY is high and HRESP is OKAY. The HPROT reset value (0011) is not checked.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HADDR is unchanged when SEQ follows BUSY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WLEN_MATCH (immediate)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A write data burst completed before its AW handshake has the beat count given by AWLEN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W_BEFORE_AW_LENGTH (immediate)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Write data started before AW does not exceed AWLEN when the AW handshake occurs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WLAST_POSITION (immediate)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WLAST is asserted exactly on the final write beat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B_WITH_REQUEST (immediate)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BVALID is asserted only for an ID whose AW and write data are complete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R_WITH_REQUEST (immediate)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RVALID is asserted only for an ID with an accepted AR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RLAST_POSITION (immediate)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RLAST is asserted exactly on the final read beat of the burst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RID_STABLE (immediate)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PG177 Ch.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Read data of different IDs is not interleaved within a burst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Four single-beat full-width write/read-back pairs at consecutive aligned addresses with zero AHB wait</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Default configuration; deterministic data; NUM_ITER, BASE_ADDR and ADDR_STRIDE plusargs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32-bit; 5 full-width INCR/WRAP/FIXED write/read-back cases; 8 single-beat narrow cases only on the C_S_AXI_SUPPORTS_NARROW_BURST=1 build (NARROW_TEST_LIST)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRG_BAS_003, BRG_SIZ_003, BRG_SIZ_004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INCR lengths 1,2,3,4,5,8,16,17,256; FIXED 1-16; WRAP 2/4/8/16; full width; one 1 KB region per case (CASE_STRIDE 0x400)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No 1 KB crossing; single-beat requests at 1/2/4-byte sizes, multi-beat requests at full width only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every legal wrap offset at full width</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exercises no-cross, exact-edge and crossing INCR4/5/8/16 cases plus a 256-beat crossing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Read/write; full width only; crossing bursts start one beat before the 1 KB boundary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Locked/exclusive requests are outside the profile. Legal traffic keeps AxLOCK low. With AxLOCK=1 the bridge completes the request with OKAY (never EXOKAY) and correct data, and HMASTLOCK follows AxLOCK for that request (reference-design behavior).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Constraint, SVA, Directed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Predictor/scoreboard per-beat HMASTLOCK compare; response and read-back checks in axi4_mst_lock_seq; LOCK_UNSUPPORTED, ARLOCK_UNSUPPORTED, NO_LOCK in legal-profile tests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bridge_unsupported_feature_test; legal-profile tests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decision 2026-09-17: keep the reference behavior, RTL unchanged (spec review 4.1). Test implemented, not yet run in a regression. Reference quirk: HMASTLOCK stays high during IDLE after a locked request until the next request.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UCDB saved per run; merged report not reviewed. Unreachable bins (cp_axi_status.unsupported, cp_resp.unsupported, cp_region) need waivers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AXI agent control coverage. cp_lock.unsupported is reached only by bridge_unsupported_feature_test.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Completed AHB transfer coverage. cp_lock.unsupported (HMASTLOCK=1) is reached only by bridge_unsupported_feature_test.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accepted AXI write request does not request an unsupported lock. Turned off at run time by bridge_unsupported_feature_test (bridge_allow_lock event).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accepted AXI read request does not request an unsupported lock. Turned off at run time by bridge_unsupported_feature_test (bridge_allow_lock event).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AHB HMASTLOCK stays low for the legal profile. Turned off at run time by bridge_unsupported_feature_test (bridge_allow_lock event).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bridge_unsupported_feature_seq (axi4_mst_lock_seq)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lock part: interleaves AxLOCK=1 and AxLOCK=0 reads/writes over SINGLE, INCR4, undefined INCR, FIXED, WRAP2 and WRAP4; checks OKAY (never EXOKAY), read-back data and per-beat HMASTLOCK. Sparse/unaligned narrow part not yet implemented.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Triggers bridge_allow_lock so bridge_tb_top turns off LOCK_UNSUPPORTED, ARLOCK_UNSUPPORTED and NO_LOCK</t>
   </si>
 </sst>
 </file>
@@ -2539,7 +2965,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J65"/>
+  <dimension ref="A1:K65"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -2552,9 +2978,10 @@
     <col min="8" max="8" width="32" customWidth="1"/>
     <col min="9" max="9" width="11" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2585,8 +3012,11 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K1" s="3" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>48</v>
       </c>
@@ -2614,11 +3044,14 @@
       <c r="I2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J2" s="7" t="s">
+        <v>682</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>54</v>
       </c>
@@ -2646,11 +3079,14 @@
       <c r="I3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J3" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J3" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>59</v>
       </c>
@@ -2681,8 +3117,11 @@
       <c r="J4" s="5" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K4" s="4" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>63</v>
       </c>
@@ -2713,8 +3152,11 @@
       <c r="J5" s="5" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K5" s="4" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>67</v>
       </c>
@@ -2742,11 +3184,14 @@
       <c r="I6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J6" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J6" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>72</v>
       </c>
@@ -2774,11 +3219,14 @@
       <c r="I7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J7" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J7" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>76</v>
       </c>
@@ -2801,16 +3249,19 @@
         <v>80</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>53</v>
+        <v>690</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J8" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J8" s="7" t="s">
+        <v>682</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>81</v>
       </c>
@@ -2838,11 +3289,14 @@
       <c r="I9" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J9" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J9" s="7" t="s">
+        <v>682</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>85</v>
       </c>
@@ -2870,11 +3324,14 @@
       <c r="I10" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J10" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J10" s="7" t="s">
+        <v>682</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>90</v>
       </c>
@@ -2894,19 +3351,22 @@
         <v>93</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>94</v>
+        <v>695</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>95</v>
+        <v>694</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J11" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J11" s="7" t="s">
+        <v>682</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>96</v>
       </c>
@@ -2926,7 +3386,7 @@
         <v>93</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>99</v>
+        <v>697</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>100</v>
@@ -2934,11 +3394,14 @@
       <c r="I12" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J12" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J12" s="7" t="s">
+        <v>682</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>101</v>
       </c>
@@ -2969,8 +3432,11 @@
       <c r="J13" s="6" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K13" s="4" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>107</v>
       </c>
@@ -3001,8 +3467,11 @@
       <c r="J14" s="6" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K14" s="4" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>112</v>
       </c>
@@ -3030,11 +3499,14 @@
       <c r="I15" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J15" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J15" s="7" t="s">
+        <v>682</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>119</v>
       </c>
@@ -3062,11 +3534,14 @@
       <c r="I16" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J16" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J16" s="7" t="s">
+        <v>682</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>123</v>
       </c>
@@ -3094,11 +3569,14 @@
       <c r="I17" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J17" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J17" s="7" t="s">
+        <v>682</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>126</v>
       </c>
@@ -3126,11 +3604,14 @@
       <c r="I18" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J18" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J18" s="7" t="s">
+        <v>682</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>129</v>
       </c>
@@ -3158,11 +3639,14 @@
       <c r="I19" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J19" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J19" s="7" t="s">
+        <v>682</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>134</v>
       </c>
@@ -3190,11 +3674,14 @@
       <c r="I20" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J20" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J20" s="7" t="s">
+        <v>682</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>139</v>
       </c>
@@ -3222,11 +3709,14 @@
       <c r="I21" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J21" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J21" s="7" t="s">
+        <v>682</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>144</v>
       </c>
@@ -3254,11 +3744,14 @@
       <c r="I22" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J22" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J22" s="7" t="s">
+        <v>682</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>149</v>
       </c>
@@ -3286,11 +3779,14 @@
       <c r="I23" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J23" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J23" s="7" t="s">
+        <v>682</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>153</v>
       </c>
@@ -3318,11 +3814,14 @@
       <c r="I24" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J24" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J24" s="7" t="s">
+        <v>682</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>157</v>
       </c>
@@ -3353,8 +3852,11 @@
       <c r="J25" s="5" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K25" s="4" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>161</v>
       </c>
@@ -3382,11 +3884,14 @@
       <c r="I26" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J26" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J26" s="7" t="s">
+        <v>682</v>
+      </c>
+      <c r="K26" s="4" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>167</v>
       </c>
@@ -3414,11 +3919,14 @@
       <c r="I27" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J27" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J27" s="7" t="s">
+        <v>682</v>
+      </c>
+      <c r="K27" s="4" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>171</v>
       </c>
@@ -3449,8 +3957,11 @@
       <c r="J28" s="5" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K28" s="4" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>176</v>
       </c>
@@ -3481,8 +3992,11 @@
       <c r="J29" s="5" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K29" s="4" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>180</v>
       </c>
@@ -3505,16 +4019,19 @@
         <v>185</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>186</v>
+        <v>712</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J30" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J30" s="7" t="s">
+        <v>682</v>
+      </c>
+      <c r="K30" s="4" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>187</v>
       </c>
@@ -3537,16 +4054,19 @@
         <v>191</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>192</v>
+        <v>714</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J31" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J31" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K31" s="4" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>193</v>
       </c>
@@ -3569,7 +4089,7 @@
         <v>197</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>198</v>
+        <v>716</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>12</v>
@@ -3577,8 +4097,11 @@
       <c r="J32" s="5" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K32" s="4" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>199</v>
       </c>
@@ -3601,7 +4124,7 @@
         <v>203</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>204</v>
+        <v>718</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>12</v>
@@ -3609,8 +4132,11 @@
       <c r="J33" s="5" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="34" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K33" s="4" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>205</v>
       </c>
@@ -3638,11 +4164,14 @@
       <c r="I34" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J34" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J34" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="K34" s="4" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>210</v>
       </c>
@@ -3673,8 +4202,11 @@
       <c r="J35" s="6" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="36" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K35" s="4" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>216</v>
       </c>
@@ -3697,7 +4229,7 @@
         <v>220</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>221</v>
+        <v>722</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>12</v>
@@ -3705,8 +4237,11 @@
       <c r="J36" s="5" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="37" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K36" s="4" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>222</v>
       </c>
@@ -3734,11 +4269,14 @@
       <c r="I37" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J37" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J37" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="K37" s="4" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>227</v>
       </c>
@@ -3766,11 +4304,14 @@
       <c r="I38" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J38" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J38" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="K38" s="4" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>231</v>
       </c>
@@ -3798,11 +4339,14 @@
       <c r="I39" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J39" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J39" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="K39" s="4" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>235</v>
       </c>
@@ -3822,7 +4366,7 @@
         <v>17</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>238</v>
+        <v>726</v>
       </c>
       <c r="H40" s="4" t="s">
         <v>58</v>
@@ -3830,11 +4374,14 @@
       <c r="I40" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J40" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J40" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="K40" s="4" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>239</v>
       </c>
@@ -3857,16 +4404,19 @@
         <v>243</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>244</v>
+        <v>728</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J41" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J41" s="7" t="s">
+        <v>682</v>
+      </c>
+      <c r="K41" s="4" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>245</v>
       </c>
@@ -3894,11 +4444,14 @@
       <c r="I42" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J42" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J42" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="K42" s="4" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>250</v>
       </c>
@@ -3926,11 +4479,14 @@
       <c r="I43" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J43" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J43" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="K43" s="4" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>255</v>
       </c>
@@ -3958,11 +4514,14 @@
       <c r="I44" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J44" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J44" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="K44" s="4" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>260</v>
       </c>
@@ -3990,11 +4549,14 @@
       <c r="I45" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J45" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J45" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="K45" s="4" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>267</v>
       </c>
@@ -4022,11 +4584,14 @@
       <c r="I46" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J46" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J46" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="K46" s="4" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>274</v>
       </c>
@@ -4054,11 +4619,14 @@
       <c r="I47" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J47" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J47" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="K47" s="4" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>278</v>
       </c>
@@ -4089,8 +4657,11 @@
       <c r="J48" s="6" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="49" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K48" s="4" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>284</v>
       </c>
@@ -4121,8 +4692,11 @@
       <c r="J49" s="6" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="50" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K49" s="4" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>288</v>
       </c>
@@ -4153,8 +4727,11 @@
       <c r="J50" s="6" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="51" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K50" s="4" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>293</v>
       </c>
@@ -4185,8 +4762,11 @@
       <c r="J51" s="6" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="52" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K51" s="4" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>298</v>
       </c>
@@ -4217,8 +4797,11 @@
       <c r="J52" s="5" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="53" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K52" s="4" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>304</v>
       </c>
@@ -4249,8 +4832,11 @@
       <c r="J53" s="6" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="54" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K53" s="4" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>308</v>
       </c>
@@ -4281,8 +4867,11 @@
       <c r="J54" s="5" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="55" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K54" s="4" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>314</v>
       </c>
@@ -4296,16 +4885,16 @@
         <v>316</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>317</v>
+        <v>809</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>318</v>
+        <v>810</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>319</v>
+        <v>811</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>320</v>
+        <v>812</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>12</v>
@@ -4313,8 +4902,11 @@
       <c r="J55" s="5" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="56" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K55" s="4" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>321</v>
       </c>
@@ -4345,8 +4937,11 @@
       <c r="J56" s="5" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="57" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K56" s="4" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>327</v>
       </c>
@@ -4374,11 +4969,14 @@
       <c r="I57" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J57" s="7" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J57" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K57" s="4" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>331</v>
       </c>
@@ -4407,10 +5005,13 @@
         <v>12</v>
       </c>
       <c r="J58" s="7" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>682</v>
+      </c>
+      <c r="K58" s="4" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>339</v>
       </c>
@@ -4439,10 +5040,13 @@
         <v>12</v>
       </c>
       <c r="J59" s="7" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>682</v>
+      </c>
+      <c r="K59" s="4" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>344</v>
       </c>
@@ -4471,10 +5075,13 @@
         <v>12</v>
       </c>
       <c r="J60" s="7" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>682</v>
+      </c>
+      <c r="K60" s="4" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>348</v>
       </c>
@@ -4503,10 +5110,13 @@
         <v>12</v>
       </c>
       <c r="J61" s="7" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>682</v>
+      </c>
+      <c r="K61" s="4" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>352</v>
       </c>
@@ -4537,8 +5147,11 @@
       <c r="J62" s="5" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="63" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K62" s="4" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>358</v>
       </c>
@@ -4569,8 +5182,11 @@
       <c r="J63" s="6" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="64" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K63" s="4" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>364</v>
       </c>
@@ -4601,8 +5217,11 @@
       <c r="J64" s="6" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="65" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K64" s="4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>370</v>
       </c>
@@ -4633,9 +5252,12 @@
       <c r="J65" s="6" t="s">
         <v>15</v>
       </c>
+      <c r="K65" s="4" t="s">
+        <v>751</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J65" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:K65" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid status" error="Select a status from the drop-down list." promptTitle="Status" prompt="Select the current verification status." sqref="J2:J1000" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Complete,In Progress,Not Started,Excluded"</formula1>
@@ -4648,7 +5270,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="28" customWidth="1"/>
@@ -5012,7 +5634,7 @@
         <v>426</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>427</v>
+        <v>752</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>428</v>
@@ -5035,7 +5657,7 @@
         <v>430</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>431</v>
+        <v>753</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>432</v>
@@ -5291,7 +5913,7 @@
         <v>470</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>471</v>
+        <v>754</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>377</v>
@@ -5395,8 +6017,146 @@
         <v>15</v>
       </c>
     </row>
+    <row r="33" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
+        <v>755</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>756</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>757</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>815</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>759</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>762</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>763</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="G34" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>766</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>767</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>768</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>769</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
+        <v>770</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>771</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>773</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="G36" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
+        <v>774</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>775</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>776</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>816</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>778</v>
+      </c>
+      <c r="G37" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
+        <v>779</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>780</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>781</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>782</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>559</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G32" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A1:G38" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid status" error="Select a status from the drop-down list." promptTitle="Status" prompt="Select the current verification status." sqref="G2:G1000" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Implemented,In Progress,Not Started,Excluded"</formula1>
@@ -5409,7 +6169,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -5768,7 +6528,7 @@
         <v>49</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>525</v>
+        <v>817</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>40</v>
@@ -5788,7 +6548,7 @@
         <v>49</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>527</v>
+        <v>818</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>40</v>
@@ -5848,13 +6608,13 @@
         <v>251</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>533</v>
+        <v>783</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>40</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>534</v>
+        <v>63</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>34</v>
@@ -6148,7 +6908,7 @@
         <v>251</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>564</v>
+        <v>784</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>40</v>
@@ -6288,7 +7048,7 @@
         <v>49</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>578</v>
+        <v>819</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>40</v>
@@ -6320,8 +7080,148 @@
         <v>34</v>
       </c>
     </row>
+    <row r="46" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
+        <v>785</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>786</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>788</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="2" t="s">
+        <v>789</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>790</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="2" t="s">
+        <v>791</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>792</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>794</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>796</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>799</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="F52" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F45" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter ref="A1:F52" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid status" error="Select a status from the drop-down list." promptTitle="Status" prompt="Select the current verification status." sqref="F2:F1000" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"Implemented,In Progress,Not Started,Excluded"</formula1>
@@ -6393,10 +7293,10 @@
         <v>655</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>585</v>
+        <v>800</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>586</v>
+        <v>801</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>587</v>
@@ -6416,10 +7316,10 @@
         <v>588</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>589</v>
+        <v>802</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>85</v>
+        <v>803</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>34</v>
@@ -6436,7 +7336,7 @@
         <v>590</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>591</v>
+        <v>804</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>388</v>
@@ -6456,7 +7356,7 @@
         <v>592</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>593</v>
+        <v>805</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>594</v>
@@ -6496,7 +7396,7 @@
         <v>597</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>598</v>
+        <v>806</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>599</v>
@@ -6513,10 +7413,10 @@
         <v>661</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>600</v>
+        <v>807</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>601</v>
+        <v>808</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>400</v>
@@ -6850,19 +7750,19 @@
         <v>320</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>677</v>
+        <v>820</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>641</v>
+        <v>821</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>642</v>
+        <v>822</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>643</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">

--- a/00_doc/axi_ahblite_bridge_vplan.xlsx
+++ b/00_doc/axi_ahblite_bridge_vplan.xlsx
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1473" uniqueCount="823">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1479" uniqueCount="828">
   <si>
     <t>ID</t>
   </si>
@@ -2511,6 +2511,21 @@
   </si>
   <si>
     <t xml:space="preserve">Triggers bridge_allow_lock so bridge_tb_top turns off LOCK_UNSUPPORTED, ARLOCK_UNSUPPORTED and NO_LOCK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Predictor/scoreboard per-beat HMASTLOCK compare; response and read-back checks in axi4_mst_lock_seq; lock=/mastlock= in transaction log lines; C_LOCKED_IDLE cover; LOCK_UNSUPPORTED, ARLOCK_UNSUPPORTED, NO_LOCK in legal-profile tests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decision 2026-09-17: keep the reference behavior, RTL unchanged (spec review 4.1). make run with seeds 38065163 and 71352677: run=30 failed=0, AHB 95/0 and AXI 30/0 mismatches. Lock values were not printed in those logs; lock=/mastlock= fields and C_LOCKED_IDLE were added afterwards and still need a run. Not yet in make regress.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C_LOCKED_IDLE (cover)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HMASTLOCK is high while HTRANS is IDLE (reference-design behavior after a locked request); first occurrence is printed to the log</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cover</t>
   </si>
 </sst>
 </file>
@@ -4891,7 +4906,7 @@
         <v>810</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>811</v>
+        <v>823</v>
       </c>
       <c r="H55" s="4" t="s">
         <v>812</v>
@@ -4903,7 +4918,7 @@
         <v>13</v>
       </c>
       <c r="K55" s="4" t="s">
-        <v>813</v>
+        <v>824</v>
       </c>
     </row>
     <row r="56" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -6169,7 +6184,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -7220,8 +7235,28 @@
         <v>34</v>
       </c>
     </row>
+    <row r="53" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>826</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="F53" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F52" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter ref="A1:F53" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid status" error="Select a status from the drop-down list." promptTitle="Status" prompt="Select the current verification status." sqref="F2:F1000" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"Implemented,In Progress,Not Started,Excluded"</formula1>

--- a/00_doc/axi_ahblite_bridge_vplan.xlsx
+++ b/00_doc/axi_ahblite_bridge_vplan.xlsx
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1479" uniqueCount="828">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1479" uniqueCount="831">
   <si>
     <t>ID</t>
   </si>
@@ -2526,6 +2526,15 @@
   </si>
   <si>
     <t xml:space="preserve">Cover</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decision 2026-09-17: keep the reference behavior, RTL unchanged (spec review 4.1). Regression 3 (5 seeds): run=30 failed=0, 0 mismatches; lock order W1 R0 W0 R1 R1 on all 6 burst types; observed HMASTLOCK stream equals predicted on all 95 beats (57 locked); no EXOKAY; C_LOCKED_IDLE fires at 155 ns. No lock=1/mastlock=1 in the 40 legal-profile runs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Built and connected in all 45 regression-3 runs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lock part (verified in regression 3): interleaves AxLOCK=1 and AxLOCK=0 reads/writes over SINGLE, INCR4, undefined INCR, FIXED, WRAP2 and WRAP4; checks OKAY (never EXOKAY), read-back data and per-beat HMASTLOCK. Sparse/unaligned narrow part (BRG_SIZ_006) not yet implemented.</t>
   </si>
 </sst>
 </file>
@@ -4914,11 +4923,11 @@
       <c r="I55" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J55" s="5" t="s">
-        <v>13</v>
+      <c r="J55" s="7" t="s">
+        <v>682</v>
       </c>
       <c r="K55" s="4" t="s">
-        <v>824</v>
+        <v>828</v>
       </c>
     </row>
     <row r="56" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -5023,7 +5032,7 @@
         <v>682</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>744</v>
+        <v>829</v>
       </c>
     </row>
     <row r="59" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -7788,7 +7797,7 @@
         <v>820</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>821</v>
+        <v>830</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>822</v>

--- a/00_doc/axi_ahblite_bridge_vplan.xlsx
+++ b/00_doc/axi_ahblite_bridge_vplan.xlsx
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1479" uniqueCount="831">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1479" uniqueCount="846">
   <si>
     <t>ID</t>
   </si>
@@ -2535,6 +2535,51 @@
   </si>
   <si>
     <t xml:space="preserve">Lock part (verified in regression 3): interleaves AxLOCK=1 and AxLOCK=0 reads/writes over SINGLE, INCR4, undefined INCR, FIXED, WRAP2 and WRAP4; checks OKAY (never EXOKAY), read-back data and per-beat HMASTLOCK. Sparse/unaligned narrow part (BRG_SIZ_006) not yet implemented.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bridge_size_mapping_test; all functional tests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSIZE compared by the scoreboard on every beat of every test. Regression 4: bridge_size_mapping_test (both builds, 5 seeds each) passes full-width SINGLE, INCR4, undefined INCR, FIXED3, WRAP2 and WRAP4 for read and write with HSIZE = AxSIZE, 0 mismatches.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">default-build regression (bridge_size_mapping_test runs full-width cases only); planned bridge_narrow_disabled_test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The default build (narrow off) runs the full regression. bridge_data_integrity_seq and bridge_size_mapping_seq fatal if narrow cases are requested on it, and bridge_size_mapping_test logs that narrow cases are skipped. Gap: bridge_incr_mapping_test still sends single-beat 1B/2B requests (byte lane 0) on this build, outside the PG177 profile.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scoreboard HSIZE/HADDR/HWDATA compare; masked read-back in axi4_mst_size_mapping_seq; cp_narrow; cx_mapping_size</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bridge_size_mapping_test (narrow build); bridge_data_integrity_test (narrow build)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regression 4, narrow build, 32-bit, 5 seeds: bridge_size_mapping_test run=48 failed=0 (AHB 126/0, AXI 48/0). 8/16-bit singles on every legal lane; 8/16-bit INCR4 (crossing a bus-word boundary), undefined INCR, FIXED3, WRAP2 and WRAP4 (wrapping immediately) with HSIZE = AxSIZE; filler bytes in non-strobed lanes never reach memory. 64-bit (32-bit narrow size) not exercised.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bridge_data_integrity_test (narrow build); bridge_size_mapping_test (narrow build); planned bridge_single_wstrb_test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All 7 legal 32-bit patterns (0x1, 0x2, 0x4, 0x8, 0x3, 0xC, 0xF) are checked on the narrow build. Regression 4: with AWSIZE full width and WSTRB 0x1/0x3, HSIZE follows WSTRB (1B/2B). 64-bit patterns are not exercised.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32-bit data/address builds pass with narrow off and on (regression 4: 55/55 runs). The compliance regression is still incomplete (ERROR, wait, timeout, HPROT).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Merged baseline, regression 4 (55 tests, make cov_report): covergroups 67.2% (323/497 bins), assertions 77.6% (38/49), cover directives 53.8% (7/13), DUT code 66.4% (79.2% hits), total 52.8% (includes testbench class code). Not reviewed bin by bin. Unreachable bins (cp_axi_status.unsupported, cp_resp.unsupported, cp_region) need waivers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bridge_size_mapping_seq (axi4_mst_size_mapping_seq)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Write then read back with the same attributes and check HSIZE per beat. Full width: SINGLE, INCR4, undefined INCR, FIXED3, WRAP2, WRAP4. Narrow build only: single transfers on every legal lane per narrow size, single writes whose size is carried only by WSTRB, and the same burst set at each narrow size.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Default build: full-width cases (run=12). Narrow build (NARROW_TEST_LIST): 24 cases on 32-bit (run=48). Non-strobed lanes carry 0xEE filler; regions on 0x100 boundaries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRG_SIZ_001, BRG_SIZ_003, BRG_SIZ_004</t>
   </si>
 </sst>
 </file>
@@ -4043,7 +4088,7 @@
         <v>185</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>712</v>
+        <v>831</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>12</v>
@@ -4052,7 +4097,7 @@
         <v>682</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>711</v>
+        <v>832</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -4078,7 +4123,7 @@
         <v>191</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>714</v>
+        <v>833</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>12</v>
@@ -4087,7 +4132,7 @@
         <v>13</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>713</v>
+        <v>834</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -4110,10 +4155,10 @@
         <v>196</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>197</v>
+        <v>835</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>716</v>
+        <v>836</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>12</v>
@@ -4122,7 +4167,7 @@
         <v>13</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>715</v>
+        <v>837</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -4148,7 +4193,7 @@
         <v>203</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>718</v>
+        <v>838</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>12</v>
@@ -4157,7 +4202,7 @@
         <v>13</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>717</v>
+        <v>839</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -4822,7 +4867,7 @@
         <v>13</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>738</v>
+        <v>840</v>
       </c>
     </row>
     <row r="53" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -5172,7 +5217,7 @@
         <v>13</v>
       </c>
       <c r="K62" s="4" t="s">
-        <v>814</v>
+        <v>841</v>
       </c>
     </row>
     <row r="63" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -7474,19 +7519,19 @@
         <v>186</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>662</v>
+        <v>842</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>602</v>
+        <v>843</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>603</v>
+        <v>844</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>604</v>
+        <v>845</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">

--- a/00_doc/axi_ahblite_bridge_vplan.xlsx
+++ b/00_doc/axi_ahblite_bridge_vplan.xlsx
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1479" uniqueCount="846">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1485" uniqueCount="885">
   <si>
     <t>ID</t>
   </si>
@@ -2580,6 +2580,123 @@
   </si>
   <si>
     <t xml:space="preserve">BRG_SIZ_001, BRG_SIZ_003, BRG_SIZ_004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full width in bridge_incr_mapping_test and bridge_burst_matrix_test; 8/16-bit single transfers in bridge_size_mapping_test (narrow build). Regression 5: 0 mismatches.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">default-build regression (all tests keep to full-width traffic)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regression 5: on the default build every test keeps to full-width traffic. bridge_incr_mapping_test, bridge_size_mapping_test, bridge_single_wstrb_test and bridge_data_integrity_test skip their narrow cases (logged) and fatal if narrow cases are requested; incr_mapping now runs 27 transactions (was 33 with out-of-profile 1B/2B singles).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whole-word read-back model in axi4_mst_single_wstrb_seq; predictor get_effective_size; scoreboard HSIZE/HADDR compare; cg_write_strobe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bridge_single_wstrb_test (both builds); bridge_size_mapping_test (narrow build); bridge_data_integrity_test (narrow build)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regression 5, 32-bit: bridge_single_wstrb_test narrow build run=66 failed=0 (9 legal cases: every legal pattern on its lane with matching AWSIZE, lane-0 patterns with full-width AWSIZE, 0xF), default build run=30 failed=0. HSIZE, HADDR and the whole written word match for every legal pattern. 64-bit patterns are not exercised.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whole-word read-back model in axi4_mst_single_wstrb_seq ([NEG] log per case); predictor fallback to AWSIZE; cp_class sparse/zero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bridge_single_wstrb_test; planned bridge_illegal_narrow_test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regression 5: single writes with zero, sparse (fallback, 9 cases) and misdirected (4 cases, narrow build) strobes are negative cases; the bridge writes the lanes selected by HADDR/HSIZE, not WSTRB (spec review 3.1). Not covered: sparse strobes inside bursts, unaligned narrow reads.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESET_HPROT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">all tests (power-on reset); planned bridge_reset_test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESET_HPROT (ahb_sva, bridge profile) checks HPROT = 4'b0011 from the second reset cycle. Regression 5: evaluated in all 65 runs, no failures. Mid-test reset is tracked by BRG_RST_005.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regression 5, full width, read and write: INCR4/5/8/16/256 crossings after the first beat, in the middle and on the last beat all map to undefined INCR and restart with NONSEQ at the predicted beat (e.g. INCR16 at beats 1, 8, 15). Narrow sizes are tracked by BRG_1KB_004.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Both directions at full width with three crossing positions (regression 5); narrow sizes and the 64-bit multi-boundary 256-beat case are not exercised.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Built and connected in all 65 regression-5 runs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">scoreboard.check_phase: empty queues and at least one AHB and one AXI comparison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">check_phase requires empty queues and now fails a test that compared no transactions. Regression 5: no run triggered either check.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Merged baseline, regression 5 (65 tests): covergroups 77.7% (327/471 bins), assertions 78.0% (39/50), cover directives 53.8% (7/13), DUT code 67.1% (79.4% hits), total 54.0% (includes testbench class code). EXOKAY/DECERR bins are illegal_bins and the address-region coverpoint was removed. Not reviewed bin by bin.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs max_outstanding &gt; 1 stimulus and a read-first check. The scoreboard and e2e coverage no longer depend on request order (matching by first-beat direction/address and by direction/ID), so a contention test can be written.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Order-independent scoreboard: AHB beats matched to requests by first-beat direction/address, AXI completions by direction/ID; RID_STABLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All tests run with one outstanding transaction; ordering under concurrent traffic is not exercised. The scoreboard is ready for it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRESP_SUPPORTED; RRESP_SUPPORTED; cp_axi_status and cp_resp illegal_bins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assertions and illegal_bins active in every run, but only OKAY is observed; SLVERR paths (ERROR, timeout) are never exercised.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32-bit data/address builds pass with narrow off and on (regression 5: 65/65 runs). The compliance regression is still incomplete (ERROR, wait, timeout, HPROT).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Response mapping for both directions. cp_axi_status.unsupported (EXOKAY/DECERR) is illegal_bins: sampling it fails the run.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cp_lane, cp_aligned</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lanes 0-3; aligned, unaligned</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Address lane and alignment. The address-region coverpoint was removed: the bridge does not remap addresses and PG177 defines no address map.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">okay, slverr; EXOKAY/DECERR are illegal_bins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AXI responses seen by the master. EXOKAY/DECERR are illegal_bins: sampling them fails the run.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">During reset, HTRANS is IDLE, HREADY is high and HRESP is OKAY. The HPROT reset value is checked by RESET_HPROT.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PG177 Ch.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPROT is 4'b0011 (non-cacheable, non-bufferable, privileged data access) during reset, checked from the second reset cycle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No 1 KB crossing; multi-beat requests at full width; single-beat requests at every AxSIZE only when the DUT supports narrow (default build: full width only, run=27)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exercises no-cross, exact-edge and crossing INCR4/5/8/16/256 cases</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Read/write; full width only; crossings after the first beat, in the middle and on the last beat (run=46)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bridge_single_wstrb_seq (axi4_mst_single_wstrb_seq)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Background write, single write (AWLEN=0), whole-word read-back. Every WSTRB value with full-width AWSIZE, plus every legal narrow pattern with matching AWSIZE on its lane; zero/sparse/misdirected strobes are negative cases logged with [NEG].</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Default build: legal full pattern + 9 fallback cases (run=30). Narrow build (NARROW_TEST_LIST): 9 legal, 4 misdirected, 9 fallback (run=66). ENABLE_NEGATIVE=0 removes negative cases</t>
   </si>
 </sst>
 </file>
@@ -3502,7 +3619,7 @@
         <v>15</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>698</v>
+        <v>864</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -3572,7 +3689,7 @@
         <v>682</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>700</v>
+        <v>846</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -4023,11 +4140,11 @@
       <c r="I28" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J28" s="5" t="s">
-        <v>13</v>
+      <c r="J28" s="7" t="s">
+        <v>682</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>709</v>
+        <v>858</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -4062,7 +4179,7 @@
         <v>13</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>710</v>
+        <v>859</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -4123,16 +4240,16 @@
         <v>191</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>833</v>
+        <v>847</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J31" s="5" t="s">
-        <v>13</v>
+      <c r="J31" s="7" t="s">
+        <v>682</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>834</v>
+        <v>848</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -4190,10 +4307,10 @@
         <v>202</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>203</v>
+        <v>849</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>838</v>
+        <v>850</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>12</v>
@@ -4202,7 +4319,7 @@
         <v>13</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>839</v>
+        <v>851</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -4260,19 +4377,19 @@
         <v>213</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>214</v>
+        <v>852</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>215</v>
+        <v>853</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J35" s="6" t="s">
-        <v>15</v>
+      <c r="J35" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>720</v>
+        <v>854</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -4435,19 +4552,19 @@
         <v>17</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>726</v>
+        <v>855</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>58</v>
+        <v>856</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J40" s="6" t="s">
-        <v>15</v>
+      <c r="J40" s="7" t="s">
+        <v>682</v>
       </c>
       <c r="K40" s="4" t="s">
-        <v>725</v>
+        <v>857</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -4867,7 +4984,7 @@
         <v>13</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>840</v>
+        <v>869</v>
       </c>
     </row>
     <row r="53" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -4995,7 +5112,7 @@
         <v>324</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>325</v>
+        <v>865</v>
       </c>
       <c r="H56" s="4" t="s">
         <v>326</v>
@@ -5007,7 +5124,7 @@
         <v>13</v>
       </c>
       <c r="K56" s="4" t="s">
-        <v>742</v>
+        <v>866</v>
       </c>
     </row>
     <row r="57" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -5030,7 +5147,7 @@
         <v>22</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>330</v>
+        <v>867</v>
       </c>
       <c r="H57" s="4" t="s">
         <v>20</v>
@@ -5042,7 +5159,7 @@
         <v>13</v>
       </c>
       <c r="K57" s="4" t="s">
-        <v>743</v>
+        <v>868</v>
       </c>
     </row>
     <row r="58" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -5077,7 +5194,7 @@
         <v>682</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>829</v>
+        <v>860</v>
       </c>
     </row>
     <row r="59" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -5170,7 +5287,7 @@
         <v>25</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>351</v>
+        <v>861</v>
       </c>
       <c r="H61" s="4" t="s">
         <v>20</v>
@@ -5182,7 +5299,7 @@
         <v>682</v>
       </c>
       <c r="K61" s="4" t="s">
-        <v>747</v>
+        <v>862</v>
       </c>
     </row>
     <row r="62" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -5217,7 +5334,7 @@
         <v>13</v>
       </c>
       <c r="K62" s="4" t="s">
-        <v>841</v>
+        <v>863</v>
       </c>
     </row>
     <row r="63" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -5982,7 +6099,7 @@
         <v>470</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>754</v>
+        <v>870</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>377</v>
@@ -6114,16 +6231,16 @@
         <v>760</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>761</v>
+        <v>871</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>762</v>
+        <v>872</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>763</v>
+        <v>873</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>764</v>
+        <v>377</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>205</v>
@@ -6140,13 +6257,13 @@
         <v>766</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>767</v>
+        <v>874</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>768</v>
+        <v>875</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="F35" s="4" t="s">
         <v>769</v>
@@ -6238,7 +6355,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -6677,7 +6794,7 @@
         <v>251</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>783</v>
+        <v>876</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>40</v>
@@ -7309,8 +7426,28 @@
         <v>34</v>
       </c>
     </row>
+    <row r="54" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>878</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="F54" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F53" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter ref="A1:F54" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid status" error="Select a status from the drop-down list." promptTitle="Status" prompt="Select the current verification status." sqref="F2:F1000" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"Implemented,In Progress,Not Started,Excluded"</formula1>
@@ -7445,7 +7582,7 @@
         <v>592</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>805</v>
+        <v>879</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>594</v>
@@ -7502,10 +7639,10 @@
         <v>661</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>807</v>
+        <v>880</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>808</v>
+        <v>881</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>400</v>
@@ -7539,19 +7676,19 @@
         <v>204</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>663</v>
+        <v>882</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>605</v>
+        <v>883</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>606</v>
+        <v>884</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>421</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">

--- a/00_doc/axi_ahblite_bridge_vplan.xlsx
+++ b/00_doc/axi_ahblite_bridge_vplan.xlsx
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1485" uniqueCount="885">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1485" uniqueCount="915">
   <si>
     <t>ID</t>
   </si>
@@ -2697,6 +2697,96 @@
   </si>
   <si>
     <t xml:space="preserve">Default build: legal full pattern + 9 fallback cases (run=30). Narrow build (NARROW_TEST_LIST): 9 legal, 4 misdirected, 9 fallback (run=66). ENABLE_NEGATIVE=0 removes negative cases</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidence / Gap (regression 6, 2026-09-18)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full width in bridge_incr_mapping_test and bridge_burst_matrix_test; 8/16-bit single transfers in bridge_size_mapping_test (narrow build). Regression 6: 0 mismatches. INCR 10, 32 and 128 added to bridge_burst_matrix_test after regression 6 (AxLEN 64-254 and other undefined-length INCR bins); not yet run.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cp_aligned.unaligned; predictor aligned HADDR; scoreboard HADDR compare; masked valid-lane data check in axi4_mst_unaligned_read_seq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bridge_unaligned_read_test (both builds)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regression 6, 5 seeds per build: full-width INCR16 background, then SINGLE/INCR4/INCR5/FIXED3 reads from every byte offset (narrow sizes from their unaligned offsets on the narrow build). Default build run=32 failed=0 unaligned=12 (308 AHB beats); narrow build run=48 failed=0 unaligned=20 (462 AHB beats); 0 mismatches. HADDR is aligned to the bus width (narrow off) or AxSIZE (narrow on) and the AXI-valid lanes carry the right data. Unaligned writes are not tested (spec review 1).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bridge_single_wstrb_test; bridge_unaligned_read_test (narrow build); planned bridge_illegal_narrow_test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regression 5: single writes with zero, sparse (fallback, 9 cases) and misdirected (4 cases, narrow build) strobes are negative cases; the bridge writes the lanes selected by HADDR/HSIZE, not WSTRB (spec review 3.1). Regression 6: unaligned narrow reads pass on the narrow build (BRG_SIZ_005). Not covered: sparse strobes inside bursts, unaligned writes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NONCACHEABLE; scoreboard HPROT compare; ahb cp_prot (HPROT[3]=1 bins are ignore_bins)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bridge_protection_mapping_test; all functional tests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regression 6: bridge_protection_mapping_test presents every legal AxCACHE, including all cacheable encodings, with every AxPROT; NONCACHEABLE never fires and the scoreboard sees HPROT[3]=0 on every beat. Merged per-bin coverage, regression 6: HPROT 0100-0111 seen 120 times each and 0000/0010/0011 240 times each, exactly as the mapping predicts over 5 seeds; 1xxx never seen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regression 6, 5 seeds: 10 legal AxCACHE x 8 AxPROT single write/read-back plus INCR4 with AxCACHE 0011 and 0010 for every AxPROT; run=192 failed=0 hprot_values=8, 288 AHB beats per run, 0 mismatches. Merged per-bin coverage, regression 6: HPROT 0100-0111 seen 120 times each and 0000/0010/0011 240 times each, exactly as the mapping predicts over 5 seeds; 1xxx never seen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regression 6: every AxPROT value on single and INCR4 transfers, read and write (bridge_protection_mapping_test, run=192 failed=0); the scoreboard compares HPROT[1] per beat. Merged per-bin coverage, regression 6: HPROT 0100-0111 seen 120 times each and 0000/0010/0011 240 times each, exactly as the mapping predicts over 5 seeds; 1xxx never seen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regression 6: every AxPROT value on single and INCR4 transfers, read and write (bridge_protection_mapping_test, run=192 failed=0); the scoreboard compares HPROT[0] per beat. Merged per-bin coverage, regression 6: HPROT 0100-0111 seen 120 times each and 0000/0010/0011 240 times each, exactly as the mapping predicts over 5 seeds; 1xxx never seen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32-bit data/address builds pass with narrow off and on (regression 6: 80/80 runs). The compliance regression is still incomplete (ERROR, wait states, timeout).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Built and connected in all 80 regression-6 runs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cg_axi_request; cg_translation; cg_ahb_response; cg_response_map; agent covergroups</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Merged baseline, regression 6 (80 tests): covergroups 84.7% (377/471 bins), assertions 78.0% (39/50), cover directives 53.8% (7/13), total 56.4% (includes testbench class code). Bin-level review of the agent covergroups and cg_axi_request: reserved AxCACHE bins are now illegal_bins (and excluded by c_cache_legal), HPROT[3]=1 bins ignore_bins; AxLEN 64-254 and other undefined-length INCR bins get stimulus in bridge_burst_matrix_test; the remaining misses are AHB ERROR, wait-state and SLVERR bins. cg_write_strobe, cg_translation, cg_ahb_response and cg_response_map still need a bin-level review.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 legal AxCACHE (6 reserved encodings are illegal_bins); all 8 AxPROT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AXI attributes feeding HPROT mapping. Regression 6: all legal bins hit by bridge_protection_mapping_test.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lock normal/unsupported; len single..max; id zero/nonzero; 10 legal AxCACHE (reserved are illegal_bins); all AxPROT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AXI agent control coverage. cp_lock.unsupported is reached only by bridge_unsupported_feature_test. cp_len.very_long (AxLEN 64-254) is reached by the INCR128 case in bridge_burst_matrix_test.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nonseq/seq; all HBURST; wait 0, 1-3, 4-15, 16+; lock normal/unsupported; HPROT 0000-0111 (HPROT[3]=1 is ignore_bins)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Completed AHB transfer coverage. cp_lock.unsupported (HMASTLOCK=1) is reached only by bridge_unsupported_feature_test; HPROT values other than 0001 only by bridge_protection_mapping_test. ERROR and wait-state bins need the P0 wait/ERROR test.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INCR lengths 1,2,3,4,5,8,10,16,17,32,128,256; FIXED 1-16; WRAP 2/4/8/16; full width; one 1 KB region per case (CASE_STRIDE 0x400)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bridge_unaligned_read_seq (axi4_mst_unaligned_read_seq)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Writes a full-width INCR16 background, then reads SINGLE, INCR4, INCR5 and FIXED3 bursts from every byte offset and checks the AXI-valid lanes of each beat; HADDR alignment is checked by the scoreboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Default build: full width, run=32 (12 unaligned). Narrow build (NARROW_TEST_LIST): adds 8/16-bit sizes at their unaligned offsets, run=48 (20 unaligned)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bridge_protection_mapping_seq (axi4_mst_protection_mapping_seq)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sweeps AxCACHE/AxPROT with write and read-back; the scoreboard checks HPROT per beat against PG177 Table 3-1 and NONCACHEABLE checks HPROT[3]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 legal AxCACHE x 8 AxPROT single transfers, plus INCR4 with AxCACHE 0011/0010 x 8 AxPROT; read and write (run=192, 288 AHB beats)</t>
   </si>
 </sst>
 </file>
@@ -3199,7 +3289,7 @@
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>681</v>
+        <v>885</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -3689,7 +3779,7 @@
         <v>682</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>846</v>
+        <v>886</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -4342,19 +4432,19 @@
         <v>19</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>208</v>
+        <v>887</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>209</v>
+        <v>888</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J34" s="6" t="s">
-        <v>15</v>
+      <c r="J34" s="7" t="s">
+        <v>682</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>719</v>
+        <v>889</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -4380,7 +4470,7 @@
         <v>852</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>853</v>
+        <v>890</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>18</v>
@@ -4389,7 +4479,7 @@
         <v>13</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>854</v>
+        <v>891</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -4412,19 +4502,19 @@
         <v>22</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>220</v>
+        <v>892</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>722</v>
+        <v>893</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J36" s="5" t="s">
-        <v>13</v>
+      <c r="J36" s="7" t="s">
+        <v>682</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>721</v>
+        <v>894</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -4455,11 +4545,11 @@
       <c r="I37" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J37" s="6" t="s">
-        <v>15</v>
+      <c r="J37" s="7" t="s">
+        <v>682</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>723</v>
+        <v>895</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -4490,11 +4580,11 @@
       <c r="I38" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J38" s="6" t="s">
-        <v>15</v>
+      <c r="J38" s="7" t="s">
+        <v>682</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>724</v>
+        <v>896</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -4525,11 +4615,11 @@
       <c r="I39" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J39" s="6" t="s">
-        <v>15</v>
+      <c r="J39" s="7" t="s">
+        <v>682</v>
       </c>
       <c r="K39" s="4" t="s">
-        <v>724</v>
+        <v>897</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -4984,7 +5074,7 @@
         <v>13</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>869</v>
+        <v>898</v>
       </c>
     </row>
     <row r="53" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -5194,7 +5284,7 @@
         <v>682</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>860</v>
+        <v>899</v>
       </c>
     </row>
     <row r="59" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -5322,7 +5412,7 @@
         <v>355</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>356</v>
+        <v>900</v>
       </c>
       <c r="H62" s="4" t="s">
         <v>357</v>
@@ -5334,7 +5424,7 @@
         <v>13</v>
       </c>
       <c r="K62" s="4" t="s">
-        <v>863</v>
+        <v>901</v>
       </c>
     </row>
     <row r="63" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -5659,10 +5749,10 @@
         <v>401</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>402</v>
+        <v>902</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>403</v>
+        <v>903</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>377</v>
@@ -6211,10 +6301,10 @@
         <v>756</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>757</v>
+        <v>904</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>815</v>
+        <v>905</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>384</v>
@@ -6303,10 +6393,10 @@
         <v>775</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>776</v>
+        <v>906</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>816</v>
+        <v>907</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>384</v>
@@ -7562,7 +7652,7 @@
         <v>590</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>804</v>
+        <v>908</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>388</v>
@@ -7696,19 +7786,19 @@
         <v>209</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>664</v>
+        <v>909</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>607</v>
+        <v>910</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>608</v>
+        <v>911</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>205</v>
+        <v>396</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -7716,19 +7806,19 @@
         <v>221</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>665</v>
+        <v>912</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>609</v>
+        <v>913</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>610</v>
+        <v>914</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>404</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">

--- a/00_doc/axi_ahblite_bridge_vplan.xlsx
+++ b/00_doc/axi_ahblite_bridge_vplan.xlsx
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1485" uniqueCount="915">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1485" uniqueCount="922">
   <si>
     <t>ID</t>
   </si>
@@ -2787,6 +2787,27 @@
   </si>
   <si>
     <t xml:space="preserve">10 legal AxCACHE x 8 AxPROT single transfers, plus INCR4 with AxCACHE 0011/0010 x 8 AxPROT; read and write (run=192, 288 AHB beats)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidence / Gap (regression 7, 2026-09-18)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full width in bridge_incr_mapping_test and bridge_burst_matrix_test (INCR 1,2,3,4,5,8,10,16,17,32,128,256); 8/16-bit single transfers in bridge_size_mapping_test (narrow build). Regression 7: burst_matrix run=62 failed=0, 1614 AHB beats, 0 mismatches; cp_len.very_long and &lt;incr,other&gt; now covered.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32-bit data/address builds pass with narrow off and on (regression 7: 80/80 runs). The compliance regression is still incomplete (ERROR, wait states, timeout).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Built and connected in all 80 regression-7 runs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Merged, regression 7 (80 tests): covergroups 84.5% of bins hit (381/451; 85.9% weighted), assertions 78.0% (39/50), cover directives 53.8% (7/13), total 56.5% (includes testbench class code). At 100%: axi4 cg_control, cg_address, cg_write_strobe; ahb cg_bus_trans; e2e cg_axi_request. 70 misses: 53 need AHB ERROR/wait/SLVERR stimulus (P0); 8 need narrow INCR8/16 and WRAP8/16 (cg_translation.cx_mapping_size); 1 needs a zero strobe on a narrow write; 8 unreachable bins still counted (5 over-wide cg_ahb_response.cp_size, 2 full/sparse strobe on a 32-bit narrow write, 1 cx_error_map AHB ERROR with AXI OKAY).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AXI agent control coverage. cp_lock.unsupported is reached only by bridge_unsupported_feature_test. cp_len.very_long (AxLEN 64-254) is reached by the INCR128 case in bridge_burst_matrix_test. Regression 7: 100%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INCR lengths 1,2,3,4,5,8,10,16,17,32,128,256; FIXED 1-16; WRAP 2/4/8/16; full width; one 1 KB region per case (CASE_STRIDE 0x400); run=62</t>
   </si>
 </sst>
 </file>
@@ -3289,7 +3310,7 @@
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>885</v>
+        <v>915</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -3779,7 +3800,7 @@
         <v>682</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>886</v>
+        <v>916</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -5074,7 +5095,7 @@
         <v>13</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>898</v>
+        <v>917</v>
       </c>
     </row>
     <row r="53" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -5284,7 +5305,7 @@
         <v>682</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>899</v>
+        <v>918</v>
       </c>
     </row>
     <row r="59" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -5424,7 +5445,7 @@
         <v>13</v>
       </c>
       <c r="K62" s="4" t="s">
-        <v>901</v>
+        <v>919</v>
       </c>
     </row>
     <row r="63" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -6304,7 +6325,7 @@
         <v>904</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>905</v>
+        <v>920</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>384</v>
@@ -7652,7 +7673,7 @@
         <v>590</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>908</v>
+        <v>921</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>388</v>

--- a/00_doc/axi_ahblite_bridge_vplan.xlsx
+++ b/00_doc/axi_ahblite_bridge_vplan.xlsx
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1485" uniqueCount="922">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1485" uniqueCount="937">
   <si>
     <t>ID</t>
   </si>
@@ -2808,6 +2808,51 @@
   </si>
   <si>
     <t xml:space="preserve">INCR lengths 1,2,3,4,5,8,10,16,17,32,128,256; FIXED 1-16; WRAP 2/4/8/16; full width; one 1 KB region per case (CASE_STRIDE 0x400); run=62</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidence / Gap (regression 8, 2026-09-18)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regression 8, narrow build, 32-bit, 5 seeds: bridge_size_mapping_test run=64 failed=0 (AHB 318/0, AXI 64/0). 8/16-bit singles on every legal lane; 8/16-bit INCR4 and INCR8 (crossing a bus-word boundary), INCR16, undefined INCR, FIXED3, WRAP2, WRAP4, WRAP8 and WRAP16 (wrapping inside the burst) with HSIZE = AxSIZE; filler bytes in non-strobed lanes never reach memory; cx_mapping_size at 100%. 64-bit (32-bit narrow size) not exercised.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single writes with zero, sparse (fallback, 11 cases incl. WSTRB=0 with 1B/2B AWSIZE on the narrow build) and misdirected (4 cases, narrow build) strobes are negative cases; the bridge writes the lanes selected by HADDR/HSIZE, not WSTRB (spec review 3.1). Regression 8: narrow run=72 failed=0, WSTRB=0 with narrow AWSIZE writes the AWSIZE lanes at AWADDR. Unaligned narrow reads pass (BRG_SIZ_005). Not covered: sparse strobes inside bursts, unaligned writes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32-bit data/address builds pass with narrow off and on (regression 8: 80/80 runs). The compliance regression is still incomplete (ERROR, wait states, timeout).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Built and connected in all 80 regression-8 runs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Merged, regression 8 (80 tests): covergroups 88.0% of bins hit (390/443; 87.8% weighted), assertions 78.0% (39/50), cover directives 53.8% (7/13), total 56.8% (includes testbench class code). Every bin reachable with OKAY/zero-wait stimulus is hit (axi4 cg_control/cg_address/cg_write_strobe, ahb cg_bus_trans, e2e cg_axi_request/cg_write_strobe/cg_translation at 100%). Unreachable bins are excluded (illegal: reserved AxCACHE, full strobe on narrow write, AHB ERROR with AXI OKAY; ignore: HPROT[3]=1, sparse strobe on narrow write; default: sizes wider than the bus). The 53 misses are all ERROR/wait/SLVERR bins (cg_response 3, cg_transfer 12, cg_ahb_response 28, cg_response_map 10).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">strobe class x narrow; &lt;full,narrow&gt; illegal_bins, &lt;sparse,narrow&gt; ignore_bins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WSTRB shape versus requested narrow/full width. A narrow write may only strobe the lanes of its size (AXI4); a sparse narrow strobe is unreachable on 32-bit and a negative case on 64-bit. Regression 8: 100%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AHB response and wait duration. cp_size counts only sizes up to the bus width. Needs the P0 wait/ERROR test.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AHB error x AXI status; &lt;error,okay&gt; illegal_bins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OKAY maps to OKAY and ERROR maps to SLVERR. An AHB ERROR returned as AXI OKAY hits illegal_bins and fails the run. &lt;okay,slverr&gt; needs a timeout.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Write then read back with the same attributes and check HSIZE per beat. Full width: SINGLE, INCR4, undefined INCR, FIXED3, WRAP2, WRAP4. Narrow build only: single transfers on every legal lane per narrow size, single writes whose size is carried only by WSTRB, the same burst set at each narrow size, and INCR8, INCR16, WRAP8 and WRAP16 at each narrow size.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Default build: full-width cases (run=12). Narrow build (NARROW_TEST_LIST): 32 cases on 32-bit (run=64). Non-strobed lanes carry 0xEE filler; regions on 0x100 boundaries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Background write, single write (AWLEN=0), whole-word read-back. Every WSTRB value with full-width AWSIZE, every legal narrow pattern with matching AWSIZE on its lane, and WSTRB=0 with each narrow AWSIZE; zero/sparse/misdirected strobes are negative cases logged with [NEG].</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Default build: legal full pattern + 9 fallback cases (run=30). Narrow build (NARROW_TEST_LIST): 9 legal, 4 misdirected, 11 fallback (run=72). ENABLE_NEGATIVE=0 removes negative cases</t>
   </si>
 </sst>
 </file>
@@ -3310,7 +3355,7 @@
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>915</v>
+        <v>922</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -4395,7 +4440,7 @@
         <v>13</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>837</v>
+        <v>923</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -4500,7 +4545,7 @@
         <v>13</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>891</v>
+        <v>924</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -5095,7 +5140,7 @@
         <v>13</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>917</v>
+        <v>925</v>
       </c>
     </row>
     <row r="53" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -5305,7 +5350,7 @@
         <v>682</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>918</v>
+        <v>926</v>
       </c>
     </row>
     <row r="59" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -5445,7 +5490,7 @@
         <v>13</v>
       </c>
       <c r="K62" s="4" t="s">
-        <v>919</v>
+        <v>927</v>
       </c>
     </row>
     <row r="63" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -5908,10 +5953,10 @@
         <v>422</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>423</v>
+        <v>928</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>424</v>
+        <v>929</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>384</v>
@@ -6118,7 +6163,7 @@
         <v>454</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>455</v>
+        <v>930</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>377</v>
@@ -6184,10 +6229,10 @@
         <v>465</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>466</v>
+        <v>931</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>467</v>
+        <v>932</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>384</v>
@@ -7770,10 +7815,10 @@
         <v>842</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>843</v>
+        <v>933</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>844</v>
+        <v>934</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>845</v>
@@ -7790,10 +7835,10 @@
         <v>882</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>883</v>
+        <v>935</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>884</v>
+        <v>936</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>421</v>

--- a/00_doc/axi_ahblite_bridge_vplan.xlsx
+++ b/00_doc/axi_ahblite_bridge_vplan.xlsx
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1485" uniqueCount="937">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1485" uniqueCount="958">
   <si>
     <t>ID</t>
   </si>
@@ -2853,6 +2853,69 @@
   </si>
   <si>
     <t xml:space="preserve">Default build: legal full pattern + 9 fallback cases (run=30). Narrow build (NARROW_TEST_LIST): 9 legal, 4 misdirected, 11 fallback (run=72). ENABLE_NEGATIVE=0 removes negative cases</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidence / Gap (regression 9, 2026-09-21)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">all functional tests; bridge_response_mapping_test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every regression transfer is compared. Regression 9, 5 seeds: bridge_response_mapping_test run=39 failed=0, 210 AHB beats (35 ERROR, 36 waited), 34 SLVERR responses, 0 scoreboard mismatches. All-OKAY bursts with 0-16 wait states return OKAY on every beat. cg_response_map at 17/19 (the 2 misses need a timeout or are unreachable).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regression 9, 5 seeds: bridge_response_mapping_test run=39 failed=0, 210 AHB beats (35 ERROR, 36 waited), 34 SLVERR responses, 0 scoreboard mismatches. Every burst with an ERROR beat returns BRESP=SLVERR; RRESP is SLVERR on exactly the errored beats; no EXOKAY/DECERR (BRESP_SUPPORTED, RRESP_SUPPORTED, illegal_bins). cx_error_map &lt;ERROR,OKAY&gt; is illegal_bins and was never hit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regression 9: the reactive AHB slave drives 35 two-cycle ERROR responses per run; ERROR_FIRST_CYCLE, ERROR_SECOND_CYCLE and ERROR_HAS_FIRST_CYCLE evaluate on every one without failure, and the bridge completes the burst after each ERROR.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cx_position_resp; scoreboard queue counts; response plan (a planned beat never issued fails the case)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oracle confirmed against the reference VHDL: the AHB state machine samples HRESP into slv_err_resp and continues the burst; WR_ERR_REG makes BRESP SLVERR sticky until write_complete; RRESP is per beat (spec review 3.4). Regression 9, 5 seeds: bridge_response_mapping_test run=39 failed=0, 210 AHB beats (35 ERROR, 36 waited), 34 SLVERR responses, 0 scoreboard mismatches. ERROR on the first, a middle and the last beat, on two beats of one burst and on every AHB burst shape; every burst completes all its beats (no planned beat left, no unplanned beat).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regression 9: bridge_response_mapping_test holds HREADY low for 1, 2, 8 and 16 cycles with OKAY and with ERROR; the scoreboard sees no extra or missing beats and cp_wait/cx_resp_wait are fully hit except &lt;ERROR, zero wait&gt;, which is unreachable (an AHB ERROR always has one HREADY-low cycle). Randomized waits are left to the random stress test.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32-bit data/address builds pass with narrow off and on (regression 9: 85/85 runs), including AHB ERROR and wait states. Timeout and 64-bit are not exercised.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Built and connected in all 85 regression-9 runs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Merged, regression 9 (85 tests): covergroups 99.3% of bins hit (440/443; 99.2% weighted), assertions 88.0% (44/50), cover directives 76.9% (10/13), total 63.2% (includes testbench class code). Every covergroup is at 100% except e2e cg_ahb_response (61/62) and cg_response_map (17/19). The 3 misses: cx_resp_wait &lt;ERROR,zero wait&gt; and cx_wait_status &lt;zero wait,SLVERR&gt; are unreachable (need ignore_bins); cx_error_map &lt;OKAY,SLVERR&gt; needs a timeout build. Assertions and cover directives not yet reviewed individually.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AHB response and wait duration. cp_size counts only sizes up to the bus width. Regression 9: hit by bridge_response_mapping_test.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error injection at every burst position. Regression 9: 100% (bridge_response_mapping_test).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OKAY/ERROR with and without wait states. &lt;ERROR, zero wait&gt; is unreachable: an AHB ERROR always has one HREADY-low cycle.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Response correctness under delayed completion. &lt;zero wait, SLVERR&gt; is unreachable without a timeout: an AHB ERROR always has one HREADY-low cycle.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bridge_response_mapping_seq (axi4_mst_response_mapping_seq, ahb_slv_response_mapping_seq, ahb_response_policy)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reactive AHB slave answers every beat from a plan set by the AXI sequence. Every AHB burst shape with one ERROR beat; ERROR at the first, a middle and the last beat; two ERROR beats in one burst; waits 1/2/8/16 with OKAY and ERROR. Checks BRESP, per-beat RRESP, beat count, OKAY read data and that every planned beat is issued.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">auto_gen_resp=0; full width; read/write; waits 0,1,2,8,16; 39 cases (run=39, 210 AHB beats)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRG_RSP_001 to BRG_RSP_004, BRG_WAI_001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Merged into bridge_response_mapping_test: ERROR on the first, middle and last beat, and on two beats of one burst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Merged into bridge_response_mapping_test: waits 1, 2, 8 and 16 with OKAY and ERROR</t>
   </si>
 </sst>
 </file>
@@ -3355,7 +3418,7 @@
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>922</v>
+        <v>937</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -4746,7 +4809,7 @@
         <v>243</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>728</v>
+        <v>938</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>12</v>
@@ -4755,7 +4818,7 @@
         <v>682</v>
       </c>
       <c r="K41" s="4" t="s">
-        <v>727</v>
+        <v>939</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -4786,11 +4849,11 @@
       <c r="I42" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J42" s="6" t="s">
-        <v>15</v>
+      <c r="J42" s="7" t="s">
+        <v>682</v>
       </c>
       <c r="K42" s="4" t="s">
-        <v>729</v>
+        <v>940</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -4821,11 +4884,11 @@
       <c r="I43" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J43" s="6" t="s">
-        <v>15</v>
+      <c r="J43" s="7" t="s">
+        <v>682</v>
       </c>
       <c r="K43" s="4" t="s">
-        <v>730</v>
+        <v>941</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -4848,19 +4911,19 @@
         <v>116</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>258</v>
+        <v>942</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J44" s="6" t="s">
-        <v>15</v>
+      <c r="J44" s="7" t="s">
+        <v>682</v>
       </c>
       <c r="K44" s="4" t="s">
-        <v>731</v>
+        <v>943</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -4886,16 +4949,16 @@
         <v>265</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>266</v>
+        <v>244</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J45" s="6" t="s">
-        <v>15</v>
+      <c r="J45" s="7" t="s">
+        <v>682</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>732</v>
+        <v>944</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -5140,7 +5203,7 @@
         <v>13</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>925</v>
+        <v>945</v>
       </c>
     </row>
     <row r="53" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -5350,7 +5413,7 @@
         <v>682</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>926</v>
+        <v>946</v>
       </c>
     </row>
     <row r="59" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -5490,7 +5553,7 @@
         <v>13</v>
       </c>
       <c r="K62" s="4" t="s">
-        <v>927</v>
+        <v>947</v>
       </c>
     </row>
     <row r="63" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -6163,7 +6226,7 @@
         <v>454</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>930</v>
+        <v>948</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>377</v>
@@ -6186,7 +6249,7 @@
         <v>458</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>459</v>
+        <v>949</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>377</v>
@@ -6209,7 +6272,7 @@
         <v>461</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>462</v>
+        <v>950</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>377</v>
@@ -6278,7 +6341,7 @@
         <v>473</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>474</v>
+        <v>951</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>377</v>
@@ -7892,19 +7955,19 @@
         <v>244</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>666</v>
+        <v>952</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>611</v>
+        <v>953</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>612</v>
+        <v>954</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>613</v>
+        <v>955</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -7912,10 +7975,10 @@
         <v>259</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>614</v>
+        <v>956</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>615</v>
@@ -7924,7 +7987,7 @@
         <v>255</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -7932,10 +7995,10 @@
         <v>266</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>616</v>
+        <v>957</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>617</v>
@@ -7944,7 +8007,7 @@
         <v>260</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">

--- a/00_doc/axi_ahblite_bridge_vplan.xlsx
+++ b/00_doc/axi_ahblite_bridge_vplan.xlsx
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1485" uniqueCount="958">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1485" uniqueCount="968">
   <si>
     <t>ID</t>
   </si>
@@ -2916,6 +2916,36 @@
   </si>
   <si>
     <t xml:space="preserve">Merged into bridge_response_mapping_test: waits 1, 2, 8 and 16 with OKAY and ERROR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidence / Gap (regression 10, 2026-09-21)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every regression transfer is compared. Regression 10, 5 seeds: bridge_response_mapping_test run=39 failed=0, 210 AHB beats (35 ERROR, 36 waited), 34 SLVERR responses, 0 scoreboard mismatches. All-OKAY bursts with 0-16 wait states return OKAY on every beat. cg_response_map at 17/18 (the miss needs a timeout build).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regression 10: bridge_response_mapping_test holds HREADY low for 1, 2, 8 and 16 cycles with OKAY and with ERROR; the scoreboard sees no extra or missing beats; cp_wait, cx_resp_wait and cx_wait_status are at 100% (&lt;ERROR, zero wait&gt; and &lt;zero wait, SLVERR&gt; are ignore_bins: an AHB ERROR always has one HREADY-low cycle). Randomized waits are left to the random stress test.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32-bit data/address builds pass with narrow off and on (regression 10: 85/85 runs, 0 UVM warnings), including AHB ERROR and wait states. Timeout and 64-bit are not exercised.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Built and connected in all 85 regression-10 runs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Merged, regression 10 (85 tests, 0 warnings): covergroups 99.8% of bins hit (440/441; 99.6% weighted), assertions 88.0% (44/50), cover directives 76.9% (10/13), total 63.2% (includes testbench class code). Every covergroup is at 100% except e2e cg_response_map (17/18); the miss, cx_error_map &lt;OKAY,SLVERR&gt;, needs a timeout build. All unreachable bins are illegal_bins, ignore_bins or default. Assertions and cover directives not yet reviewed individually.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">response x wait bucket; &lt;ERROR, zero wait&gt; ignore_bins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OKAY/ERROR with and without wait states. &lt;ERROR, zero wait&gt; is ignore_bins: an AHB ERROR always has one HREADY-low cycle. Regression 10: 100%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AHB wait x AXI status; &lt;zero wait, SLVERR&gt; ignore_bins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Response correctness under delayed completion. &lt;zero wait, SLVERR&gt; is ignore_bins: an AHB ERROR or a timeout always holds HREADY low for at least one cycle. Regression 10: 100%.</t>
   </si>
 </sst>
 </file>
@@ -3418,7 +3448,7 @@
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>937</v>
+        <v>958</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -4818,7 +4848,7 @@
         <v>682</v>
       </c>
       <c r="K41" s="4" t="s">
-        <v>939</v>
+        <v>959</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -4958,7 +4988,7 @@
         <v>682</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>944</v>
+        <v>960</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -5203,7 +5233,7 @@
         <v>13</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>945</v>
+        <v>961</v>
       </c>
     </row>
     <row r="53" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -5413,7 +5443,7 @@
         <v>682</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>946</v>
+        <v>962</v>
       </c>
     </row>
     <row r="59" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -5553,7 +5583,7 @@
         <v>13</v>
       </c>
       <c r="K62" s="4" t="s">
-        <v>947</v>
+        <v>963</v>
       </c>
     </row>
     <row r="63" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -6269,10 +6299,10 @@
         <v>460</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>461</v>
+        <v>964</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>950</v>
+        <v>965</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>377</v>
@@ -6338,10 +6368,10 @@
         <v>472</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>473</v>
+        <v>966</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>951</v>
+        <v>967</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>377</v>

--- a/00_doc/axi_ahblite_bridge_vplan.xlsx
+++ b/00_doc/axi_ahblite_bridge_vplan.xlsx
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1485" uniqueCount="968">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1485" uniqueCount="980">
   <si>
     <t>ID</t>
   </si>
@@ -2946,6 +2946,42 @@
   </si>
   <si>
     <t xml:space="preserve">Response correctness under delayed completion. &lt;zero wait, SLVERR&gt; is ignore_bins: an AHB ERROR or a timeout always holds HREADY low for at least one cycle. Regression 10: 100%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidence / Gap (regression 11, 2026-09-22)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every regression transfer is compared. Regression 11, 5 seeds: bridge_response_mapping_test run=61 failed=0, 384 AHB beats (44 ERROR, 172 waited), 43 SLVERR responses, 0 scoreboard mismatches. All-OKAY bursts with 1-16 wait states (read and write, INCR4/INCR16/WRAP8/FIXED3/1 KB split, per-beat waits) return OKAY on every beat. cg_response_map at 17/18 (the miss needs a timeout build).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regression 11, 5 seeds: bridge_response_mapping_test run=61 failed=0, 384 AHB beats (44 ERROR, 172 waited), 43 SLVERR responses, 0 scoreboard mismatches. Every burst with an ERROR beat returns BRESP=SLVERR; RRESP is SLVERR on exactly the errored beats; no EXOKAY/DECERR (BRESP_SUPPORTED, RRESP_SUPPORTED, illegal_bins). cx_error_map &lt;ERROR,OKAY&gt; is illegal_bins and was never hit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oracle confirmed against the reference VHDL: the AHB state machine samples HRESP into slv_err_resp and continues the burst; WR_ERR_REG makes BRESP SLVERR sticky until write_complete; RRESP is per beat (spec review 3.4). Regression 11, 5 seeds: bridge_response_mapping_test run=61 failed=0, 384 AHB beats (44 ERROR, 172 waited), 43 SLVERR responses, 0 scoreboard mismatches. ERROR on the first, a middle and the last beat with 0 and 3 waits, on two beats of one burst, on every AHB burst shape and on the NONSEQ restart beat after a 1 KB split; every burst completes all its beats (no planned beat left, no unplanned beat).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regression 11, 5 seeds: bridge_response_mapping_test run=61 failed=0, 384 AHB beats (44 ERROR, 172 waited), 43 SLVERR responses, 0 scoreboard mismatches. HREADY is held low for 1, 2, 3, 8 and 16 cycles with OKAY and ERROR, read and write, on INCR4, INCR16, WRAP8, FIXED3 and across a 1 KB split, plus a different wait on every beat of an INCR8 (0/5/1/16/0/2/0/3). No extra or missing beats; cp_wait, cx_resp_wait and cx_wait_status at 100%. Randomized waits are left to the random stress test.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32-bit data/address builds pass with narrow off and on (regression 11: 85/85 runs, 0 UVM warnings), including AHB ERROR and wait states. Timeout and 64-bit are not exercised.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Built and connected in all 85 regression-11 runs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Merged, regression 11 (85 tests, 0 warnings): covergroups 99.8% of bins hit (440/441), assertions 88.0% (44/50), cover directives 76.9% (10/13). Every covergroup is at 100% except e2e cg_response_map (17/18); the miss, cx_error_map &lt;OKAY,SLVERR&gt;, needs a timeout build. All unreachable bins are illegal_bins, ignore_bins or default. Assertions and cover directives not yet reviewed individually.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reactive AHB slave answers every beat from a plan set by the AXI sequence. Every AHB burst shape with one ERROR beat; ERROR at the first, a middle and the last beat with 0 and 3 waits; two ERROR beats in one burst; waits 1/2/8/16 with OKAY (read and write) and ERROR; waits on WRAP8/FIXED3/INCR16; INCR16 across a 1 KB split with waits and with ERROR on the restart beat; per-beat waits. Checks BRESP, per-beat RRESP, beat count, OKAY read data and that every planned beat is issued.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">auto_gen_resp=0; full width; read/write; waits 0,1,2,3,8,16 and per-beat; 61 cases (run=61, 384 AHB beats)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Merged into bridge_response_mapping_test: ERROR on the first, middle and last beat with and without waits, on two beats of one burst and on the restart beat of a 1 KB split</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Merged into bridge_response_mapping_test: waits 1, 2, 3, 8 and 16 with OKAY and ERROR, read and write, on INCR/WRAP/FIXED and across a 1 KB split, and per-beat waits</t>
   </si>
 </sst>
 </file>
@@ -3448,7 +3484,7 @@
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>958</v>
+        <v>968</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -4848,7 +4884,7 @@
         <v>682</v>
       </c>
       <c r="K41" s="4" t="s">
-        <v>959</v>
+        <v>969</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -4883,7 +4919,7 @@
         <v>682</v>
       </c>
       <c r="K42" s="4" t="s">
-        <v>940</v>
+        <v>970</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -4953,7 +4989,7 @@
         <v>682</v>
       </c>
       <c r="K44" s="4" t="s">
-        <v>943</v>
+        <v>971</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -4988,7 +5024,7 @@
         <v>682</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>960</v>
+        <v>972</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -5233,7 +5269,7 @@
         <v>13</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>961</v>
+        <v>973</v>
       </c>
     </row>
     <row r="53" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -5443,7 +5479,7 @@
         <v>682</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>962</v>
+        <v>974</v>
       </c>
     </row>
     <row r="59" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -5583,7 +5619,7 @@
         <v>13</v>
       </c>
       <c r="K62" s="4" t="s">
-        <v>963</v>
+        <v>975</v>
       </c>
     </row>
     <row r="63" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -7988,10 +8024,10 @@
         <v>952</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>953</v>
+        <v>976</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>954</v>
+        <v>977</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>955</v>
@@ -8008,7 +8044,7 @@
         <v>666</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>956</v>
+        <v>978</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>615</v>
@@ -8028,7 +8064,7 @@
         <v>666</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>957</v>
+        <v>979</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>617</v>

--- a/00_doc/axi_ahblite_bridge_vplan.xlsx
+++ b/00_doc/axi_ahblite_bridge_vplan.xlsx
@@ -4081,7 +4081,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>Merged, regression 11 (85 tests, 0 warnings): covergroups 99.8% of bins hit (440/441), assertions 88.0% (44/50), cover directives 76.9% (10/13). Every covergroup is at 100% except e2e cg_response_map (17/18); the miss, cx_error_map &lt;OKAY,SLVERR&gt;, needs a timeout build. All unreachable bins are illegal_bins, ignore_bins or default. Assertions and cover directives not yet reviewed individually.</t>
+          <t>Merged, regression 12 (90 tests, 0 warnings, 0 failures): assertions 100% (50/50, 0 failures) and cover directives 100% (13/13), both reviewed individually from the assert_report text reports. The four address rules (INCR_ADDRESS, WRAP4/8/16_ADDRESS) and C_WAIT_STATE were vacuous until regression 12 because they assumed HTRANS stays NONSEQ/SEQ where the bridge drives BUSY; reworked and now hit. WLEN_MATCH and W_BEFORE_AW_LENGTH are unreachable on this DUT and waived (see the Assertions sheet). Covergroups were last measured in regression 11: 99.8% of bins (440/441), every covergroup at 100% except e2e cg_response_map (17/18); the miss, cx_error_map &lt;OKAY,SLVERR&gt;, needs a timeout build. All unreachable bins are illegal_bins, ignore_bins or default. Covergroups not re-measured in regression 12 (cov_report not re-run).</t>
         </is>
       </c>
     </row>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>SEQ address increments by the transfer size Reworked after regression 12: the original form required $past(HTRANS) != BUSY, but the bridge drives BUSY before every SEQ beat, so it never evaluated (pass count 0 in all 90 runs). It now compares against the last issued NONSEQ/SEQ beat. Pending re-run.</t>
+          <t>SEQ address increments by the transfer size Reworked after regression 12: the original form required $past(HTRANS) != BUSY, but the bridge drives BUSY before every SEQ beat, so it never evaluated (pass count 0 in all 90 runs). It now compares against the last issued NONSEQ/SEQ beat and is hit in 65 of 90 runs with 0 failures.</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -6868,7 +6868,7 @@
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>Implemented, pending re-run</t>
+          <t>Implemented</t>
         </is>
       </c>
     </row>
@@ -6917,7 +6917,7 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>WRAP4 address sequence wraps at four transfers Reworked after regression 12: the original form required $past(HTRANS) != BUSY, but the bridge drives BUSY before every SEQ beat, so it never evaluated (pass count 0 in all 90 runs). It now compares against the last issued NONSEQ/SEQ beat. Pending re-run.</t>
+          <t>WRAP4 address sequence wraps at four transfers Reworked after regression 12: the original form required $past(HTRANS) != BUSY, but the bridge drives BUSY before every SEQ beat, so it never evaluated (pass count 0 in all 90 runs). It now compares against the last issued NONSEQ/SEQ beat and is hit in 45 of 90 runs with 0 failures.</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -6932,7 +6932,7 @@
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>Implemented, pending re-run</t>
+          <t>Implemented</t>
         </is>
       </c>
     </row>
@@ -6949,7 +6949,7 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>WRAP8 address sequence wraps at eight transfers Reworked after regression 12: the original form required $past(HTRANS) != BUSY, but the bridge drives BUSY before every SEQ beat, so it never evaluated (pass count 0 in all 90 runs). It now compares against the last issued NONSEQ/SEQ beat. Pending re-run.</t>
+          <t>WRAP8 address sequence wraps at eight transfers Reworked after regression 12: the original form required $past(HTRANS) != BUSY, but the bridge drives BUSY before every SEQ beat, so it never evaluated (pass count 0 in all 90 runs). It now compares against the last issued NONSEQ/SEQ beat and is hit in 25 of 90 runs with 0 failures.</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>Implemented, pending re-run</t>
+          <t>Implemented</t>
         </is>
       </c>
     </row>
@@ -6981,7 +6981,7 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>WRAP16 address sequence wraps at sixteen transfers Reworked after regression 12: the original form required $past(HTRANS) != BUSY, but the bridge drives BUSY before every SEQ beat, so it never evaluated (pass count 0 in all 90 runs). It now compares against the last issued NONSEQ/SEQ beat. Pending re-run.</t>
+          <t>WRAP16 address sequence wraps at sixteen transfers Reworked after regression 12: the original form required $past(HTRANS) != BUSY, but the bridge drives BUSY before every SEQ beat, so it never evaluated (pass count 0 in all 90 runs). It now compares against the last issued NONSEQ/SEQ beat and is hit in 20 of 90 runs with 0 failures.</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>Implemented, pending re-run</t>
+          <t>Implemented</t>
         </is>
       </c>
     </row>
@@ -7493,7 +7493,7 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>A data phase is extended by HREADY low. Reworked after regression 12: the original form required HTRANS to be NONSEQ/SEQ during the wait, but the bridge drives BUSY there, so it never hit (0 of 13 directives). It now keys on the active data phase. Pending re-run.</t>
+          <t>A data phase is extended by HREADY low. Reworked after regression 12: the original form required HTRANS to be NONSEQ/SEQ during the wait, but the bridge drives BUSY there, so it never hit (0 of 13 directives). It now keys on the active data phase and is Covered with 3630 hits, taking directive coverage to 100.0%.</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -7508,7 +7508,7 @@
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>Implemented, pending re-run</t>
+          <t>Implemented</t>
         </is>
       </c>
     </row>

--- a/00_doc/axi_ahblite_bridge_vplan.xlsx
+++ b/00_doc/axi_ahblite_bridge_vplan.xlsx
@@ -604,7 +604,7 @@
       </c>
       <c r="K1" s="3" t="inlineStr">
         <is>
-          <t>Evidence / Gap (regression 12, 2026-09-24)</t>
+          <t>Evidence / Gap (regression 13, 2026-09-24)</t>
         </is>
       </c>
     </row>
@@ -3278,12 +3278,12 @@
       </c>
       <c r="J48" s="6" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>The default build has C_DPHASE_TIMEOUT = 0, but no long AHB wait is applied.</t>
+          <t>Regression 13, default build (C_DPHASE_TIMEOUT = 0), 5 seeds: bridge_timeout_test run=4 failed=0, identical on every seed. An AHB wait of 512 cycles, longer than every supported threshold, is applied to a single write, a single read and to beat 1 of an INCR4 write and beat 2 of an INCR4 read. All four complete with OKAY and all 10 predicted AHB beats are issued (timeouts_seen=0, long_waits_completed=4, cancelled_beats=0), so the watchdog really is generated away. Scoreboard AHB 10/0, AXI 4/0 with no request declared as abandoned.</t>
         </is>
       </c>
     </row>
@@ -3335,12 +3335,12 @@
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>No timeout build in the Makefile; the predictor does not model timeout.</t>
+          <t>Regression 13: one vopt image per value (make optimize_timeout) and bridge_timeout_test on each, 5 seeds per build. All of 16, 32, 64, 128 and 256 elaborate and behave identically: run=10 failed=0, timeouts_seen=4, long_waits_completed=4, cancelled_beats=3, 25 AHB beats. A wait of N-4 completes with OKAY on a single transfer and on a mid-burst INCR4 beat, read and write; a wait of N+32 returns SLVERR on the same four shapes; the two INCR4 read/write cases that follow then complete normally, so the watchdog does not leave the bridge stuck. An abandoned read still returns ARLEN+1 beats with no OKAY beat after a SLVERR beat. Scoreboard AHB 21/0, AXI 6/0 plus 4 declared timeouts and 7 cancelled beats (4 reported late by the slave, 3 never issued), which balances against the 25 beats observed. The exact threshold is BRG_TMO_003 and the AHB IDLE and reset recovery are BRG_TMO_004.</t>
         </is>
       </c>
     </row>
@@ -8194,12 +8194,12 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Runs timeout disabled and all supported non-zero configurations</t>
+          <t>One test for the whole C_DPHASE_TIMEOUT matrix: it reads the value the DUT was elaborated with and adapts. On the default build a 512-cycle AHB wait must still complete with OKAY; on a timeout build a wait of N-4 completes and a wait of N+32 returns SLVERR, on a single transfer and on a mid-burst INCR4 beat, read and write, followed by ordinary INCR4 traffic that must still work. The sequence declares each request the watchdog will abandon to the scoreboard (scoreboard::expect_timeout), so the beats the bridge never issues are not reported as lost while everything else in the run is still compared.</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>C_DPHASE_TIMEOUT=0/16/32/64/128/256</t>
+          <t>C_DPHASE_TIMEOUT=0 on the default build plus one image per 16/32/64/128/256 (TIMEOUT_VALUES); return_responses=1; max_outstanding=1; auto_gen_resp=0; full width; run=4 on the default build and run=10 on each timeout build</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -8209,7 +8209,7 @@
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Implemented</t>
         </is>
       </c>
     </row>

--- a/00_doc/axi_ahblite_bridge_vplan.xlsx
+++ b/00_doc/axi_ahblite_bridge_vplan.xlsx
@@ -604,7 +604,7 @@
       </c>
       <c r="K1" s="3" t="inlineStr">
         <is>
-          <t>Evidence / Gap (regression 13, 2026-09-24)</t>
+          <t>Evidence / Gap (regression 15, 2026-09-24)</t>
         </is>
       </c>
     </row>
@@ -3392,12 +3392,12 @@
       </c>
       <c r="J50" s="6" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>Depends on BRG_TMO_002.</t>
+          <t>Regression 15, one image per supported value, 5 seeds each: bridge_timeout_boundary_test run=24 failed=0, identical on every seed. The AHB wait of a single transfer is swept from C_DPHASE_TIMEOUT-3 to C_DPHASE_TIMEOUT+8, read and write, and the smallest wait the watchdog terminates is measured, so the case one clock before the threshold, the case on it and the case one clock after are all exercised. The response is monotonic in the wait on every build and the window brackets the boundary in both directions. Measured thresholds are C_DPHASE_TIMEOUT+2 for read and C_DPHASE_TIMEOUT+1 for write on all of 16, 32, 64, 128 and 256 (18/17, 34/33, 66/65, 130/129, 258/257), so the offset is a property of the watchdog pipeline and not of the programmed value. Read costs one cycle more than write because the beat travels back through the read path before the watchdog sees it complete. Both offsets are required by the test, not just reported. Scoreboard AHB 15/0, AXI 9/0 with 15 declared timeouts and 9 cancelled beats, balancing the 24 beats observed.</t>
         </is>
       </c>
     </row>
@@ -3449,12 +3449,12 @@
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>Depends on BRG_TMO_002.</t>
+          <t>Regression 15, one image per supported value, 5 seeds each: bridge_timeout_recovery_test run=13 failed=0, identical on every build and seed. Termination is observed on the AHB interface, not inferred from the response: an abandoned single transfer issues exactly one address phase and an INCR4 abandoned on its second beat exactly two, so the remaining beats are never issued (extra_beats=0), and HTRANS stays IDLE from the moment the watchdog fires until the slave releases the bus (idle_violations=0). Both directions return SLVERR. Three resets per run through the bridge_reset_req event, after a write timeout, after a read timeout, and while the slave is still holding HREADY low, are each followed by INCR4 write and read traffic that completes with OKAY and is compared in full by the scoreboard (AHB 26/0, AXI 6/0, 7 declared timeouts, 6 cancelled beats). Regression 15 also fixed a testbench gap this test exposed: ahb_slv_driver.drive_idle waited a clock before restoring HREADY, so a reset landing during a held-off data phase left HREADY low into the second reset cycle and RESET_DEFAULTS fired; the reset values are now driven before the wait.</t>
         </is>
       </c>
     </row>
@@ -8226,12 +8226,12 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Completes AHB one cycle before, on and after each timeout threshold</t>
+          <t>Sweeps the AHB wait of a single transfer from C_DPHASE_TIMEOUT-3 to C_DPHASE_TIMEOUT+8, read and write, and measures the smallest wait the watchdog terminates, so the three cases the plan names are the measured threshold and its two neighbours. Checks that the response is monotonic in the wait, that the window brackets the boundary, that read and write stay within a pipeline stage of each other, and that each threshold is C_DPHASE_TIMEOUT plus its required offset (read +2, write +1). The sequence declares each request with scoreboard::allow_timeout, since a sweep cannot say in advance which side of the threshold a wait falls on.</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Every non-zero timeout value</t>
+          <t>Every non-zero timeout value (TIMEOUT_VALUES); not run on the default build, where the sequence stops with a message naming the TIMEOUT to use; return_responses=1; max_outstanding=1; auto_gen_resp=0 with an all-OKAY plan so SLVERR can only be the watchdog; run=24 per build; EXPECT_OFFSET_RD/WR override the requirement and +MEASURE_ONLY reports instead of requiring</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -8241,7 +8241,7 @@
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Implemented</t>
         </is>
       </c>
     </row>
@@ -8258,12 +8258,12 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Checks AHB IDLE, AXI SLVERR and post-reset recovery after timeout</t>
+          <t>Checks the three parts of BRG_TMO_004. Termination: an observer on the AHB interface counts the address phases the bridge issues and watches HTRANS once the watchdog has fired, for an abandoned single transfer and an INCR4 abandoned on its second beat, read and write. Response: both directions return SLVERR. Recovery: three resets through the bridge_reset_req event, after a write timeout, after a read timeout and while the slave still holds HREADY low, each followed by INCR4 write and read traffic that the scoreboard compares in full.</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Read/write timeout paths</t>
+          <t>Every non-zero timeout value (TIMEOUT_VALUES); not run on the default build; return_responses=1; max_outstanding=1; auto_gen_resp=0; clear_queues_on_reset=1; AHB wait C_DPHASE_TIMEOUT+32; run=13 per build (7 timeouts, 3 resets, 6 recovery transfers)</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -8273,7 +8273,7 @@
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Implemented</t>
         </is>
       </c>
     </row>

--- a/00_doc/axi_ahblite_bridge_vplan.xlsx
+++ b/00_doc/axi_ahblite_bridge_vplan.xlsx
@@ -604,7 +604,7 @@
       </c>
       <c r="K1" s="3" t="inlineStr">
         <is>
-          <t>Evidence / Gap (regression 17, 2026-09-25)</t>
+          <t>Evidence / Gap (regression 18, 2026-09-25)</t>
         </is>
       </c>
     </row>
@@ -884,12 +884,12 @@
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>Reset hooks exist (vip_env reset_state, driver/monitor flush, bridge_reset_req event) but no test triggers a mid-test reset.</t>
+          <t>Regression 18, 5 seeds: bridge_reset_mid_transfer_test cases=10 failed=0 resets=10, identical on every seed. Each case sends a request without waiting for its response, waits on the interfaces until the named phase is actually reached rather than after a fixed delay, and then resets: AXI address phase on a write and a read and on a single write, AXI write data phase before WLAST, AXI read data phase before RLAST, AXI response phase with BVALID up and BREADY still held off, and the AHB wait and error phases on both directions. ghost_responses=0: after every reset an observer watches B and R for 32 cycles while nothing is outstanding, and no response came back for a request the reset had discarded. No run hung, and the scoreboard end-of-test check, which requires every queue to be empty, passed in all 5 runs, so the vip_env reset_state hooks and the driver and monitor flushes clear the partial activity. 0 SVA failures in the whole regression, including RESET_DEFAULTS and RESET_AHB_CONTROL across the AHB error phase resets.</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>Depends on BRG_RST_005.</t>
+          <t>Regression 18, 5 seeds: bridge_reset_mid_transfer_test cases=10 failed=0 resets=10, identical on every seed. Each case sends a request without waiting for its response, waits on the interfaces until the named phase is actually reached rather than after a fixed delay, and then resets: AXI address phase on a write and a read and on a single write, AXI write data phase before WLAST, AXI read data phase before RLAST, AXI response phase with BVALID up and BREADY still held off, and the AHB wait and error phases on both directions. After each of the 10 resets an INCR4 write and an INCR4 read run and are compared end to end by the scoreboard: AHB 84/0 and AXI 20/0 per run, the 20 being the two recovery requests of each case. Every recovery burst issued all four of its predicted AHB beats and returned OKAY with the expected read data, so the bridge is fully usable after a reset taken at any of the phases above.</t>
         </is>
       </c>
     </row>
@@ -8386,12 +8386,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Resets during AXI address/data/response and AHB wait/error phases then resumes</t>
+          <t>Interrupts a transfer with a reset at each phase the plan names, detected on the interfaces rather than after a fixed delay: AXI address, AXI write data before WLAST, AXI read data before RLAST, AXI response with BREADY held off, and the AHB wait and error phases. The interrupted request is never waited on, since the driver discards it. After each reset an observer watches B and R for 32 cycles with nothing outstanding, so a response for a discarded request is caught, and then an INCR4 write and read run and are compared in full.</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Queue reset hooks enabled; watchdog active</t>
+          <t>Default build only: the 20-cycle AHB wait that opens the wait phase is longer than the smallest supported watchdog. return_responses=1; max_outstanding=1; auto_gen_resp=0; clear_queues_on_reset=1; bready_delay=4 and rready_delay=2 to hold the response phases open; run=10 resets plus 20 recovery transfers</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -8401,7 +8401,7 @@
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Implemented</t>
         </is>
       </c>
     </row>

--- a/00_doc/axi_ahblite_bridge_vplan.xlsx
+++ b/00_doc/axi_ahblite_bridge_vplan.xlsx
@@ -604,7 +604,7 @@
       </c>
       <c r="K1" s="3" t="inlineStr">
         <is>
-          <t>Evidence / Gap (regression 18, 2026-09-25)</t>
+          <t>Evidence / Gap (regression 20, 2026-09-28)</t>
         </is>
       </c>
     </row>
@@ -1967,12 +1967,12 @@
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>Stimulus complete: 20 matrix entries x read/write with non-overlapping addresses (case_stride 0x400). Merged coverage not yet reviewed.</t>
+          <t>Stimulus complete: 20 matrix entries crossed with read and write on non-overlapping addresses. Merged coverage reviewed in regression 20 and closed: cx_dir_mapping and cx_burst_beats are at 100%, as is every other covergroup (441/441 bins). bridge_burst_matrix_test also runs on the 64-bit build with the same 1614/62 scoreboard figures. Regression 19 fixed a 32-bit assumption the 64-bit build exposed in axi4_mst_burst_matrix_seq: it nudged a long INCR to the next 1 KB boundary, which at 8 bytes a beat pushed a 256-beat burst across a 4 KB boundary and made the request unrandomizable. The start is now aligned down to a power of two at least as large as the burst, which respects the AXI 4 KB rule at any width; on 32 bits it changes no address.</t>
         </is>
       </c>
     </row>
@@ -2195,12 +2195,12 @@
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>Both directions at full width with three crossing positions (regression 5); narrow sizes and the 64-bit multi-boundary 256-beat case are not exercised.</t>
+          <t>Both directions at full width with three crossing positions (regression 5). Regression 20 adds the 64-bit half: bridge_1kb_boundary_test is now in PARAM_TEST_LIST and runs on both 64-bit builds, run=46 failed=0 on each, the same 46 cases but with 8 bytes a beat, so the 256-beat burst spans 2 KB and crosses the boundary in the middle of the burst rather than at its edge. The narrow build covers the boundary classes at the narrow sizes. Every case keeps to its own 4 KB page, so no burst crosses the AXI 4 KB boundary at either width.</t>
         </is>
       </c>
     </row>
@@ -2366,12 +2366,12 @@
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>Regression 8, narrow build, 32-bit, 5 seeds: bridge_size_mapping_test run=64 failed=0 (AHB 318/0, AXI 64/0). 8/16-bit singles on every legal lane; 8/16-bit INCR4 and INCR8 (crossing a bus-word boundary), INCR16, undefined INCR, FIXED3, WRAP2, WRAP4, WRAP8 and WRAP16 (wrapping inside the burst) with HSIZE = AxSIZE; filler bytes in non-strobed lanes never reach memory; cx_mapping_size at 100%. 64-bit (32-bit narrow size) not exercised.</t>
+          <t>Regression 8, narrow build, 32-bit, 5 seeds: bridge_size_mapping_test run=64 failed=0 (AHB 318/0, AXI 64/0). 8/16-bit singles on every legal lane; 8/16-bit INCR4 and INCR8 (crossing a bus-word boundary), INCR16, undefined INCR, FIXED3, WRAP2, WRAP4, WRAP8 and WRAP16 (wrapping inside the burst) with HSIZE = AxSIZE; filler bytes in non-strobed lanes never reach memory; cx_mapping_size at 100%. 64-bit (32-bit narrow size) not exercised. Regression 20 closes the 64-bit gap: on the 64-bit narrow build bridge_parameter_test writes 1, 2 and 4 byte transfers on every legal lane, 14 cases in all, and reads each word back at full width so the lanes outside the transfer are checked as untouched. The 4-byte case is the 32-bit narrow size on a 64-bit bus that was missing.</t>
         </is>
       </c>
     </row>
@@ -2423,12 +2423,12 @@
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>Regression 5, 32-bit: bridge_single_wstrb_test narrow build run=66 failed=0 (9 legal cases: every legal pattern on its lane with matching AWSIZE, lane-0 patterns with full-width AWSIZE, 0xF), default build run=30 failed=0. HSIZE, HADDR and the whole written word match for every legal pattern. 64-bit patterns are not exercised.</t>
+          <t>Regression 20 closes the 64-bit gap: bridge_single_wstrb_test is now in PARAM_TEST_LIST and the sweep is exhaustive at the wider bus, because it iterates every one of the 2^AXI4_STRB_WIDTH strobe values. On 64 bits that is 256 patterns against 16 on 32 bits: narrow off run=726 failed=0 with 241 fallback cases, narrow on run=819 failed=0 with 18 legal, 11 misdirected and 244 fallback. The 15 contiguous aligned patterns of a 64-bit bus, 8 single-byte lanes, 4 two-byte, 2 four-byte and 1 eight-byte, all derive the expected HSIZE and lane, and the whole written word is compared every time. 32-bit stays at run=30 and run=72.</t>
         </is>
       </c>
     </row>
@@ -3506,12 +3506,12 @@
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>32-bit data/address builds pass with narrow off and on (regression 11: 85/85 runs, 0 UVM warnings), including AHB ERROR and wait states. Timeout and 64-bit are not exercised.</t>
+          <t>The bus widths are package parameters, so vopt -G cannot reach them and each width is its own compilation: BRIDGE_DATA_WIDTH selects it and the Makefile builds the 64-bit variant into its own library (compile_wide, optimize_wide). bridge_parameter_test runs the same source on all four builds and the profile grows with the bus: 32-bit narrow off run=12, 32-bit narrow on run=18 with 6 narrow writes, 64-bit narrow off run=12, 64-bit narrow on run=26 with 14 narrow writes, all failed=0 on 5 seeds each. Regression 20: 275 runs, 0 failures, 0 UVM warnings. The 32-bit configuration carries the whole regression, narrow off and on, including AHB ERROR, wait states, all five C_DPHASE_TIMEOUT builds and mid-test reset. vip_env_cfg.is_valid is checked by bridge_parameter_seq before the profile starts.</t>
         </is>
       </c>
     </row>
@@ -3563,12 +3563,12 @@
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>No 64-bit build.</t>
+          <t>The bus widths are package parameters, so vopt -G cannot reach them and each width is its own compilation: BRIDGE_DATA_WIDTH selects it and the Makefile builds the 64-bit variant into its own library (compile_wide, optimize_wide). bridge_parameter_test runs the same source on all four builds and the profile grows with the bus: 32-bit narrow off run=12, 32-bit narrow on run=18 with 6 narrow writes, 64-bit narrow off run=12, 64-bit narrow on run=26 with 14 narrow writes, all failed=0 on 5 seeds each. Both 64-bit images elaborate and run: this is the first time the gen_64_data_width and gen_64_narrow_decode branches of ahb_mstr_if and axi_slv_if have been simulated. The compliance subset (sanity, data integrity, burst matrix, size mapping, response mapping) reports identical scoreboard figures on 32 and 64 bits, for example burst matrix 1614/62 and response mapping 384/61, so the same translation work is done correctly with 8 bytes a beat. Address width stays at 32 on both; the 32 to 64 bit address sweep is not built yet.</t>
         </is>
       </c>
     </row>
@@ -4081,7 +4081,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>Merged, regression 17 (180 tests, 0 failures, 0 UVM warnings): functional coverage is closed. Covergroups 100% of bins hit (441/441), every covergroup at 100% including e2e cg_response_map at 18/18, whose last bin cx_error_map &lt;OKAY,SLVERR&gt; needed a timeout build and is hit by the watchdog tests. Assertions 51/51 hit with 0 failures and cover directives 13/13 (100.0%), both read individually from the text reports that 'make assert_report' produces. RESET_AHB_CONTROL, added for BRG_RST_004, passes in all 180 runs. All unreachable bins are illegal_bins, ignore_bins or default, and the two immediate assertions WLEN_MATCH and W_BEFORE_AW_LENGTH are waived as unreachable on this DUT. Still open for this item: code coverage has not been reviewed, and the constrained-random regression of BRG_ENV_008 does not exist yet.</t>
+          <t>Merged, regression 20 (275 tests, 0 failures, 0 UVM warnings): functional coverage is closed. Covergroups 100% of bins (441/441), assertions 51/51 hit with 0 failures, cover directives 13/13 (100.0%), the last two read individually from the reports 'make assert_report' produces. The merge now spans four bus configurations as well as the narrow and timeout builds. All unreachable bins are illegal_bins, ignore_bins or default, and WLEN_MATCH and W_BEFORE_AW_LENGTH are waived as unreachable on this DUT. Still open: code coverage has not been reviewed, and the constrained-random regression of BRG_ENV_008 does not exist yet.</t>
         </is>
       </c>
     </row>
@@ -8418,12 +8418,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Runs the compliance subset across supported widths and narrow modes</t>
+          <t>Runs one compliance profile on every supported build and lets it grow with the bus, reading AXI4_DATA_WIDTH and AXI4_STRB_WIDTH instead of assuming them: full-width SINGLE, INCR4, INCR16, undefined INCR5, WRAP4 and FIXED3 read and write with the read data checked beat by beat, plus one single write per legal narrow size on every lane it can occupy, each read back at full width so the untouched lanes are checked too. The AHB slave answers from its memory model, which is what makes the read-back meaningful.</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>32/64-bit data; supported address widths; narrow off/on</t>
+          <t>Four builds: 32 and 64 bit data, narrow off and on. The widths are package parameters, so the 64-bit variant is a separate compilation into its own library, selected by BRIDGE_DATA_WIDTH and built by 'make optimize_wide'. Address width 32 on all four. run=12 (32-bit narrow off), 18 (32-bit narrow on), 12 (64-bit narrow off), 26 (64-bit narrow on)</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -8433,7 +8433,7 @@
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Implemented</t>
         </is>
       </c>
     </row>

--- a/00_doc/axi_ahblite_bridge_vplan.xlsx
+++ b/00_doc/axi_ahblite_bridge_vplan.xlsx
@@ -604,7 +604,7 @@
       </c>
       <c r="K1" s="3" t="inlineStr">
         <is>
-          <t>Evidence / Gap (regression 20, 2026-09-28)</t>
+          <t>Evidence / Gap (regression 21, 2026-09-28)</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>AXI IDs are randomized in every request and compared by the scoreboard. Only one outstanding transaction, so concurrent ID reuse is covered by BRG_UNS_002.</t>
+          <t>AXI IDs are randomized in every request and compared by the scoreboard. Concurrent ID reuse is now closed by BRG_UNS_002: regression 21 runs eight reads that share one ID with the queue full, and two of the four conflict phases put every access of the phase on a single address with one ID across both directions. Every BID and RID came back on the request that asked for it.</t>
         </is>
       </c>
     </row>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>Stimulus complete: 20 matrix entries crossed with read and write on non-overlapping addresses. Merged coverage reviewed in regression 20 and closed: cx_dir_mapping and cx_burst_beats are at 100%, as is every other covergroup (441/441 bins). bridge_burst_matrix_test also runs on the 64-bit build with the same 1614/62 scoreboard figures. Regression 19 fixed a 32-bit assumption the 64-bit build exposed in axi4_mst_burst_matrix_seq: it nudged a long INCR to the next 1 KB boundary, which at 8 bytes a beat pushed a 256-beat burst across a 4 KB boundary and made the request unrandomizable. The start is now aligned down to a power of two at least as large as the burst, which respects the AXI 4 KB rule at any width; on 32 bits it changes no address.</t>
+          <t>Stimulus complete: 20 matrix entries crossed with read and write on non-overlapping addresses. Merged coverage reviewed in regression 21 and closed: cx_dir_mapping and cx_burst_beats are at 100%, as is every other covergroup (462/462 bins; earlier entries said 441/441, which was a miscount of the same report). bridge_burst_matrix_test also runs on the 64-bit build with the same 1614/62 scoreboard figures. Regression 19 fixed a 32-bit assumption the 64-bit build exposed in axi4_mst_burst_matrix_seq: it nudged a long INCR to the next 1 KB boundary, which at 8 bytes a beat pushed a 256-beat burst across a 4 KB boundary and made the request unrandomizable. The start is now aligned down to a power of two at least as large as the burst, which respects the AXI 4 KB rule at any width; on 32 bits it changes no address.</t>
         </is>
       </c>
     </row>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>The bus widths are package parameters, so vopt -G cannot reach them and each width is its own compilation: BRIDGE_DATA_WIDTH selects it and the Makefile builds the 64-bit variant into its own library (compile_wide, optimize_wide). bridge_parameter_test runs the same source on all four builds and the profile grows with the bus: 32-bit narrow off run=12, 32-bit narrow on run=18 with 6 narrow writes, 64-bit narrow off run=12, 64-bit narrow on run=26 with 14 narrow writes, all failed=0 on 5 seeds each. Regression 20: 275 runs, 0 failures, 0 UVM warnings. The 32-bit configuration carries the whole regression, narrow off and on, including AHB ERROR, wait states, all five C_DPHASE_TIMEOUT builds and mid-test reset. vip_env_cfg.is_valid is checked by bridge_parameter_seq before the profile starts.</t>
+          <t>The bus widths are package parameters, so vopt -G cannot reach them and each width is its own compilation: BRIDGE_DATA_WIDTH selects it and the Makefile builds the 64-bit variant into its own library (compile_wide, optimize_wide). bridge_parameter_test runs the same source on all four builds and the profile grows with the bus: 32-bit narrow off run=12, 32-bit narrow on run=18 with 6 narrow writes, 64-bit narrow off run=12, 64-bit narrow on run=26 with 14 narrow writes, all failed=0 on 5 seeds each. Regression 21: 280 runs, 0 failures. 25 of the 280 runs carry one UVM_WARNING each, all of them bridge_timeout_test on the five C_DPHASE_TIMEOUT builds: the e2e coverage collector reports unmatched input streams at the end of the test. It is a residue check in the coverage collector, not a bridge check; the scoreboard, which does have explicit declared-timeout handling, reports clean on the same runs. The same 25 warnings are in regression 20, so this is a standing gap in e2e_cov rather than a new one. Not yet diagnosed: bridge_timeout_recovery_test abandons requests through the same expect_timeout path and does not warn, so the cause is narrower than 'any abandoned request'.  The 32-bit configuration carries the whole regression, narrow off and on, including AHB ERROR, wait states, all five C_DPHASE_TIMEOUT builds and mid-test reset. vip_env_cfg.is_valid is checked by bridge_parameter_seq before the profile starts.</t>
         </is>
       </c>
     </row>
@@ -3734,12 +3734,12 @@
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>All tests run with one outstanding transaction; ordering under concurrent traffic is not exercised. The scoreboard is ready for it.</t>
+          <t>Closed by bridge_ordering_test, regression 21 (280 runs, 0 failures). The gap was that every other test sends one request and waits for it, so the bridge was never given the chance to reorder anything. This test hands the driver a whole phase in one time step with max_outstanding=0 and lets the queue back up behind the bridge: 88 requests over 8 phases, a queue 24 deep, and 1151 to 1394 cycles a run in which a request was asking and the bridge refused it. That count is checked, so a phase where the queue never backed up fails instead of passing on a technicality. The reference order is the order the bridge accepted the requests on AW and AR, which is what the requirement says, not the order they were issued in: the two differ by design, because a read arriving with a write wins arbitration and the write then takes the next turn. Against that order, on all 5 seeds, B and R completions come back in order per direction, each read returns the beat count its AR asked for, and RID never changes inside a burst (interleaved=0 over 49 to 55 read bursts a run). The acceptance order is also replayed through a reference copy of the AHB slave memory and every read beat is compared against what an in-order bridge would owe it at that point, which is the value a read overtaking a write would change. 12 to 22 reads a run returned data an earlier write had left rather than the address pattern, and the run fails if that count is zero. The AHB side shows one contiguous burst per accepted request, in the same order and with the same beat count, in all 8 phases, so the two directions are not interleaved there either. Measured rather than assumed: max_accepted, the most requests the bridge had accepted and not completed at one time, is 1 in the seven deterministic phases and 2 only in the mixed stress phase. That matches the RTL. In axi_slv_if the read FSM leaves AXI_RD_IDLE only on !write_pending &amp;&amp; !write_in_progress and the write FSM leaves AXI_WR_IDLE only on !read_in_progress, so the two machines exclude each other; read_in_progress clears on RLAST_sm rather than on the R handshake, which is what lets a write be accepted while the last read beat still waits for RREADY, and that is the only overlap seen. Reordering on this bridge is therefore structural, not incidental. Stimulus: eight reads sharing one ID, eight reads with rotating IDs and falling burst lengths so a bridge returning completions as they became ready would show it, a write and read stream over the same eight addresses, four phases that put every access of the phase on a single address (two with one ID across both directions, two with a different ID per request), and 24 randomized mixed requests with AHB wait states and AXI response backpressure. FIXED and WRAP2 are left out because the bridge expands each into several AHB bursts by design, which the one-burst-per-request check could not tell from interleaving; their mapping is bridge_fixed_mapping_test and bridge_wrap_mapping_test.</t>
         </is>
       </c>
     </row>
@@ -4081,7 +4081,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>Merged, regression 20 (275 tests, 0 failures, 0 UVM warnings): functional coverage is closed. Covergroups 100% of bins (441/441), assertions 51/51 hit with 0 failures, cover directives 13/13 (100.0%), the last two read individually from the reports 'make assert_report' produces. The merge now spans four bus configurations as well as the narrow and timeout builds. All unreachable bins are illegal_bins, ignore_bins or default, and WLEN_MATCH and W_BEFORE_AW_LENGTH are waived as unreachable on this DUT. Still open: code coverage has not been reviewed, and the constrained-random regression of BRG_ENV_008 does not exist yet.</t>
+          <t>Merged, regression 21 (280 runs, 0 failures): functional coverage is closed. Covergroups 100% of bins (462/462), assertions 51/51 hit with 0 failures, cover directives 13/13 (100.0%), the last two read from the reports 'make assert_report' produces. Two figures in the regression 20 entry were wrong and are corrected here: the bin total is 462, not 441, and the run was not warning-free. 25 of the 280 runs carry one UVM_WARNING each, all of them bridge_timeout_test on the five C_DPHASE_TIMEOUT builds: the e2e coverage collector reports unmatched input streams at the end of the test. It is a residue check in the coverage collector, not a bridge check; the scoreboard, which does have explicit declared-timeout handling, reports clean on the same runs. The same 25 warnings are in regression 20, so this is a standing gap in e2e_cov rather than a new one. Not yet diagnosed: bridge_timeout_recovery_test abandons requests through the same expect_timeout path and does not warn, so the cause is narrower than 'any abandoned request'. The merge spans four bus configurations as well as the narrow and timeout builds. All unreachable bins are illegal_bins, ignore_bins or default, and WLEN_MATCH and W_BEFORE_AW_LENGTH are waived as unreachable on this DUT. Still open: code coverage has not been reviewed, the constrained-random regression of BRG_ENV_008 does not exist yet, and the e2e_cov residue warning above is undiagnosed.</t>
         </is>
       </c>
     </row>
@@ -8327,7 +8327,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>max_outstanding=2, the only test in the regression with two requests outstanding; return_responses=1; auto_gen_resp=0; full width; the write of a pair sits in the lower half of its region and the read in the upper half so the scoreboard can tell them apart by address; run=17, 67 AHB beats</t>
+          <t>max_outstanding=2, enough for a read and a write to ask together (bridge_ordering_test goes further and lifts the limit entirely); return_responses=1; auto_gen_resp=0; full width; the write of a pair sits in the lower half of its region and the read in the upper half so the scoreboard can tell them apart by address; run=17, 67 AHB beats</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -8514,22 +8514,22 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Stresses supported in-order completion without loss, duplication or interleaving</t>
+          <t>Hands the driver a whole list of requests in one time step instead of sending one and waiting, so the queue backs up behind the bridge and the bridge is the only thing deciding what runs next. Eight phases: eight reads on one ID, eight reads on rotating IDs with falling burst lengths, a write and read stream over the same eight addresses, four phases that put every access of the phase on a single address (two with one ID across both directions, two with a different ID per request), and 24 randomized mixed requests with AHB wait states and AXI response backpressure. The reference order is the order the bridge accepted the requests on AW and AR, not the order they were issued, because a read arriving with a write wins arbitration. Four checks run against it: completions in acceptance order per direction with the beat count the AR asked for; a replay of the acceptance order through a reference copy of the AHB slave memory, comparing every read beat against what an in-order bridge would owe it; one contiguous AHB burst per accepted request, same order and same length; and RID stable inside a read burst. The cycles a request spent asking while the bridge refused it are counted, and a phase where the queue never backed up fails.</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Mixed IDs and read/write traffic</t>
+          <t>max_outstanding=0 so the driver never throttles the queue; return_responses=1 with an unlimited response queue; auto_gen_resp=1 so a read returns what an earlier write left and the order of the two is visible in the data; addr_pattern_read=1; AHB ready_delay moved per phase (0, 1, then 3) and AXI rready/bready delay only in the stress phase; full width, INCR, SINGLE and WRAP4/8/16, every burst inside its own 256-byte slot so none crosses the 1 KB boundary the bridge splits on. Per run: 88 requests over 8 phases, queue_depth=24, max_accepted=2 (1 in the seven deterministic phases), stall_cycles 1151-1394, interleaved=0, ordered_reads 12-22, scoreboard AXI 88/0</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>BRG_UNS_002</t>
+          <t>BRG_UNS_002, BRG_BAS_004</t>
         </is>
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Implemented</t>
         </is>
       </c>
     </row>

--- a/00_doc/axi_ahblite_bridge_vplan.xlsx
+++ b/00_doc/axi_ahblite_bridge_vplan.xlsx
@@ -604,7 +604,7 @@
       </c>
       <c r="K1" s="3" t="inlineStr">
         <is>
-          <t>Evidence / Gap (regression 21, 2026-09-28)</t>
+          <t>Evidence / Gap (regression 22, 2026-09-28)</t>
         </is>
       </c>
     </row>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>The bus widths are package parameters, so vopt -G cannot reach them and each width is its own compilation: BRIDGE_DATA_WIDTH selects it and the Makefile builds the 64-bit variant into its own library (compile_wide, optimize_wide). bridge_parameter_test runs the same source on all four builds and the profile grows with the bus: 32-bit narrow off run=12, 32-bit narrow on run=18 with 6 narrow writes, 64-bit narrow off run=12, 64-bit narrow on run=26 with 14 narrow writes, all failed=0 on 5 seeds each. Regression 21: 280 runs, 0 failures. 25 of the 280 runs carry one UVM_WARNING each, all of them bridge_timeout_test on the five C_DPHASE_TIMEOUT builds: the e2e coverage collector reports unmatched input streams at the end of the test. It is a residue check in the coverage collector, not a bridge check; the scoreboard, which does have explicit declared-timeout handling, reports clean on the same runs. The same 25 warnings are in regression 20, so this is a standing gap in e2e_cov rather than a new one. Not yet diagnosed: bridge_timeout_recovery_test abandons requests through the same expect_timeout path and does not warn, so the cause is narrower than 'any abandoned request'.  The 32-bit configuration carries the whole regression, narrow off and on, including AHB ERROR, wait states, all five C_DPHASE_TIMEOUT builds and mid-test reset. vip_env_cfg.is_valid is checked by bridge_parameter_seq before the profile starts.</t>
+          <t>The bus widths are package parameters, so vopt -G cannot reach them and each width is its own compilation: BRIDGE_DATA_WIDTH selects it and the Makefile builds the 64-bit variant into its own library (compile_wide, optimize_wide). bridge_parameter_test runs the same source on all four builds and the profile grows with the bus: 32-bit narrow off run=12, 32-bit narrow on run=18 with 6 narrow writes, 64-bit narrow off run=12, 64-bit narrow on run=26 with 14 narrow writes, all failed=0 on 5 seeds each. Regression 22: 280 runs, 0 failures, 0 UVM warnings. The 32-bit configuration carries the whole regression, narrow off and on, including AHB ERROR, wait states, all five C_DPHASE_TIMEOUT builds and mid-test reset. vip_env_cfg.is_valid is checked by bridge_parameter_seq before the profile starts.</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>Closed by bridge_ordering_test, regression 21 (280 runs, 0 failures). The gap was that every other test sends one request and waits for it, so the bridge was never given the chance to reorder anything. This test hands the driver a whole phase in one time step with max_outstanding=0 and lets the queue back up behind the bridge: 88 requests over 8 phases, a queue 24 deep, and 1151 to 1394 cycles a run in which a request was asking and the bridge refused it. That count is checked, so a phase where the queue never backed up fails instead of passing on a technicality. The reference order is the order the bridge accepted the requests on AW and AR, which is what the requirement says, not the order they were issued in: the two differ by design, because a read arriving with a write wins arbitration and the write then takes the next turn. Against that order, on all 5 seeds, B and R completions come back in order per direction, each read returns the beat count its AR asked for, and RID never changes inside a burst (interleaved=0 over 49 to 55 read bursts a run). The acceptance order is also replayed through a reference copy of the AHB slave memory and every read beat is compared against what an in-order bridge would owe it at that point, which is the value a read overtaking a write would change. 12 to 22 reads a run returned data an earlier write had left rather than the address pattern, and the run fails if that count is zero. The AHB side shows one contiguous burst per accepted request, in the same order and with the same beat count, in all 8 phases, so the two directions are not interleaved there either. Measured rather than assumed: max_accepted, the most requests the bridge had accepted and not completed at one time, is 1 in the seven deterministic phases and 2 only in the mixed stress phase. That matches the RTL. In axi_slv_if the read FSM leaves AXI_RD_IDLE only on !write_pending &amp;&amp; !write_in_progress and the write FSM leaves AXI_WR_IDLE only on !read_in_progress, so the two machines exclude each other; read_in_progress clears on RLAST_sm rather than on the R handshake, which is what lets a write be accepted while the last read beat still waits for RREADY, and that is the only overlap seen. Reordering on this bridge is therefore structural, not incidental. Stimulus: eight reads sharing one ID, eight reads with rotating IDs and falling burst lengths so a bridge returning completions as they became ready would show it, a write and read stream over the same eight addresses, four phases that put every access of the phase on a single address (two with one ID across both directions, two with a different ID per request), and 24 randomized mixed requests with AHB wait states and AXI response backpressure. FIXED and WRAP2 are left out because the bridge expands each into several AHB bursts by design, which the one-burst-per-request check could not tell from interleaving; their mapping is bridge_fixed_mapping_test and bridge_wrap_mapping_test.</t>
+          <t>Closed by bridge_ordering_test, regression 21 (280 runs, 0 failures). The gap was that every other test sends one request and waits for it, so the bridge was never given the chance to reorder anything. This test hands the driver a whole phase in one time step with max_outstanding=0 and lets the queue back up behind the bridge: 88 requests over 8 phases, a queue 24 deep, and 1151 to 1394 cycles a run (1257 to 1371 on the reseeded regression 22) in which a request was asking and the bridge refused it. That count is checked, so a phase where the queue never backed up fails instead of passing on a technicality. The reference order is the order the bridge accepted the requests on AW and AR, which is what the requirement says, not the order they were issued in: the two differ by design, because a read arriving with a write wins arbitration and the write then takes the next turn. Against that order, on all 5 seeds, B and R completions come back in order per direction, each read returns the beat count its AR asked for, and RID never changes inside a burst (interleaved=0 over 49 to 57 read bursts a run, and the number of read bursts equals the number of reads on every seed). The acceptance order is also replayed through a reference copy of the AHB slave memory and every read beat is compared against what an in-order bridge would owe it at that point, which is the value a read overtaking a write would change. 12 to 23 reads a run returned data an earlier write had left rather than the address pattern, and the run fails if that count is zero. The AHB side shows one contiguous burst per accepted request, in the same order and with the same beat count, in all 8 phases, so the two directions are not interleaved there either. Measured rather than assumed: max_accepted, the most requests the bridge had accepted and not completed at one time, is 1 in the seven deterministic phases and 2 only in the mixed stress phase. That matches the RTL. In axi_slv_if the read FSM leaves AXI_RD_IDLE only on !write_pending &amp;&amp; !write_in_progress and the write FSM leaves AXI_WR_IDLE only on !read_in_progress, so the two machines exclude each other; read_in_progress clears on RLAST_sm rather than on the R handshake, which is what lets a write be accepted while the last read beat still waits for RREADY, and that is the only overlap seen. Reordering on this bridge is therefore structural, not incidental. Stimulus: eight reads sharing one ID, eight reads with rotating IDs and falling burst lengths so a bridge returning completions as they became ready would show it, a write and read stream over the same eight addresses, four phases that put every access of the phase on a single address (two with one ID across both directions, two with a different ID per request), and 24 randomized mixed requests with AHB wait states and AXI response backpressure. FIXED and WRAP2 are left out because the bridge expands each into several AHB bursts by design, which the one-burst-per-request check could not tell from interleaving; their mapping is bridge_fixed_mapping_test and bridge_wrap_mapping_test. Confirmed a second time on a fresh set of seeds in regression 22: 88 requests and 8 phases every run, queue_depth 24, max_accepted 1 in the deterministic phases and 2 in the stress phase, interleaved=0, 0 failures.</t>
         </is>
       </c>
     </row>
@@ -4081,7 +4081,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>Merged, regression 21 (280 runs, 0 failures): functional coverage is closed. Covergroups 100% of bins (462/462), assertions 51/51 hit with 0 failures, cover directives 13/13 (100.0%), the last two read from the reports 'make assert_report' produces. Two figures in the regression 20 entry were wrong and are corrected here: the bin total is 462, not 441, and the run was not warning-free. 25 of the 280 runs carry one UVM_WARNING each, all of them bridge_timeout_test on the five C_DPHASE_TIMEOUT builds: the e2e coverage collector reports unmatched input streams at the end of the test. It is a residue check in the coverage collector, not a bridge check; the scoreboard, which does have explicit declared-timeout handling, reports clean on the same runs. The same 25 warnings are in regression 20, so this is a standing gap in e2e_cov rather than a new one. Not yet diagnosed: bridge_timeout_recovery_test abandons requests through the same expect_timeout path and does not warn, so the cause is narrower than 'any abandoned request'. The merge spans four bus configurations as well as the narrow and timeout builds. All unreachable bins are illegal_bins, ignore_bins or default, and WLEN_MATCH and W_BEFORE_AW_LENGTH are waived as unreachable on this DUT. Still open: code coverage has not been reviewed, the constrained-random regression of BRG_ENV_008 does not exist yet, and the e2e_cov residue warning above is undiagnosed.</t>
+          <t>Merged, regression 22 (280 runs, 0 failures, 0 UVM warnings): functional coverage is closed. Covergroups 100% of bins (462/462), assertions 51/51 hit with 0 failures, cover directives 13/13 (100.0%), the last two read from the reports 'make assert_report' produces. The e2e_cov residue warning that regression 21 carried on 25 runs is fixed and the regression is warning-free on all 280. It was a defect in the coverage collector, not in the bridge: e2e_cov retired a response context only once it had consumed len+1 actual AHB beats, so a request the C_DPHASE_TIMEOUT watchdog abandoned never retired, sat in rsp_ctx_queue for the rest of the test and went on swallowing the beats of the requests behind it. The residue was the visible half; the damaging half was that every AHB beat after the first timeout was credited to the wrong request, so the beat position in cg_ahb_response and the saw_error/saw_wait pair in cg_response_map were wrong for those tests. It showed up only in bridge_timeout_test because bridge_timeout_boundary_test loses no beats (its requests are single beat and the slave still reports the beat the bridge walked away from) and bridge_timeout_recovery_test asserts reset three times, which calls cov.reset_state() and wiped the evidence. e2e_cov now has the same abandoned-request handling as the scoreboard, driven by the completion arriving while its request still owes beats rather than by a declaration, and the two agree independently on how many beats arrived after the bridge left: 4 and 4 in bridge_timeout_test, 9 and 9 in bridge_timeout_boundary_test, 6 and 6 in bridge_timeout_recovery_test. In bridge_timeout_test the scoreboard's 7 cancelled beats split exactly into the 4 that arrived late and the 3 never issued (28 predicted against 25 observed). cg_response_map now sees the timeout source of SLVERR that its cx_wait_status ignore_bins already reasoned about and that had never reached it. Two figures in the regression 20 entry were wrong and were corrected in regression 21: the bin total is 462, not 441, and that run was not warning-free. The merge spans four bus configurations as well as the narrow and timeout builds. All unreachable bins are illegal_bins, ignore_bins or default, and WLEN_MATCH and W_BEFORE_AW_LENGTH are waived as unreachable on this DUT. Still open: code coverage has not been reviewed, and the constrained-random regression of BRG_ENV_008 does not exist yet.</t>
         </is>
       </c>
     </row>
@@ -8519,7 +8519,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>max_outstanding=0 so the driver never throttles the queue; return_responses=1 with an unlimited response queue; auto_gen_resp=1 so a read returns what an earlier write left and the order of the two is visible in the data; addr_pattern_read=1; AHB ready_delay moved per phase (0, 1, then 3) and AXI rready/bready delay only in the stress phase; full width, INCR, SINGLE and WRAP4/8/16, every burst inside its own 256-byte slot so none crosses the 1 KB boundary the bridge splits on. Per run: 88 requests over 8 phases, queue_depth=24, max_accepted=2 (1 in the seven deterministic phases), stall_cycles 1151-1394, interleaved=0, ordered_reads 12-22, scoreboard AXI 88/0</t>
+          <t>max_outstanding=0 so the driver never throttles the queue; return_responses=1 with an unlimited response queue; auto_gen_resp=1 so a read returns what an earlier write left and the order of the two is visible in the data; addr_pattern_read=1; AHB ready_delay moved per phase (0, 1, then 3) and AXI rready/bready delay only in the stress phase; full width, INCR, SINGLE and WRAP4/8/16, every burst inside its own 256-byte slot so none crosses the 1 KB boundary the bridge splits on. Per run: 88 requests over 8 phases, queue_depth=24, max_accepted=2 (1 in the seven deterministic phases), stall_cycles 1151-1394, interleaved=0, ordered_reads 12-23, raw/war conflict pairs 12-16 and 24-28, scoreboard AXI 88/0</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">

--- a/00_doc/axi_ahblite_bridge_vplan.xlsx
+++ b/00_doc/axi_ahblite_bridge_vplan.xlsx
@@ -604,7 +604,7 @@
       </c>
       <c r="K1" s="3" t="inlineStr">
         <is>
-          <t>Evidence / Gap (regression 22, 2026-09-28)</t>
+          <t>Evidence / Gap (regression 23, 2026-09-28)</t>
         </is>
       </c>
     </row>
@@ -3791,12 +3791,12 @@
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>Assertions and illegal_bins active in every run, but only OKAY is observed; SLVERR paths (ERROR, timeout) are never exercised.</t>
+          <t>Closed in regression 23. The gap was that only OKAY was ever observed, so the assertions and illegal_bins were passing on traffic that could not have failed them. Both supported responses are now driven from three independent sources: an AHB ERROR answer (bridge_response_mapping_test, 43 SLVERR responses a run, and bridge_random_stress_test, 44 to 60 a run on randomized traffic), and the C_DPHASE_TIMEOUT watchdog (bridge_timeout_test and bridge_timeout_recovery_test on all five timeout builds). Both channels are covered, because the random test sends reads and writes in roughly equal numbers and checks the per-beat RRESP as well as BRESP against the plan it drew. BRESP_SUPPORTED and RRESP_SUPPORTED are hit in all 285 runs with 0 failures, so no EXOKAY or DECERR was ever emitted on either channel, and the cp_axi_status bins for OKAY and SLVERR are both covered with their illegal_bins never taken (462/462 covergroup bins, 51/51 assertions with 0 failures). Regression 22 also closed the last hole on the coverage side: until the e2e_cov fix no watchdog SLVERR ever reached cg_response_map at all.</t>
         </is>
       </c>
     </row>
@@ -4081,7 +4081,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>Merged, regression 22 (280 runs, 0 failures, 0 UVM warnings): functional coverage is closed. Covergroups 100% of bins (462/462), assertions 51/51 hit with 0 failures, cover directives 13/13 (100.0%), the last two read from the reports 'make assert_report' produces. The e2e_cov residue warning that regression 21 carried on 25 runs is fixed and the regression is warning-free on all 280. It was a defect in the coverage collector, not in the bridge: e2e_cov retired a response context only once it had consumed len+1 actual AHB beats, so a request the C_DPHASE_TIMEOUT watchdog abandoned never retired, sat in rsp_ctx_queue for the rest of the test and went on swallowing the beats of the requests behind it. The residue was the visible half; the damaging half was that every AHB beat after the first timeout was credited to the wrong request, so the beat position in cg_ahb_response and the saw_error/saw_wait pair in cg_response_map were wrong for those tests. It showed up only in bridge_timeout_test because bridge_timeout_boundary_test loses no beats (its requests are single beat and the slave still reports the beat the bridge walked away from) and bridge_timeout_recovery_test asserts reset three times, which calls cov.reset_state() and wiped the evidence. e2e_cov now has the same abandoned-request handling as the scoreboard, driven by the completion arriving while its request still owes beats rather than by a declaration, and the two agree independently on how many beats arrived after the bridge left: 4 and 4 in bridge_timeout_test, 9 and 9 in bridge_timeout_boundary_test, 6 and 6 in bridge_timeout_recovery_test. In bridge_timeout_test the scoreboard's 7 cancelled beats split exactly into the 4 that arrived late and the 3 never issued (28 predicted against 25 observed). cg_response_map now sees the timeout source of SLVERR that its cx_wait_status ignore_bins already reasoned about and that had never reached it. Two figures in the regression 20 entry were wrong and were corrected in regression 21: the bin total is 462, not 441, and that run was not warning-free. The merge spans four bus configurations as well as the narrow and timeout builds. All unreachable bins are illegal_bins, ignore_bins or default, and WLEN_MATCH and W_BEFORE_AW_LENGTH are waived as unreachable on this DUT. Still open: code coverage has not been reviewed, and the constrained-random regression of BRG_ENV_008 does not exist yet.</t>
+          <t>Merged, regression 23 (285 runs, 0 failures, 0 UVM warnings): functional coverage is closed. Covergroups 100% of bins (462/462), assertions 51/51 hit with 0 failures, cover directives 13/13 (100.0%), the last two read from the reports 'make assert_report' produces. The e2e_cov residue warning that regression 21 carried on 25 runs is fixed and the regression is warning-free on all 280. It was a defect in the coverage collector, not in the bridge: e2e_cov retired a response context only once it had consumed len+1 actual AHB beats, so a request the C_DPHASE_TIMEOUT watchdog abandoned never retired, sat in rsp_ctx_queue for the rest of the test and went on swallowing the beats of the requests behind it. The residue was the visible half; the damaging half was that every AHB beat after the first timeout was credited to the wrong request, so the beat position in cg_ahb_response and the saw_error/saw_wait pair in cg_response_map were wrong for those tests. It showed up only in bridge_timeout_test because bridge_timeout_boundary_test loses no beats (its requests are single beat and the slave still reports the beat the bridge walked away from) and bridge_timeout_recovery_test asserts reset three times, which calls cov.reset_state() and wiped the evidence. e2e_cov now has the same abandoned-request handling as the scoreboard, driven by the completion arriving while its request still owes beats rather than by a declaration, and the two agree independently on how many beats arrived after the bridge left: 4 and 4 in bridge_timeout_test, 9 and 9 in bridge_timeout_boundary_test, 6 and 6 in bridge_timeout_recovery_test. In bridge_timeout_test the scoreboard's 7 cancelled beats split exactly into the 4 that arrived late and the 3 never issued (28 predicted against 25 observed). cg_response_map now sees the timeout source of SLVERR that its cx_wait_status ignore_bins already reasoned about and that had never reached it. Two figures in the regression 20 entry were wrong and were corrected in regression 21: the bin total is 462, not 441, and that run was not warning-free. The merge spans four bus configurations as well as the narrow and timeout builds. All unreachable bins are illegal_bins, ignore_bins or default, and WLEN_MATCH and W_BEFORE_AW_LENGTH are waived as unreachable on this DUT. The constrained-random regression of BRG_ENV_008 now exists and is part of the merge. Still open: code coverage has not been reviewed.</t>
         </is>
       </c>
     </row>
@@ -4247,12 +4247,12 @@
       </c>
       <c r="J65" s="6" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>Seeds only change AXI IDs and FIXED lengths; no constrained-random test exists.</t>
+          <t>Closed by bridge_random_stress_test, regression 23 (285 runs, 0 failures, 0 UVM warnings). The gap was that a seed only moved the AXI IDs and the FIXED lengths, because every sequence pinned its traffic from a case list. This is the first test that hands a request to the solver with only the legal profile fixed, so the constraint set of axi4_transaction shapes it: c_burst_length, c_wrap_alignment, c_4kb_boundary, c_cache_legal and c_distribution all take part, which no other test lets them do. The wait and error policy is independent in the sense the requirement asks for: the answer for each AHB beat is drawn before the request is sent and the only thing the request contributes is how many beats need one. Because the plan is known in advance the sequence is a full oracle on its own, separate from the scoreboard: every read beat must carry the address-derived word for its own address, a beat answered with ERROR must report SLVERR and no other beat may, and a write must report SLVERR exactly when one of its beats was. 64 requests a run on 5 seeds, all failed=0. A run is 493 to 576 AHB beats with 56 to 78 injected errors, 166 to 191 wait states and 44 to 60 SLVERR responses, split 20/44 to 32/32 between reads and writes and 14/34/7 to 20/38/13 between FIXED, INCR and WRAP. The two independent counts agree exactly on all five seeds: the beats the sequence planned equal the AHB transfers the scoreboard matched (537, 493, 576, 515, 546) and the requests equal the AXI completions it matched (64), with zero mismatches, so the bridge issued exactly the predicted beats and every one of them matched the prediction. The run also has to be varied to pass: it fails if a direction, a burst type, an injected error, a wait state, a SLVERR or an OKAY never appeared. The first twelve requests walk every burst type in both directions before the random bulk starts, so those checks cannot flake on an unlucky seed. Deliberately kept out of the traffic, with reasons: sparse strobes and unaligned narrow writes are the negative cases of BRG_SIZ_006, narrow sizes are used only where the build supports them, and AXI4_WR_AW_BEFORE_W deadlocks this DUT. The test also runs only on the C_DPHASE_TIMEOUT=0 build and refuses to elaborate on a watchdog build: a random wait could be abandoned by the watchdog, and the scoreboard only tolerates that for a request the test declared in advance, which a random policy cannot do. Extending it to the timeout and narrow builds is the obvious next step and needs the wait cap tied to the built C_DPHASE_TIMEOUT first.</t>
         </is>
       </c>
     </row>
@@ -8546,22 +8546,22 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Constrained-random mixed traffic with independent AHB wait/error policy</t>
+          <t>The only test whose traffic is not a case list. Direction, burst, length, address, ID, cache and protection are left to the constraint set of axi4_transaction; only the legal profile is pinned, so lock stays normal, the strobes are the contiguous lanes the address and size select, narrow sizes appear only where the build supports them and AXI4_WR_AW_BEFORE_W is never sent. The AHB answer for each beat is drawn before the request is sent, without reference to it, so the sequence knows which beat will be answered with ERROR and checks every read word and every per-beat response against that plan while the scoreboard independently rebuilds the completion from the beats it observed. The first twelve requests walk every burst type in both directions, then the random bulk runs; the test fails if a direction, a burst type, an injected error, a wait state, a SLVERR or an OKAY never appeared.</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Multi-seed; coverage-driven; legal profile only</t>
+          <t>Default build only, C_DPHASE_TIMEOUT=0: a random wait on a watchdog build could be abandoned, and the scoreboard only tolerates a timeout the test declared in advance, so the test refuses to elaborate when dphase_timeout is non-zero. max_outstanding=1; return_responses=1; auto_gen_resp=0 with the plan drawn per request; AXI bready/rready delay 0 to 2, randomized per beat by the driver; AHB waits 0 to 4 on about a third of beats; errors on 12% of beats; AxLEN capped at 15 so SINGLE, INCR4/8/16 and WRAP4/8/16 all stay reachable and a run stays short. wr_order is 80/20 over all requests, which lands at roughly 35% of writes because a read is forced to PARALLEL. Per run: 64 requests, 493-576 AHB beats, 56-78 injected errors, 166-191 wait states, 44-60 SLVERR; scoreboard AHB and AXI mismatches 0 and its AHB match count equal to the beats the sequence planned on every seed</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>BRG_ENV_005, BRG_ENV_008</t>
+          <t>BRG_ENV_008, BRG_UNS_003</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Implemented</t>
         </is>
       </c>
     </row>

--- a/00_doc/axi_ahblite_bridge_vplan.xlsx
+++ b/00_doc/axi_ahblite_bridge_vplan.xlsx
@@ -604,7 +604,7 @@
       </c>
       <c r="K1" s="3" t="inlineStr">
         <is>
-          <t>Evidence / Gap (regression 23, 2026-09-28)</t>
+          <t>Evidence / Gap (regression 24, 2026-09-29)</t>
         </is>
       </c>
     </row>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>Regression 8, narrow build, 32-bit, 5 seeds: bridge_size_mapping_test run=64 failed=0 (AHB 318/0, AXI 64/0). 8/16-bit singles on every legal lane; 8/16-bit INCR4 and INCR8 (crossing a bus-word boundary), INCR16, undefined INCR, FIXED3, WRAP2, WRAP4, WRAP8 and WRAP16 (wrapping inside the burst) with HSIZE = AxSIZE; filler bytes in non-strobed lanes never reach memory; cx_mapping_size at 100%. 64-bit (32-bit narrow size) not exercised. Regression 20 closes the 64-bit gap: on the 64-bit narrow build bridge_parameter_test writes 1, 2 and 4 byte transfers on every legal lane, 14 cases in all, and reads each word back at full width so the lanes outside the transfer are checked as untouched. The 4-byte case is the 32-bit narrow size on a 64-bit bus that was missing.</t>
+          <t>Regression 8, narrow build, 32-bit, 5 seeds: bridge_size_mapping_test run=64 failed=0 (AHB 318/0, AXI 64/0). 8/16-bit singles on every legal lane; 8/16-bit INCR4 and INCR8 (crossing a bus-word boundary), INCR16, undefined INCR, FIXED3, WRAP2, WRAP4, WRAP8 and WRAP16 (wrapping inside the burst) with HSIZE = AxSIZE; filler bytes in non-strobed lanes never reach memory; cx_mapping_size at 100%. 64-bit (32-bit narrow size) not exercised. Regression 20 closes the 64-bit gap: on the 64-bit narrow build bridge_parameter_test writes 1, 2 and 4 byte transfers on every legal lane, 14 cases in all, and reads each word back at full width so the lanes outside the transfer are checked as untouched. The 4-byte case is the 32-bit narrow size on a 64-bit bus that was missing. Regression 24 closes the part of this item that the single-transfer evidence above could not reach. Every narrow case in the regression was a single write, and a single write never increments an address, so gen_32_data_width_narrow in ahb_mstr_if, which holds the whole per-size address increment and the WRAP2/4/8/16 wrapping for narrow bursts and exists only when C_S_AXI_SUPPORTS_NARROW_BURST is 1, had never been driven. bridge_random_stress_test now runs on the narrow build with the size drawn per request, so 34 to 44 of its 64 requests a run are narrow multi-beat bursts of every burst type, 23 to 30 of them starting at a byte lane inside the word. 5 seeds, 0 failures, and the predictor and the bus agree on every beat: the scoreboard matched 575 AHB transfers against 575 planned with 0 mismatches on the first seed, and the same identity holds on the others.</t>
         </is>
       </c>
     </row>
@@ -4081,7 +4081,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>Merged, regression 23 (285 runs, 0 failures, 0 UVM warnings): functional coverage is closed. Covergroups 100% of bins (462/462), assertions 51/51 hit with 0 failures, cover directives 13/13 (100.0%), the last two read from the reports 'make assert_report' produces. The e2e_cov residue warning that regression 21 carried on 25 runs is fixed and the regression is warning-free on all 280. It was a defect in the coverage collector, not in the bridge: e2e_cov retired a response context only once it had consumed len+1 actual AHB beats, so a request the C_DPHASE_TIMEOUT watchdog abandoned never retired, sat in rsp_ctx_queue for the rest of the test and went on swallowing the beats of the requests behind it. The residue was the visible half; the damaging half was that every AHB beat after the first timeout was credited to the wrong request, so the beat position in cg_ahb_response and the saw_error/saw_wait pair in cg_response_map were wrong for those tests. It showed up only in bridge_timeout_test because bridge_timeout_boundary_test loses no beats (its requests are single beat and the slave still reports the beat the bridge walked away from) and bridge_timeout_recovery_test asserts reset three times, which calls cov.reset_state() and wiped the evidence. e2e_cov now has the same abandoned-request handling as the scoreboard, driven by the completion arriving while its request still owes beats rather than by a declaration, and the two agree independently on how many beats arrived after the bridge left: 4 and 4 in bridge_timeout_test, 9 and 9 in bridge_timeout_boundary_test, 6 and 6 in bridge_timeout_recovery_test. In bridge_timeout_test the scoreboard's 7 cancelled beats split exactly into the 4 that arrived late and the 3 never issued (28 predicted against 25 observed). cg_response_map now sees the timeout source of SLVERR that its cx_wait_status ignore_bins already reasoned about and that had never reached it. Two figures in the regression 20 entry were wrong and were corrected in regression 21: the bin total is 462, not 441, and that run was not warning-free. The merge spans four bus configurations as well as the narrow and timeout builds. All unreachable bins are illegal_bins, ignore_bins or default, and WLEN_MATCH and W_BEFORE_AW_LENGTH are waived as unreachable on this DUT. The constrained-random regression of BRG_ENV_008 now exists and is part of the merge. Still open: code coverage has not been reviewed.</t>
+          <t>Merged, regression 24 (315 runs, 0 failures, 0 UVM warnings). Functional coverage is closed: covergroups 100% of bins (462/462), assertions 51/51 hit with 0 failures and none left unhit, cover directives 13/13 (100.0%), the last two read from the reports 'make assert_report' produces. The merge spans seven builds: 32 and 64 bit, narrow off and on, and all five C_DPHASE_TIMEOUT values. Code coverage is now reviewed, which was the last thing open here. The DUT stands at 88.90% hits and 84.25% coverage, up from 83.00% in regression 22, the rise coming from the narrow burst traffic bridge_random_stress_test added on the narrow build. By design unit: time_out 100.00%, axi_ahblite_bridge 90.87%, axi_slv_if 90.05% (statement 96.80, branch 96.02, FEC condition 74.07), ahb_mstr_if 85.16% (statement 91.50, branch 86.13, FEC condition 70.64), ahb_skid_buf 72.92% and counter_f 70.02%. time_out reaching 100% is the five C_DPHASE_TIMEOUT builds paying off. Two units are waived, with the reason visible at their instantiation rather than argued from the numbers. counter_f is a generic up/down counter reused from the reference design and the bridge wires it one way only: time_out ties Count_Down to 1'b1 and leaves Count_Out unconnected, so the up-count path is dead code and the count output cannot toggle, which is what its FEC condition of 50.00% and toggle of 61.22% are made of. ahb_skid_buf is likewise instantiated with skid_stop, S_STRB and S_User all tied to constants, so the stop path and those payload bits are unreachable in this configuration and account for its FEC condition of 36.36%. Neither shortfall is missing verification of bridge behaviour. Not waived and still open: ahb_mstr_if is the weakest real logic in the design at 85.16% with FEC condition 70.64%, and the residual there has not been itemised, so it is not yet known which of it is unreachable in the supported configurations and which is untested. This item stays In Progress for that reason alone; requirement and assertion coverage are closed.</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>Closed by bridge_random_stress_test, regression 23 (285 runs, 0 failures, 0 UVM warnings). The gap was that a seed only moved the AXI IDs and the FIXED lengths, because every sequence pinned its traffic from a case list. This is the first test that hands a request to the solver with only the legal profile fixed, so the constraint set of axi4_transaction shapes it: c_burst_length, c_wrap_alignment, c_4kb_boundary, c_cache_legal and c_distribution all take part, which no other test lets them do. The wait and error policy is independent in the sense the requirement asks for: the answer for each AHB beat is drawn before the request is sent and the only thing the request contributes is how many beats need one. Because the plan is known in advance the sequence is a full oracle on its own, separate from the scoreboard: every read beat must carry the address-derived word for its own address, a beat answered with ERROR must report SLVERR and no other beat may, and a write must report SLVERR exactly when one of its beats was. 64 requests a run on 5 seeds, all failed=0. A run is 493 to 576 AHB beats with 56 to 78 injected errors, 166 to 191 wait states and 44 to 60 SLVERR responses, split 20/44 to 32/32 between reads and writes and 14/34/7 to 20/38/13 between FIXED, INCR and WRAP. The two independent counts agree exactly on all five seeds: the beats the sequence planned equal the AHB transfers the scoreboard matched (537, 493, 576, 515, 546) and the requests equal the AXI completions it matched (64), with zero mismatches, so the bridge issued exactly the predicted beats and every one of them matched the prediction. The run also has to be varied to pass: it fails if a direction, a burst type, an injected error, a wait state, a SLVERR or an OKAY never appeared. The first twelve requests walk every burst type in both directions before the random bulk starts, so those checks cannot flake on an unlucky seed. Deliberately kept out of the traffic, with reasons: sparse strobes and unaligned narrow writes are the negative cases of BRG_SIZ_006, narrow sizes are used only where the build supports them, and AXI4_WR_AW_BEFORE_W deadlocks this DUT. The test also runs only on the C_DPHASE_TIMEOUT=0 build and refuses to elaborate on a watchdog build: a random wait could be abandoned by the watchdog, and the scoreboard only tolerates that for a request the test declared in advance, which a random policy cannot do. Extending it to the timeout and narrow builds is the obvious next step and needs the wait cap tied to the built C_DPHASE_TIMEOUT first.</t>
+          <t>Closed by bridge_random_stress_test, regression 23 (285 runs, 0 failures, 0 UVM warnings). The gap was that a seed only moved the AXI IDs and the FIXED lengths, because every sequence pinned its traffic from a case list. This is the first test that hands a request to the solver with only the legal profile fixed, so the constraint set of axi4_transaction shapes it: c_burst_length, c_wrap_alignment, c_4kb_boundary, c_cache_legal and c_distribution all take part, which no other test lets them do. The wait and error policy is independent in the sense the requirement asks for: the answer for each AHB beat is drawn before the request is sent and the only thing the request contributes is how many beats need one. Because the plan is known in advance the sequence is a full oracle on its own, separate from the scoreboard: every read beat must carry the address-derived word for its own address, a beat answered with ERROR must report SLVERR and no other beat may, and a write must report SLVERR exactly when one of its beats was. 64 requests a run on 5 seeds, all failed=0. A run is 493 to 576 AHB beats with 56 to 78 injected errors, 166 to 191 wait states and 44 to 60 SLVERR responses, split 20/44 to 32/32 between reads and writes and 14/34/7 to 20/38/13 between FIXED, INCR and WRAP. The two independent counts agree exactly on all five seeds: the beats the sequence planned equal the AHB transfers the scoreboard matched (537, 493, 576, 515, 546) and the requests equal the AXI completions it matched (64), with zero mismatches, so the bridge issued exactly the predicted beats and every one of them matched the prediction. The run also has to be varied to pass: it fails if a direction, a burst type, an injected error, a wait state, a SLVERR or an OKAY never appeared. The first twelve requests walk every burst type in both directions before the random bulk starts, so those checks cannot flake on an unlucky seed. Deliberately kept out of the traffic, with reasons: sparse strobes and unaligned narrow writes are the negative cases of BRG_SIZ_006, narrow sizes are used only where the build supports them, and AXI4_WR_AW_BEFORE_W deadlocks this DUT. The test also runs only on the C_DPHASE_TIMEOUT=0 build and refuses to elaborate on a watchdog build: a random wait could be abandoned by the watchdog, and the scoreboard only tolerates that for a request the test declared in advance, which a random policy cannot do. Regression 24 extends it to the narrow build and to all five C_DPHASE_TIMEOUT builds, 35 runs in all, 0 failures. On the narrow build the size is drawn per request, so 34 to 44 of the 64 requests are narrow and 23 to 30 of them start at a byte lane inside the word. On a watchdog build the policy cannot simply draw a wait at random, because one that tripped the watchdog would not have been declared; ordinary requests are capped four cycles below the threshold and every eighth request after the seeded head is a deliberate timeout instead, all of its beats answered OKAY so SLVERR can only mean the watchdog, declared with expect_timeout so the watchdog is required to fire. 7 of them a run on every build, and the run fails if a watchdog build never trips it. The two independent counts still close on every build: the beats the sequence planned equal the AHB transfers the scoreboard matched plus the ones it recorded as cancelled, for example 558 = 551 + 7 on the 16-cycle build and 512 = 505 + 7 on the 256-cycle one, with one cancelled beat per timeout. Across all 35 runs a run is 476 to 624 beats and 40 to 70 SLVERR responses.</t>
         </is>
       </c>
     </row>
@@ -8551,12 +8551,12 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Default build only, C_DPHASE_TIMEOUT=0: a random wait on a watchdog build could be abandoned, and the scoreboard only tolerates a timeout the test declared in advance, so the test refuses to elaborate when dphase_timeout is non-zero. max_outstanding=1; return_responses=1; auto_gen_resp=0 with the plan drawn per request; AXI bready/rready delay 0 to 2, randomized per beat by the driver; AHB waits 0 to 4 on about a third of beats; errors on 12% of beats; AxLEN capped at 15 so SINGLE, INCR4/8/16 and WRAP4/8/16 all stay reachable and a run stays short. wr_order is 80/20 over all requests, which lands at roughly 35% of writes because a read is forced to PARALLEL. Per run: 64 requests, 493-576 AHB beats, 56-78 injected errors, 166-191 wait states, 44-60 SLVERR; scoreboard AHB and AXI mismatches 0 and its AHB match count equal to the beats the sequence planned on every seed</t>
+          <t>Seven builds: default, narrow, and all five C_DPHASE_TIMEOUT values. max_outstanding=1; return_responses=1; auto_gen_resp=0 with the plan drawn per request; AXI bready/rready delay 0 to 2, randomized per beat by the driver; AHB waits 0 to 4 on about a third of beats; errors on 12% of beats; AxLEN capped at 15 so SINGLE, INCR4/8/16 and WRAP4/8/16 all stay reachable and a run stays short. wr_order is 80/20 over all requests, which lands at roughly 35% of writes because a read is forced to PARALLEL. On the narrow build the size is drawn per request instead of being fixed at the bus width. On a watchdog build ordinary waits are capped four cycles below the threshold and every eighth request after the seeded head is a deliberate timeout, with its last beat held past the threshold and expect_timeout declared for it. The last beat and not a middle one: after the watchdog fires the bridge drives HTRANS IDLE and accepts the rest of a write burst, moving HWDATA while the slave is still in the data phase, and it answers on B in the same cycle the slave releases HREADY, so a mid-burst hang puts a beat carrying later data and the completion that would excuse it into one time step. Abandoning a burst part way through stays with bridge_timeout_test. Per run: 64 requests, 476-624 AHB beats, 40-70 SLVERR, 7 timeout cases on a watchdog build; scoreboard mismatches 0 and its AHB match count plus its cancelled beats equal the beats the sequence planned</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>BRG_ENV_008, BRG_UNS_003</t>
+          <t>BRG_ENV_008, BRG_UNS_003, BRG_SIZ_003</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">

--- a/00_doc/axi_ahblite_bridge_vplan.xlsx
+++ b/00_doc/axi_ahblite_bridge_vplan.xlsx
@@ -4081,7 +4081,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>Merged, regression 24 (315 runs, 0 failures, 0 UVM warnings). Functional coverage is closed: covergroups 100% of bins (462/462), assertions 51/51 hit with 0 failures and none left unhit, cover directives 13/13 (100.0%), the last two read from the reports 'make assert_report' produces. The merge spans seven builds: 32 and 64 bit, narrow off and on, and all five C_DPHASE_TIMEOUT values. Code coverage is now reviewed, which was the last thing open here. The DUT stands at 88.90% hits and 84.25% coverage, up from 83.00% in regression 22, the rise coming from the narrow burst traffic bridge_random_stress_test added on the narrow build. By design unit: time_out 100.00%, axi_ahblite_bridge 90.87%, axi_slv_if 90.05% (statement 96.80, branch 96.02, FEC condition 74.07), ahb_mstr_if 85.16% (statement 91.50, branch 86.13, FEC condition 70.64), ahb_skid_buf 72.92% and counter_f 70.02%. time_out reaching 100% is the five C_DPHASE_TIMEOUT builds paying off. Two units are waived, with the reason visible at their instantiation rather than argued from the numbers. counter_f is a generic up/down counter reused from the reference design and the bridge wires it one way only: time_out ties Count_Down to 1'b1 and leaves Count_Out unconnected, so the up-count path is dead code and the count output cannot toggle, which is what its FEC condition of 50.00% and toggle of 61.22% are made of. ahb_skid_buf is likewise instantiated with skid_stop, S_STRB and S_User all tied to constants, so the stop path and those payload bits are unreachable in this configuration and account for its FEC condition of 36.36%. Neither shortfall is missing verification of bridge behaviour. Not waived and still open: ahb_mstr_if is the weakest real logic in the design at 85.16% with FEC condition 70.64%, and the residual there has not been itemised, so it is not yet known which of it is unreachable in the supported configurations and which is untested. This item stays In Progress for that reason alone; requirement and assertion coverage are closed.</t>
+          <t>Merged, regression 24 (315 runs, 0 failures, 0 UVM warnings). Functional coverage is closed: covergroups 100% of bins (462/462), assertions 51/51 hit with 0 failures and none left unhit, cover directives 13/13 (100.0%). The merge spans seven builds: 32 and 64 bit, narrow off and on, and all five C_DPHASE_TIMEOUT values. Code coverage is now reviewed to the line. The HTML report stops at a percentage per design unit, so 'make code_report' was added to produce the text report that carries the uncovered statements, branches and conditions; it covers the six design units of the bridge only. The DUT is at 88.90% hits and 84.25% coverage, up from 83.00% in regression 22, the rise coming from the narrow burst traffic bridge_random_stress_test added. By design unit: time_out 100.00%, axi_ahblite_bridge 90.87%, axi_slv_if 90.05% (statements 182/188), ahb_mstr_if 85.16% (statements 280/306, branches 205/238, FEC conditions 77/109), ahb_skid_buf 72.92%, counter_f 70.02%. All four address generators of ahb_mstr_if are now exercised: gen_32_data_width and gen_64_data_width at 100%, and the two narrow ones at 96.07% and 96.87%. Waived, with the reason visible in the source rather than argued from the numbers. First, unused generality of blocks reused from the reference design: time_out ties counter_f's Count_Down to 1'b1 and leaves Count_Out unconnected, so the up-count path is dead and the count output cannot toggle, which is its FEC condition of 50.00% and toggle of 61.22%; ahb_skid_buf is instantiated with skid_stop, S_STRB and S_User tied to constants, which is its FEC condition of 36.36%. Second, states AXI4 itself forbids: ahb_mstr_if lines 259 and 324 are the default arms of case (axi_size) in the narrow address generators and need a size wider than the bus, and the axi_slv_if condition rows for AxBURST[1] with AxLEN == 0 need a one-beat WRAP, which c_burst_length rules out. None of these hides bridge behaviour. Not waived. One gap accounts for almost all of the rest, and it is the same cause on both sides of the bridge: no stimulus ever drops WVALID in the middle of a write burst, because axi4_mst_driver.drive_w streams the beats of a burst back to back and the agent has no knob for a gap. In ahb_mstr_if that leaves four FSM states unreached, AHB_WR_WAIT, AHB_LAST_WAIT, AHB_LAST and AHB_ONEKB_LAST, together with the two branches that enter them, and it accounts for 24 of its 26 unexecuted statements; in axi_slv_if it leaves AXI_WVALID_WAIT unreached along with the S_AXI_WVALID condition rows. AXI_WR_RESP_WAIT in axi_slv_if is also unreached and is not yet attributed. This item stays In Progress for that gap alone: requirement coverage and assertion coverage are closed, and the review itself is done. Closing it needs a write-data starvation test, which is a WVALID gap knob on the AXI master agent and a sequence that uses it; the AHB BUSY transfer the bridge inserts in reply is already a covered value elsewhere, so the check is that the burst still completes correctly around the gap.</t>
         </is>
       </c>
     </row>

--- a/00_doc/axi_ahblite_bridge_vplan.xlsx
+++ b/00_doc/axi_ahblite_bridge_vplan.xlsx
@@ -604,7 +604,7 @@
       </c>
       <c r="K1" s="3" t="inlineStr">
         <is>
-          <t>Evidence / Gap (regression 24, 2026-09-29)</t>
+          <t>Evidence / Gap (regression 26, 2026-09-29)</t>
         </is>
       </c>
     </row>
@@ -4076,12 +4076,12 @@
       </c>
       <c r="J62" s="5" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>Merged, regression 24 (315 runs, 0 failures, 0 UVM warnings). Functional coverage is closed: covergroups 100% of bins (462/462), assertions 51/51 hit with 0 failures and none left unhit, cover directives 13/13 (100.0%). The merge spans seven builds: 32 and 64 bit, narrow off and on, and all five C_DPHASE_TIMEOUT values. Code coverage is now reviewed to the line. The HTML report stops at a percentage per design unit, so 'make code_report' was added to produce the text report that carries the uncovered statements, branches and conditions; it covers the six design units of the bridge only. The DUT is at 88.90% hits and 84.25% coverage, up from 83.00% in regression 22, the rise coming from the narrow burst traffic bridge_random_stress_test added. By design unit: time_out 100.00%, axi_ahblite_bridge 90.87%, axi_slv_if 90.05% (statements 182/188), ahb_mstr_if 85.16% (statements 280/306, branches 205/238, FEC conditions 77/109), ahb_skid_buf 72.92%, counter_f 70.02%. All four address generators of ahb_mstr_if are now exercised: gen_32_data_width and gen_64_data_width at 100%, and the two narrow ones at 96.07% and 96.87%. Waived, with the reason visible in the source rather than argued from the numbers. First, unused generality of blocks reused from the reference design: time_out ties counter_f's Count_Down to 1'b1 and leaves Count_Out unconnected, so the up-count path is dead and the count output cannot toggle, which is its FEC condition of 50.00% and toggle of 61.22%; ahb_skid_buf is instantiated with skid_stop, S_STRB and S_User tied to constants, which is its FEC condition of 36.36%. Second, states AXI4 itself forbids: ahb_mstr_if lines 259 and 324 are the default arms of case (axi_size) in the narrow address generators and need a size wider than the bus, and the axi_slv_if condition rows for AxBURST[1] with AxLEN == 0 need a one-beat WRAP, which c_burst_length rules out. None of these hides bridge behaviour. Not waived. One gap accounts for almost all of the rest, and it is the same cause on both sides of the bridge: no stimulus ever drops WVALID in the middle of a write burst, because axi4_mst_driver.drive_w streams the beats of a burst back to back and the agent has no knob for a gap. In ahb_mstr_if that leaves four FSM states unreached, AHB_WR_WAIT, AHB_LAST_WAIT, AHB_LAST and AHB_ONEKB_LAST, together with the two branches that enter them, and it accounts for 24 of its 26 unexecuted statements; in axi_slv_if it leaves AXI_WVALID_WAIT unreached along with the S_AXI_WVALID condition rows. AXI_WR_RESP_WAIT in axi_slv_if is also unreached and is not yet attributed. This item stays In Progress for that gap alone: requirement coverage and assertion coverage are closed, and the review itself is done. Closing it needs a write-data starvation test, which is a WVALID gap knob on the AXI master agent and a sequence that uses it; the AHB BUSY transfer the bridge inserts in reply is already a covered value elsewhere, so the check is that the burst still completes correctly around the gap.</t>
+          <t>Merged, regression 26 (320 runs, 0 failures, 0 UVM warnings). Functional coverage is closed: covergroups 100% of bins (462/462), assertions 51/51 hit with 0 failures and none left unhit, cover directives 13/13. The merge spans seven builds. Code coverage is reviewed to the line, using 'make code_report', a target added for this because the HTML report stops at a percentage per design unit. The review drove two tests and the DUT moved from 83.00% in regression 22 to 87.40%: bridge_random_stress_test on the narrow build woke the narrow burst address generators, and bridge_write_starvation_test closed the biggest hole it found. ahb_mstr_if is at 302/306 statements (98.6%, from 280/306) and axi_slv_if at 186/188 (98.9%, from 182/188). Every uncovered item is now accounted for. Waived, each with the reason in the source rather than argued from the numbers: (1) unused generality of blocks reused from the reference design, time_out ties counter_f's Count_Down to 1'b1 and leaves Count_Out unconnected, and ahb_skid_buf is instantiated with skid_stop, S_STRB and S_User tied to constants, which is what their FEC condition scores of 50.00% and 36.36% are made of; (2) states AXI4 forbids, ahb_mstr_if lines 259 and 324 are the default arms of case (axi_size) and need a size wider than the bus, and the axi_slv_if condition rows for AxBURST[1] with AxLEN == 0 need a one-beat WRAP; (3) two branches that are dead by construction, proved by there being exactly one entry into each state and its condition contradicting the branch: AHB_LAST_WAIT is entered only when one_kb_in_progress, fixed_burst_access or wrap_2_in_progress holds, so its plain else at line 572 cannot run, and AHB_LAST is entered only when none of them holds, so its fixed/wrap2 arm at line 583 cannot. One item is covered by decision rather than by stimulus. Decision 2026-09-29: accept AXI_WR_RESP_WAIT in axi_slv_if, lines 473 to 475, as an exception. It needs send_bresp already high in the cycle AXI_WRITING accepts WLAST. On an untimed write that cannot happen, because the last AHB beat is the one carrying the WLAST data and so completes after it; it is reachable only when the watchdog fires part way through a multi-beat write and the AHB counter drains before the master has delivered WLAST. It is therefore reachable but not reached, and it is recorded as such rather than waived on a false claim of unreachability. The traffic that would produce it is a mid-burst write timeout, which bridge_random_stress_test deliberately avoids: it hangs the last beat of its timeout cases so that the beat the bridge abandons and the completion that marks it abandoned cannot land in the same time step, a race that cost three regressions to diagnose. Two statements out of the 494 in the two main design units were judged not worth reopening that. If the item is ever wanted, the shape is known: a declared timeout on a middle beat of a multi-beat write, with the write data of that request left out of the scoreboard comparison.</t>
         </is>
       </c>
     </row>
@@ -4195,7 +4195,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>Conflict: the Tests sheet marks bridge_vhdl_equivalence_test as Excluded. Decide and align both sheets.</t>
+          <t>The conflict this entry used to record is gone: both sheets now read Not Started. The Tests sheet did mark bridge_vhdl_equivalence_test as Excluded up to 2026-09-24 and was changed on 2026-09-25; the note here was left stale. Decision 2026-09-29: do not exclude it. The project's own spec review makes it a prerequisite rather than an optional extra, in its own words 'required before treating the translated DUT, or the RTL observations above, as golden' (pg177_spec_review.md, closing table). Several decisions in that review lean on it already: the lock handling kept in Section 4.1, the continue-and-report error oracle in Section 3.4, and the unsupported single-write strobe behaviour, are all justified as matching the reference VHDL, and that match was established by reading the VHDL, never by running it. Excluding the item would leave those justifications resting on a review no simulation has ever checked. It is also not blocked for want of material. 00_doc/axi_ahblite_bridge_v3_0_vh_rfs.vhd is the complete reference design, 3953 lines, and its six entities are exactly the six SystemVerilog modules of the DUT: counter_f, time_out, ahb_skid_buf, axi_slv_if, ahb_mstr_if and axi_ahblite_bridge. A side-by-side harness would compile it into its own library, instantiate both bridges in bridge_tb_top on the same clock, reset and AXI stimulus, and compare the AHB master ports and the AXI responses cycle by cycle; the existing regression is the stimulus. One thing to establish first: whether this Questa 10.6b installation is licensed for VHDL, which a single 'vcom -version' answers. If it is not, the item cannot be done here and should be excluded on that ground, which is a different and honest reason from the one the sheets carried.</t>
         </is>
       </c>
     </row>

--- a/00_doc/axi_ahblite_bridge_vplan.xlsx
+++ b/00_doc/axi_ahblite_bridge_vplan.xlsx
@@ -4195,7 +4195,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>The conflict this entry used to record is gone: both sheets now read Not Started. The Tests sheet did mark bridge_vhdl_equivalence_test as Excluded up to 2026-09-24 and was changed on 2026-09-25; the note here was left stale. Decision 2026-09-29: do not exclude it. The project's own spec review makes it a prerequisite rather than an optional extra, in its own words 'required before treating the translated DUT, or the RTL observations above, as golden' (pg177_spec_review.md, closing table). Several decisions in that review lean on it already: the lock handling kept in Section 4.1, the continue-and-report error oracle in Section 3.4, and the unsupported single-write strobe behaviour, are all justified as matching the reference VHDL, and that match was established by reading the VHDL, never by running it. Excluding the item would leave those justifications resting on a review no simulation has ever checked. It is also not blocked for want of material. 00_doc/axi_ahblite_bridge_v3_0_vh_rfs.vhd is the complete reference design, 3953 lines, and its six entities are exactly the six SystemVerilog modules of the DUT: counter_f, time_out, ahb_skid_buf, axi_slv_if, ahb_mstr_if and axi_ahblite_bridge. A side-by-side harness would compile it into its own library, instantiate both bridges in bridge_tb_top on the same clock, reset and AXI stimulus, and compare the AHB master ports and the AXI responses cycle by cycle; the existing regression is the stimulus. One thing to establish first: whether this Questa 10.6b installation is licensed for VHDL, which a single 'vcom -version' answers. If it is not, the item cannot be done here and should be excluded on that ground, which is a different and honest reason from the one the sheets carried.</t>
+          <t>The conflict this entry used to record is gone: both sheets now read Not Started. The Tests sheet did mark bridge_vhdl_equivalence_test as Excluded up to 2026-09-24 and was changed on 2026-09-25; the note here was left stale. Decision 2026-09-29: do not exclude it. The project's own spec review makes it a prerequisite rather than an optional extra, in its own words 'required before treating the translated DUT, or the RTL observations above, as golden' (pg177_spec_review.md, closing table). Several decisions in that review lean on it already: the lock handling kept in Section 4.1, the continue-and-report error oracle in Section 3.4, and the unsupported single-write strobe behaviour, are all justified as matching the reference VHDL, and that match was established by reading the VHDL, never by running it. Excluding the item would leave those justifications resting on a review no simulation has ever checked. It is also not blocked for want of material. 00_doc/axi_ahblite_bridge_v3_0_vh_rfs.vhd is the complete reference design, 3953 lines, and its six entities are exactly the six SystemVerilog modules of the DUT: counter_f, time_out, ahb_skid_buf, axi_slv_if, ahb_mstr_if and axi_ahblite_bridge. A side-by-side harness would compile it into its own library, instantiate both bridges in bridge_tb_top on the same clock, reset and AXI stimulus, and compare the AHB master ports and the AXI responses cycle by cycle; the existing regression is the stimulus. Tried on 2026-10-01 with 'make compile_ref', a target added for this that builds the reference into its own library and that nothing else depends on. The result rules out the reason the sheets used to imply and names the real one: VHDL itself is fine here, vcom loaded STANDARD, TEXTIO, std_logic_1164 and NUMERIC_STD without complaint, so this is not a licence or a tool-support problem. It stopped at line 105 with 'Library "unisim" not found': the reference instantiates Xilinx UNISIM primitives, so it needs the Xilinx simulation libraries compiled for this Questa, which Vivado's compile_simlib produces. Blocked on that infrastructure, not on the testbench. Parked by decision on 2026-10-01 rather than excluded, because the spec review still treats the comparison as a prerequisite for calling the translation golden; if the UNISIM libraries are never going to be available here, that is the ground to exclude it on.</t>
         </is>
       </c>
     </row>

--- a/00_doc/axi_ahblite_bridge_vplan.xlsx
+++ b/00_doc/axi_ahblite_bridge_vplan.xlsx
@@ -536,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K65"/>
+  <dimension ref="A1:K66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -605,7 +605,7 @@
       </c>
       <c r="K1" s="3" t="inlineStr">
         <is>
-          <t>Evidence / Gap (regression 31, 2026-10-01)</t>
+          <t>Evidence / Gap (regression 32, 2026-10-01)</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>Oracle confirmed against the reference VHDL: the AHB state machine samples HRESP into slv_err_resp and continues the burst; WR_ERR_REG makes BRESP SLVERR sticky until write_complete; RRESP is per beat (spec review 3.4). Regression 11, 5 seeds: bridge_response_mapping_test run=61 failed=0, 384 AHB beats (44 ERROR, 172 waited), 43 SLVERR responses, 0 scoreboard mismatches. ERROR on the first, a middle and the last beat with 0 and 3 waits, on two beats of one burst, on every AHB burst shape and on the NONSEQ restart beat after a 1 KB split; every burst completes all its beats (no planned beat left, no unplanned beat).</t>
+          <t>Oracle confirmed against the reference design: the AHB state machine samples HRESP into slv_err_resp and continues the burst; WR_ERR_REG makes BRESP SLVERR sticky until write_complete; RRESP is per beat (spec review 3.4). Regression 11, 5 seeds: bridge_response_mapping_test run=61 failed=0, 384 AHB beats (44 ERROR, 172 waited), 43 SLVERR responses, 0 scoreboard mismatches. ERROR on the first, a middle and the last beat with 0 and 3 waits, on two beats of one burst, on every AHB burst shape and on the NONSEQ restart beat after a 1 KB split; every burst completes all its beats (no planned beat left, no unplanned beat).</t>
         </is>
       </c>
     </row>
@@ -3539,7 +3539,7 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Equal 64-bit AXI/AHB data width and 32-64-bit address configuration passes the compliance regression</t>
+          <t>Equal 64-bit AXI/AHB data width at 32-bit address width, narrow burst off and on, passes the compliance regression</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>The bus widths are package parameters, so vopt -G cannot reach them and each width is its own compilation: BRIDGE_DATA_WIDTH selects it and the Makefile builds the 64-bit variant into its own library (compile_wide, optimize_wide). bridge_parameter_test runs the same source on all four builds and the profile grows with the bus: 32-bit narrow off run=12, 32-bit narrow on run=18 with 6 narrow writes, 64-bit narrow off run=12, 64-bit narrow on run=26 with 14 narrow writes, all failed=0 on 5 seeds each. Both 64-bit images elaborate and run: this is the first time the gen_64_data_width and gen_64_narrow_decode branches of ahb_mstr_if and axi_slv_if have been simulated. The compliance subset (sanity, data integrity, burst matrix, size mapping, response mapping) reports identical scoreboard figures on 32 and 64 bits, for example burst matrix 1614/62 and response mapping 384/61, so the same translation work is done correctly with 8 bytes a beat. Address width stays at 32 on both; the 32 to 64 bit address sweep is not built yet.</t>
+          <t>The bus widths are package parameters, so vopt -G cannot reach them and each width is its own compilation: BRIDGE_DATA_WIDTH selects it and the Makefile builds the 64-bit variant into its own library (compile_wide, optimize_wide). bridge_parameter_test runs the same source on all four builds and the profile grows with the bus: 32-bit narrow off run=12, 32-bit narrow on run=18 with 6 narrow writes, 64-bit narrow off run=12, 64-bit narrow on run=26 with 14 narrow writes, all failed=0 on 5 seeds each. Both 64-bit images elaborate and run: this is the first time the gen_64_data_width and gen_64_narrow_decode branches of ahb_mstr_if and axi_slv_if have been simulated. The compliance subset (sanity, data integrity, burst matrix, size mapping, response mapping) reports identical scoreboard figures on 32 and 64 bits, for example burst matrix 1614/62 and response mapping 384/61, so the same translation work is done correctly with 8 bytes a beat. Scope narrowed on 2026-10-01 so the requirement states what this matrix actually runs: 64-bit data at 32-bit address, narrow off and on. The 33 to 64 bit address range PG177 also permits was never exercised here and has been moved out to BRG_CFG_004 rather than left as an unmet clause inside an item marked Complete.</t>
         </is>
       </c>
     </row>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>bridge_illegal_parameter_test</t>
+          <t>bridge_illegal_param_top; make illegal_param_check</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -3621,19 +3621,19 @@
       </c>
       <c r="J54" s="8" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>Environment-side checks only (vip_env_cfg.is_valid, transaction constructors, SVA $fatal). The DUT has no elaboration guards; no negative test.</t>
+          <t>Closed on 2026-10-01. The gap was on both sides: the design had no configuration guards at all, and there was no negative test. axi_ahblite_bridge now carries eight, one generate branch each, for an AXI or AHB data width that is not 32 or 64, the two widths differing, the AXI and AHB address widths differing, an address width outside 32 to 64, an ID width outside 1 to 32, a C_DPHASE_TIMEOUT that is not 0, 16, 32, 64, 128 or 256, and a non-boolean C_S_AXI_SUPPORTS_NARROW_BURST. A legal build elaborates none of them, so they cost nothing and do not show up in code coverage, which the unchanged 335-run regression confirms. They report with $fatal from an initial block rather than with an elaboration $error, and they compare with != rather than with inside. Both choices are about this file parsing on every tool that reads it: an elaboration task reports a cycle earlier and inside reads better, but a parse failure inside a guard would stop a legal build as well, which is far worse than reporting at time zero before anything has run. The reason is written in the source next to the guards. The negative test is 'make illegal_param_check' over bridge_illegal_param_top, which instantiates the bridge on its own with no ports connected and no stimulus, so a build can only be judged on whether the guards stop it. Each of the nine cases is its own compilation with the parameter under test from a define and every other one legal, so a case that fails can only have failed for the reason it names. All nine were rejected and each by its own guard, with the message naming the parameter and its value: data widths 8 and 16, a 64/32 data width mismatch, an address width mismatch, an address width of 16, an ID width of 33, C_DPHASE_TIMEOUT of 7 and of 1000, and narrow burst set to 2. None was caught by a generic tool error instead of a guard, and none got through. It is a separate target rather than part of regress on purpose: a set of cases that all have to fail cannot share a pass criterion with a set that all have to pass. A case counts as rejected whichever stage catches it, because some illegal widths are refused by the tool before the guards get a chance, and that is still a rejection. The environment-side checks this entry already had, vip_env_cfg.is_valid and the transaction constructors, are unchanged and now sit behind a design that refuses the same configurations on its own.</t>
         </is>
       </c>
     </row>
     <row r="55" ht="28.8" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>BRG_UNS_001</t>
+          <t>BRG_CFG_004</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -3643,54 +3643,54 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Unsupported Features</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Locked/exclusive access</t>
+          <t>Address width above 32 bits</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Locked/exclusive requests are outside the profile. Legal traffic keeps AxLOCK low. With AxLOCK=1 the bridge completes the request with OKAY (never EXOKAY) and correct data, and HMASTLOCK follows AxLOCK for that request (reference-design behavior).</t>
+          <t>Equal AXI/AHB address widths above 32 bits, up to the 64 PG177 allows, pass the compliance regression</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>Constraint, SVA, Directed</t>
+          <t>Parameter regression</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>Predictor/scoreboard per-beat HMASTLOCK compare; response and read-back checks in axi4_mst_lock_seq; lock=/mastlock= in transaction log lines; C_LOCKED_IDLE cover; LOCK_UNSUPPORTED, ARLOCK_UNSUPPORTED, NO_LOCK in legal-profile tests</t>
+          <t>Address-width compile/run matrix (not built)</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>bridge_unsupported_feature_test; legal-profile tests</t>
+          <t>none</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J55" s="6" t="inlineStr">
-        <is>
-          <t>Complete</t>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J55" s="8" t="inlineStr">
+        <is>
+          <t>Deferred</t>
         </is>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>Decision 2026-09-17: keep the reference behavior, RTL unchanged (spec review 4.1). Regression 3 (5 seeds): run=30 failed=0, 0 mismatches; lock order W1 R0 W0 R1 R1 on all 6 burst types; observed HMASTLOCK stream equals predicted on all 95 beats (57 locked); no EXOKAY; C_LOCKED_IDLE fires at 155 ns. No lock=1/mastlock=1 in the 40 legal-profile runs.</t>
+          <t>Split out of BRG_CFG_002 on 2026-10-01 by decision, so that neither item claims something it did not run. Nothing here has been attempted: every one of the 335 runs uses a 32-bit address. BRIDGE_ADDR_WIDTH defaults to 32 in 10_tb/cfg/axi4_types.sv and 10_tb/cfg/ahb_types.sv - one shared knob, so the two sides cannot be built unequal by accident - and the Makefile never overrides it, unlike BRIDGE_DATA_WIDTH which drives the separate work64 compilation. What is known about wider addresses is only negative: BRG_CFG_003's guard cases addr_width_mismatch (AHB 40 against AXI 32) and addr_width_too_small (16/16) both fail elaboration as required, which shows the guards reject illegal and unequal widths but runs no traffic at a legal width above 32. Nothing in the DUT is known to be width-dependent beyond the address buses themselves, but that is a reading of the RTL, not a measurement, and it is exactly the kind of assumption the rest of this plan declines to rest on. Cost to close is small and the hook already exists: BRIDGE_ADDR_WIDTH is ifndef-guarded, so a 64-bit-address build is one more compilation into its own library following the compile_wide/optimize_wide pattern, plus PARAM_TEST_LIST run on it; the predictor, scoreboard and covergroups are all written against the parameters rather than against 32. Deferred rather than excluded: this is a configuration PG177 supports, so the ground to close the item is a decision that the product will never ship it, not the absence of a testbench. Tracked on the Coverage sheet as the one remaining Not Started row.</t>
         </is>
       </c>
     </row>
     <row r="56" ht="28.8" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>BRG_UNS_002</t>
+          <t>BRG_UNS_001</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -3705,27 +3705,27 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>No out-of-order completion</t>
+          <t>Locked/exclusive access</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>The bridge completes accepted AXI requests in supported order without response reordering or interleaving</t>
+          <t>Locked/exclusive requests are outside the profile. Legal traffic keeps AxLOCK low. With AxLOCK=1 the bridge completes the request with OKAY (never EXOKAY) and correct data, and HMASTLOCK follows AxLOCK for that request (reference-design behavior).</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>Scoreboard, Stress</t>
+          <t>Constraint, SVA, Directed</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>Order-independent scoreboard: AHB beats matched to requests by first-beat direction/address, AXI completions by direction/ID; RID_STABLE</t>
+          <t>Predictor/scoreboard per-beat HMASTLOCK compare; response and read-back checks in axi4_mst_lock_seq; lock=/mastlock= in transaction log lines; C_LOCKED_IDLE cover; LOCK_UNSUPPORTED, ARLOCK_UNSUPPORTED, NO_LOCK in legal-profile tests</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>bridge_ordering_test</t>
+          <t>bridge_unsupported_feature_test; legal-profile tests</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -3733,21 +3733,21 @@
           <t>High</t>
         </is>
       </c>
-      <c r="J56" s="8" t="inlineStr">
+      <c r="J56" s="6" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>Closed by bridge_ordering_test, regression 21 (280 runs, 0 failures). The gap was that every other test sends one request and waits for it, so the bridge was never given the chance to reorder anything. This test hands the driver a whole phase in one time step with max_outstanding=0 and lets the queue back up behind the bridge: 88 requests over 8 phases, a queue 24 deep, and 1151 to 1394 cycles a run (1257 to 1371 on the reseeded regression 22) in which a request was asking and the bridge refused it. That count is checked, so a phase where the queue never backed up fails instead of passing on a technicality. The reference order is the order the bridge accepted the requests on AW and AR, which is what the requirement says, not the order they were issued in: the two differ by design, because a read arriving with a write wins arbitration and the write then takes the next turn. Against that order, on all 5 seeds, B and R completions come back in order per direction, each read returns the beat count its AR asked for, and RID never changes inside a burst (interleaved=0 over 49 to 57 read bursts a run, and the number of read bursts equals the number of reads on every seed). The acceptance order is also replayed through a reference copy of the AHB slave memory and every read beat is compared against what an in-order bridge would owe it at that point, which is the value a read overtaking a write would change. 12 to 23 reads a run returned data an earlier write had left rather than the address pattern, and the run fails if that count is zero. The AHB side shows one contiguous burst per accepted request, in the same order and with the same beat count, in all 8 phases, so the two directions are not interleaved there either. Measured rather than assumed: max_accepted, the most requests the bridge had accepted and not completed at one time, is 1 in the seven deterministic phases and 2 only in the mixed stress phase. That matches the RTL. In axi_slv_if the read FSM leaves AXI_RD_IDLE only on !write_pending &amp;&amp; !write_in_progress and the write FSM leaves AXI_WR_IDLE only on !read_in_progress, so the two machines exclude each other; read_in_progress clears on RLAST_sm rather than on the R handshake, which is what lets a write be accepted while the last read beat still waits for RREADY, and that is the only overlap seen. Reordering on this bridge is therefore structural, not incidental. Stimulus: eight reads sharing one ID, eight reads with rotating IDs and falling burst lengths so a bridge returning completions as they became ready would show it, a write and read stream over the same eight addresses, four phases that put every access of the phase on a single address (two with one ID across both directions, two with a different ID per request), and 24 randomized mixed requests with AHB wait states and AXI response backpressure. FIXED and WRAP2 are left out because the bridge expands each into several AHB bursts by design, which the one-burst-per-request check could not tell from interleaving; their mapping is bridge_fixed_mapping_test and bridge_wrap_mapping_test. Confirmed a second time on a fresh set of seeds in regression 22: 88 requests and 8 phases every run, queue_depth 24, max_accepted 1 in the deterministic phases and 2 in the stress phase, interleaved=0, 0 failures.</t>
+          <t>Decision 2026-09-17: keep the reference behavior, RTL unchanged (spec review 4.1). Regression 3 (5 seeds): run=30 failed=0, 0 mismatches; lock order W1 R0 W0 R1 R1 on all 6 burst types; observed HMASTLOCK stream equals predicted on all 95 beats (57 locked); no EXOKAY; C_LOCKED_IDLE fires at 155 ns. No lock=1/mastlock=1 in the 40 legal-profile runs.</t>
         </is>
       </c>
     </row>
     <row r="57" ht="28.8" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>BRG_UNS_003</t>
+          <t>BRG_UNS_002</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3762,27 +3762,27 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Response subset</t>
+          <t>No out-of-order completion</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>Only OKAY and SLVERR are emitted on B and R channels</t>
+          <t>The bridge completes accepted AXI requests in supported order without response reordering or interleaving</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>SVA, Coverage</t>
+          <t>Scoreboard, Stress</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>BRESP_SUPPORTED; RRESP_SUPPORTED; cp_axi_status and cp_resp illegal_bins</t>
+          <t>Order-independent scoreboard: AHB beats matched to requests by first-beat direction/address, AXI completions by direction/ID; RID_STABLE</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>bridge_ordering_test</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -3797,49 +3797,49 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>Closed in regression 23. The gap was that only OKAY was ever observed, so the assertions and illegal_bins were passing on traffic that could not have failed them. Both supported responses are now driven from three independent sources: an AHB ERROR answer (bridge_response_mapping_test, 43 SLVERR responses a run, and bridge_random_stress_test, 44 to 60 a run on randomized traffic), and the C_DPHASE_TIMEOUT watchdog (bridge_timeout_test and bridge_timeout_recovery_test on all five timeout builds). Both channels are covered, because the random test sends reads and writes in roughly equal numbers and checks the per-beat RRESP as well as BRESP against the plan it drew. BRESP_SUPPORTED and RRESP_SUPPORTED are hit in all 285 runs with 0 failures, so no EXOKAY or DECERR was ever emitted on either channel, and the cp_axi_status bins for OKAY and SLVERR are both covered with their illegal_bins never taken (462/462 covergroup bins, 51/51 assertions with 0 failures). Regression 22 also closed the last hole on the coverage side: until the e2e_cov fix no watchdog SLVERR ever reached cg_response_map at all.</t>
+          <t>Closed by bridge_ordering_test, regression 21 (280 runs, 0 failures). The gap was that every other test sends one request and waits for it, so the bridge was never given the chance to reorder anything. This test hands the driver a whole phase in one time step with max_outstanding=0 and lets the queue back up behind the bridge: 88 requests over 8 phases, a queue 24 deep, and 1151 to 1394 cycles a run (1257 to 1371 on the reseeded regression 22) in which a request was asking and the bridge refused it. That count is checked, so a phase where the queue never backed up fails instead of passing on a technicality. The reference order is the order the bridge accepted the requests on AW and AR, which is what the requirement says, not the order they were issued in: the two differ by design, because a read arriving with a write wins arbitration and the write then takes the next turn. Against that order, on all 5 seeds, B and R completions come back in order per direction, each read returns the beat count its AR asked for, and RID never changes inside a burst (interleaved=0 over 49 to 57 read bursts a run, and the number of read bursts equals the number of reads on every seed). The acceptance order is also replayed through a reference copy of the AHB slave memory and every read beat is compared against what an in-order bridge would owe it at that point, which is the value a read overtaking a write would change. 12 to 23 reads a run returned data an earlier write had left rather than the address pattern, and the run fails if that count is zero. The AHB side shows one contiguous burst per accepted request, in the same order and with the same beat count, in all 8 phases, so the two directions are not interleaved there either. Measured rather than assumed: max_accepted, the most requests the bridge had accepted and not completed at one time, is 1 in the seven deterministic phases and 2 only in the mixed stress phase. That matches the RTL. In axi_slv_if the read FSM leaves AXI_RD_IDLE only on !write_pending &amp;&amp; !write_in_progress and the write FSM leaves AXI_WR_IDLE only on !read_in_progress, so the two machines exclude each other; read_in_progress clears on RLAST_sm rather than on the R handshake, which is what lets a write be accepted while the last read beat still waits for RREADY, and that is the only overlap seen. Reordering on this bridge is therefore structural, not incidental. Stimulus: eight reads sharing one ID, eight reads with rotating IDs and falling burst lengths so a bridge returning completions as they became ready would show it, a write and read stream over the same eight addresses, four phases that put every access of the phase on a single address (two with one ID across both directions, two with a different ID per request), and 24 randomized mixed requests with AHB wait states and AXI response backpressure. FIXED and WRAP2 are left out because the bridge expands each into several AHB bursts by design, which the one-burst-per-request check could not tell from interleaving; their mapping is bridge_fixed_mapping_test and bridge_wrap_mapping_test. Confirmed a second time on a fresh set of seeds in regression 22: 88 requests and 8 phases every run, queue_depth 24, max_accepted 1 in the deterministic phases and 2 in the stress phase, interleaved=0, 0 failures.</t>
         </is>
       </c>
     </row>
     <row r="58" ht="28.8" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>BRG_ENV_001</t>
+          <t>BRG_UNS_003</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Verification plan</t>
+          <t>PG177 Ch.2</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>Unsupported Features</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Agent topology</t>
+          <t>Response subset</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Active AXI master, reactive AHB slave, predictor, scoreboard, coverage and virtual sequencer build and connect</t>
+          <t>Only OKAY and SLVERR are emitted on B and R channels</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>UVM structure</t>
+          <t>SVA, Coverage</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>vip_env; virtual_sequencer; agent configs</t>
+          <t>BRESP_SUPPORTED; RRESP_SUPPORTED; cp_axi_status and cp_resp illegal_bins</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>bridge_base_test</t>
+          <t>all</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -3847,21 +3847,21 @@
           <t>High</t>
         </is>
       </c>
-      <c r="J58" s="6" t="inlineStr">
+      <c r="J58" s="8" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>Built and connected in all 85 regression-11 runs.</t>
+          <t>Closed in regression 23. The gap was that only OKAY was ever observed, so the assertions and illegal_bins were passing on traffic that could not have failed them. Both supported responses are now driven from three independent sources: an AHB ERROR answer (bridge_response_mapping_test, 43 SLVERR responses a run, and bridge_random_stress_test, 44 to 60 a run on randomized traffic), and the C_DPHASE_TIMEOUT watchdog (bridge_timeout_test and bridge_timeout_recovery_test on all five timeout builds). Both channels are covered, because the random test sends reads and writes in roughly equal numbers and checks the per-beat RRESP as well as BRESP against the plan it drew. BRESP_SUPPORTED and RRESP_SUPPORTED are hit in all 285 runs with 0 failures, so no EXOKAY or DECERR was ever emitted on either channel, and the cp_axi_status bins for OKAY and SLVERR are both covered with their illegal_bins never taken (462/462 covergroup bins, 51/51 assertions with 0 failures). Regression 22 also closed the last hole on the coverage side: until the e2e_cov fix no watchdog SLVERR ever reached cg_response_map at all.</t>
         </is>
       </c>
     </row>
     <row r="59" ht="28.8" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>BRG_ENV_002</t>
+          <t>BRG_ENV_001</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3876,27 +3876,27 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Independent request prediction</t>
+          <t>Agent topology</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>AXI requests are expanded into an independently predicted AHB beat stream</t>
+          <t>Active AXI master, reactive AHB slave, predictor, scoreboard, coverage and virtual sequencer build and connect</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>Scoreboard</t>
+          <t>UVM structure</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>predictor.expected_ahb_ap</t>
+          <t>vip_env; virtual_sequencer; agent configs</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>all functional tests</t>
+          <t>bridge_base_test</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
@@ -3911,14 +3911,14 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>Predictor expands every AXI request; 0 mismatches in regression 2.</t>
+          <t>Built and connected in all 85 regression-11 runs.</t>
         </is>
       </c>
     </row>
     <row r="60" ht="28.8" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>BRG_ENV_003</t>
+          <t>BRG_ENV_002</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>End-to-end response checking</t>
+          <t>Independent request prediction</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>Observed AHB response/data reconstructs the expected AXI completion and compares against the AXI monitor</t>
+          <t>AXI requests are expanded into an independently predicted AHB beat stream</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>scoreboard expected/actual AXI queues</t>
+          <t>predictor.expected_ahb_ap</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
@@ -3968,14 +3968,14 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>Includes read data; unwritten AHB memory returns address-derived data.</t>
+          <t>Predictor expands every AXI request; 0 mismatches in regression 2.</t>
         </is>
       </c>
     </row>
     <row r="61" ht="28.8" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>BRG_ENV_004</t>
+          <t>BRG_ENV_003</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3990,12 +3990,12 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Loss/duplication detection</t>
+          <t>End-to-end response checking</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>End-of-test checks require every expected and actual queue to be empty</t>
+          <t>Observed AHB response/data reconstructs the expected AXI completion and compares against the AXI monitor</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
@@ -4005,12 +4005,12 @@
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>scoreboard.check_phase: empty queues and at least one AHB and one AXI comparison</t>
+          <t>scoreboard expected/actual AXI queues</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>all functional tests</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
@@ -4025,14 +4025,14 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>check_phase requires empty queues and now fails a test that compared no transactions. Regression 5: no run triggered either check.</t>
+          <t>Includes read data; unwritten AHB memory returns address-derived data.</t>
         </is>
       </c>
     </row>
     <row r="62" ht="28.8" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>BRG_ENV_005</t>
+          <t>BRG_ENV_004</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -4047,49 +4047,49 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Coverage closure</t>
+          <t>Loss/duplication detection</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>Requirement coverage, assertion coverage and code coverage are reviewed with explicit waivers</t>
+          <t>End-of-test checks require every expected and actual queue to be empty</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>Coverage review</t>
+          <t>Scoreboard</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>cg_axi_request; cg_translation; cg_ahb_response; cg_response_map; agent covergroups</t>
+          <t>scoreboard.check_phase: empty queues and at least one AHB and one AXI comparison</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>bridge_random_stress_test</t>
+          <t>all</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J62" s="8" t="inlineStr">
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J62" s="6" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>Merged, regression 26 (320 runs, 0 failures, 0 UVM warnings). Functional coverage is closed: covergroups 100% of bins (462/462), assertions 51/51 hit with 0 failures and none left unhit, cover directives 13/13. The merge spans seven builds. Code coverage is reviewed to the line, using 'make code_report', a target added for this because the HTML report stops at a percentage per design unit. The review drove two tests and the DUT moved from 83.00% in regression 22 to 87.40%: bridge_random_stress_test on the narrow build woke the narrow burst address generators, and bridge_write_starvation_test closed the biggest hole it found. ahb_mstr_if is at 302/306 statements (98.6%, from 280/306) and axi_slv_if at 186/188 (98.9%, from 182/188). Every uncovered item is now accounted for. Waived, each with the reason in the source rather than argued from the numbers: (1) unused generality of blocks reused from the reference design, time_out ties counter_f's Count_Down to 1'b1 and leaves Count_Out unconnected, and ahb_skid_buf is instantiated with skid_stop, S_STRB and S_User tied to constants, which is what their FEC condition scores of 50.00% and 36.36% are made of; (2) states AXI4 forbids, ahb_mstr_if lines 259 and 324 are the default arms of case (axi_size) and need a size wider than the bus, and the axi_slv_if condition rows for AxBURST[1] with AxLEN == 0 need a one-beat WRAP; (3) two branches that are dead by construction, proved by there being exactly one entry into each state and its condition contradicting the branch: AHB_LAST_WAIT is entered only when one_kb_in_progress, fixed_burst_access or wrap_2_in_progress holds, so its plain else at line 572 cannot run, and AHB_LAST is entered only when none of them holds, so its fixed/wrap2 arm at line 583 cannot. One item is covered by decision rather than by stimulus. Decision 2026-09-29: accept AXI_WR_RESP_WAIT in axi_slv_if, lines 473 to 475, as an exception. It needs send_bresp already high in the cycle AXI_WRITING accepts WLAST. On an untimed write that cannot happen, because the last AHB beat is the one carrying the WLAST data and so completes after it; it is reachable only when the watchdog fires part way through a multi-beat write and the AHB counter drains before the master has delivered WLAST. It is therefore reachable but not reached, and it is recorded as such rather than waived on a false claim of unreachability. The traffic that would produce it is a mid-burst write timeout, which bridge_random_stress_test deliberately avoids: it hangs the last beat of its timeout cases so that the beat the bridge abandons and the completion that marks it abandoned cannot land in the same time step, a race that cost three regressions to diagnose. Two statements out of the 494 in the two main design units were judged not worth reopening that. If the item is ever wanted, the shape is known: a declared timeout on a middle beat of a multi-beat write, with the write data of that request left out of the scoreboard comparison.</t>
+          <t>check_phase requires empty queues and now fails a test that compared no transactions. Regression 5: no run triggered either check.</t>
         </is>
       </c>
     </row>
     <row r="63" ht="28.8" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>BRG_ENV_006</t>
+          <t>BRG_ENV_005</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -4104,27 +4104,27 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Mutation sensitivity</t>
+          <t>Coverage closure</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>Injected faults in address, burst, size, protection, data, ID, response, beat count and timeout are detected</t>
+          <t>Requirement coverage, assertion coverage and code coverage are reviewed with explicit waivers</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>Mutation testing</t>
+          <t>Coverage review</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>Predictor/scoreboard/assertion sensitivity suite</t>
+          <t>cg_axi_request; cg_translation; cg_ahb_response; cg_response_map; agent covergroups</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>bridge_mutation_test</t>
+          <t>bridge_random_stress_test</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
@@ -4132,21 +4132,21 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="J63" s="7" t="inlineStr">
+      <c r="J63" s="8" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>Closed by bridge_mutation_test, regression 31 (335 runs, 0 failures, 0 UVM warnings). Every other test asks whether the bridge is right; this one asks whether the answer would have been different had it been wrong, which is what the rest of the regression rests on and what none of them checked. The target is the pair of hand-written comparisons at the heart of the scoreboard, ahb_request_matches and axi_transaction_matches. Both are lists of fields, so a field left out of one of them would make the whole regression blind to it and still report a pass. The suite corrupts one named field at a time in the stream the scoreboard observes and requires a mismatch to come back. 16 faults, all injected and all caught, identically on 5 seeds: the eight fields ahb_request_matches claims to compare (address, direction, HTRANS, burst, size, protection, mastlock and write data), six that a corrupted AXI completion can reach (address, length, strobes, BRESP, RRESP and read data), and two declared timeouts that do not happen, which is the same question asked of the declared-timeout path. Faults go into a beat after the first, because the first beat is what find_start_ctx uses to bind a transfer to its request, so a fault there would stop the beat being attributed rather than being compared and found wrong. It runs inside the regression rather than beside it. While the suite is active the scoreboard reports a failed comparison as a caught fault instead of an error, so the run stays green and the verdict is in the counts: 16 armed, 16 caught, nothing missed. The running totals mismatched_ahb, mismatched_axi and missed_timeouts now mean real findings only and read 0 for this test, which also keeps check_phase from reporting an injected fault a second time at the end of the run. Two things it deliberately does not cover. A wrong ID cannot be injected this way: the scoreboard pairs a completion with its request by direction and ID, so a corrupted ID produces an unmatched completion rather than a mismatch, and the enum has no entry for it so nobody tries. ID sensitivity rests on the driver and monitor ID checks and on B_WITH_REQUEST and R_WITH_REQUEST. The assertions are not covered either, because they report with $error, which does not pass through the UVM report server and so cannot be demoted; proving their sensitivity needs a run whose pass criterion is inverted. The other half of what this entry asked for, that the Makefile failure gate be proven by fault injection, was settled along the way and not by design: FAIL_REGEX caught illegal cover bins (vsim-8567) twice during this work, in bridge_random_stress_test and in bridge_illegal_narrow_test, on runs where the UVM report server said TEST PASSED. The gate catches what the report server cannot see, on real faults rather than staged ones.</t>
+          <t>Merged, regression 26 (320 runs, 0 failures, 0 UVM warnings). Functional coverage is closed: covergroups 100% of bins (462/462), assertions 51/51 hit with 0 failures and none left unhit, cover directives 13/13. The merge spans seven builds. Code coverage is reviewed to the line, using 'make code_report', a target added for this because the HTML report stops at a percentage per design unit. The review drove two tests and the DUT moved from 83.00% in regression 22 to 87.40%: bridge_random_stress_test on the narrow build woke the narrow burst address generators, and bridge_write_starvation_test closed the biggest hole it found. ahb_mstr_if is at 302/306 statements (98.6%, from 280/306) and axi_slv_if at 186/188 (98.9%, from 182/188). Every uncovered item is now accounted for. Waived, each with the reason in the source rather than argued from the numbers: (1) unused generality of blocks reused from the reference design, time_out ties counter_f's Count_Down to 1'b1 and leaves Count_Out unconnected, and ahb_skid_buf is instantiated with skid_stop, S_STRB and S_User tied to constants, which is what their FEC condition scores of 50.00% and 36.36% are made of; (2) states AXI4 forbids, ahb_mstr_if lines 259 and 324 are the default arms of case (axi_size) and need a size wider than the bus, and the axi_slv_if condition rows for AxBURST[1] with AxLEN == 0 need a one-beat WRAP; (3) two branches that are dead by construction, proved by there being exactly one entry into each state and its condition contradicting the branch: AHB_LAST_WAIT is entered only when one_kb_in_progress, fixed_burst_access or wrap_2_in_progress holds, so its plain else at line 572 cannot run, and AHB_LAST is entered only when none of them holds, so its fixed/wrap2 arm at line 583 cannot. One item is covered by decision rather than by stimulus. Decision 2026-09-29: accept AXI_WR_RESP_WAIT in axi_slv_if, lines 473 to 475, as an exception. It needs send_bresp already high in the cycle AXI_WRITING accepts WLAST. On an untimed write that cannot happen, because the last AHB beat is the one carrying the WLAST data and so completes after it; it is reachable only when the watchdog fires part way through a multi-beat write and the AHB counter drains before the master has delivered WLAST. It is therefore reachable but not reached, and it is recorded as such rather than waived on a false claim of unreachability. The traffic that would produce it is a mid-burst write timeout, which bridge_random_stress_test deliberately avoids: it hangs the last beat of its timeout cases so that the beat the bridge abandons and the completion that marks it abandoned cannot land in the same time step, a race that cost three regressions to diagnose. Two statements out of the 494 in the two main design units were judged not worth reopening that. If the item is ever wanted, the shape is known: a declared timeout on a middle beat of a multi-beat write, with the write data of that request left out of the scoreboard comparison.</t>
         </is>
       </c>
     </row>
     <row r="64" ht="28.8" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>BRG_ENV_007</t>
+          <t>BRG_ENV_006</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -4161,27 +4161,27 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Reference equivalence</t>
+          <t>Mutation sensitivity</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>Translated SystemVerilog DUT matches the original VHDL under identical stimulus</t>
+          <t>Injected faults in address, burst, size, protection, data, ID, response, beat count and timeout are detected</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>Side-by-side simulation</t>
+          <t>Mutation testing</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>Cycle/transaction comparison</t>
+          <t>Predictor/scoreboard/assertion sensitivity suite</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>bridge_vhdl_equivalence_test</t>
+          <t>bridge_mutation_test</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -4191,67 +4191,124 @@
       </c>
       <c r="J64" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>The conflict this entry used to record is gone: both sheets now read Not Started. The Tests sheet did mark bridge_vhdl_equivalence_test as Excluded up to 2026-09-24 and was changed on 2026-09-25; the note here was left stale. Decision 2026-09-29: do not exclude it. The project's own spec review makes it a prerequisite rather than an optional extra, in its own words 'required before treating the translated DUT, or the RTL observations above, as golden' (pg177_spec_review.md, closing table). Several decisions in that review lean on it already: the lock handling kept in Section 4.1, the continue-and-report error oracle in Section 3.4, and the unsupported single-write strobe behaviour, are all justified as matching the reference VHDL, and that match was established by reading the VHDL, never by running it. Excluding the item would leave those justifications resting on a review no simulation has ever checked. It is also not blocked for want of material. 00_doc/axi_ahblite_bridge_v3_0_vh_rfs.vhd is the complete reference design, 3953 lines, and its six entities are exactly the six SystemVerilog modules of the DUT: counter_f, time_out, ahb_skid_buf, axi_slv_if, ahb_mstr_if and axi_ahblite_bridge. A side-by-side harness would compile it into its own library, instantiate both bridges in bridge_tb_top on the same clock, reset and AXI stimulus, and compare the AHB master ports and the AXI responses cycle by cycle; the existing regression is the stimulus. Tried on 2026-10-01 with 'make compile_ref', a target added for this that builds the reference into its own library and that nothing else depends on. The result rules out the reason the sheets used to imply and names the real one: VHDL itself is fine here, vcom loaded STANDARD, TEXTIO, std_logic_1164 and NUMERIC_STD without complaint, so this is not a licence or a tool-support problem. It stopped at line 105 with 'Library "unisim" not found': the reference instantiates Xilinx UNISIM primitives, so it needs the Xilinx simulation libraries compiled for this Questa, which Vivado's compile_simlib produces. Blocked on that infrastructure, not on the testbench. Parked by decision on 2026-10-01 rather than excluded, because the spec review still treats the comparison as a prerequisite for calling the translation golden; if the UNISIM libraries are never going to be available here, that is the ground to exclude it on.</t>
+          <t>Closed by bridge_mutation_test, regression 31 (335 runs, 0 failures, 0 UVM warnings). Every other test asks whether the bridge is right; this one asks whether the answer would have been different had it been wrong, which is what the rest of the regression rests on and what none of them checked. The target is the pair of hand-written comparisons at the heart of the scoreboard, ahb_request_matches and axi_transaction_matches. Both are lists of fields, so a field left out of one of them would make the whole regression blind to it and still report a pass. The suite corrupts one named field at a time in the stream the scoreboard observes and requires a mismatch to come back. 16 faults, all injected and all caught, identically on 5 seeds: the eight fields ahb_request_matches claims to compare (address, direction, HTRANS, burst, size, protection, mastlock and write data), six that a corrupted AXI completion can reach (address, length, strobes, BRESP, RRESP and read data), and two declared timeouts that do not happen, which is the same question asked of the declared-timeout path. Faults go into a beat after the first, because the first beat is what find_start_ctx uses to bind a transfer to its request, so a fault there would stop the beat being attributed rather than being compared and found wrong. It runs inside the regression rather than beside it. While the suite is active the scoreboard reports a failed comparison as a caught fault instead of an error, so the run stays green and the verdict is in the counts: 16 armed, 16 caught, nothing missed. The running totals mismatched_ahb, mismatched_axi and missed_timeouts now mean real findings only and read 0 for this test, which also keeps check_phase from reporting an injected fault a second time at the end of the run. Two things it deliberately does not cover. A wrong ID cannot be injected this way: the scoreboard pairs a completion with its request by direction and ID, so a corrupted ID produces an unmatched completion rather than a mismatch, and the enum has no entry for it so nobody tries. ID sensitivity rests on the driver and monitor ID checks and on B_WITH_REQUEST and R_WITH_REQUEST. The assertions are not covered either, because they report with $error, which does not pass through the UVM report server and so cannot be demoted; proving their sensitivity needs a run whose pass criterion is inverted. The other half of what this entry asked for, that the Makefile failure gate be proven by fault injection, was settled along the way and not by design: FAIL_REGEX caught illegal cover bins (vsim-8567) twice during this work, in bridge_random_stress_test and in bridge_illegal_narrow_test, on runs where the UVM report server said TEST PASSED. The gate catches what the report server cannot see, on real faults rather than staged ones.</t>
         </is>
       </c>
     </row>
     <row r="65" ht="28.8" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>BRG_ENV_007</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Verification plan</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Environment</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>Reference equivalence</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>Translated SystemVerilog DUT matches the reference design it was translated from, under identical stimulus</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>Side-by-side simulation</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>Cycle/transaction comparison</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>bridge_reference_equivalence_test</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J65" s="7" t="inlineStr">
+        <is>
+          <t>Excluded</t>
+        </is>
+      </c>
+      <c r="K65" s="4" t="inlineStr">
+        <is>
+          <t>Excluded by decision 2026-10-01, at the project owner's direction. The reference source was only ever in this repository as a reading aid for checking the SystemVerilog translation by eye; it was never intended to be simulated, so an equivalence run was never a deliverable of this project. In the owner's words: the purpose of keeping the VHDL file was only to cross-check the DUT rewritten in SystemVerilog, with no intention of using VHDL. The source file, the compile_ref make target added for this item and the separate library mapping it used have all been removed from the repository, so the item has no material to run against and is closed rather than parked. The earlier blocker is moot: the 2026-10-01 'make compile_ref' attempt had shown VHDL support itself was fine (vcom loaded STANDARD, TEXTIO, std_logic_1164 and NUMERIC_STD) and stopped at line 105 with 'Library "unisim" not found', needing the Xilinx simulation libraries compiled for this Questa. That infrastructure is no longer being pursued. What this leaves standing: the three decisions that used to cite the reference (the lock handling kept in spec review 4.1, the continue-and-report error oracle in 3.4, and the unsupported single-write strobe behaviour) are each justified behaviourally against PG177 by the regression, not by the comparison; the spec review has been reworded so it no longer makes equivalence a prerequisite for treating the DUT as golden. Residual risk, accepted: nothing in this environment confirms the SystemVerilog matches the original source statement for statement. A divergence that PG177 does not pin down, and that no assertion, covergroup or scoreboard check reaches, would not be caught here. The 335-run regression, 462/462 functional coverage bins, 51/51 assertions and 87.40% DUT code coverage bound that risk to behaviour the specification leaves open.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
           <t>BRG_ENV_008</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>Verification plan</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>Environment</t>
         </is>
       </c>
-      <c r="D65" s="4" t="inlineStr">
+      <c r="D66" s="4" t="inlineStr">
         <is>
           <t>Random regression</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr">
+      <c r="E66" s="4" t="inlineStr">
         <is>
           <t>Multi-seed mixed traffic with independent wait/error policy finishes with zero unexplained errors and empty queues</t>
         </is>
       </c>
-      <c r="F65" s="4" t="inlineStr">
+      <c r="F66" s="4" t="inlineStr">
         <is>
           <t>Constrained random</t>
         </is>
       </c>
-      <c r="G65" s="4" t="inlineStr">
+      <c r="G66" s="4" t="inlineStr">
         <is>
           <t>Functional coverage and scoreboard summaries</t>
         </is>
       </c>
-      <c r="H65" s="4" t="inlineStr">
+      <c r="H66" s="4" t="inlineStr">
         <is>
           <t>bridge_random_stress_test</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr">
+      <c r="I66" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J65" s="7" t="inlineStr">
+      <c r="J66" s="7" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
       </c>
-      <c r="K65" s="4" t="inlineStr">
+      <c r="K66" s="4" t="inlineStr">
         <is>
           <t>Closed by bridge_random_stress_test, regression 23 (285 runs, 0 failures, 0 UVM warnings). The gap was that a seed only moved the AXI IDs and the FIXED lengths, because every sequence pinned its traffic from a case list. This is the first test that hands a request to the solver with only the legal profile fixed, so the constraint set of axi4_transaction shapes it: c_burst_length, c_wrap_alignment, c_4kb_boundary, c_cache_legal and c_distribution all take part, which no other test lets them do. The wait and error policy is independent in the sense the requirement asks for: the answer for each AHB beat is drawn before the request is sent and the only thing the request contributes is how many beats need one. Because the plan is known in advance the sequence is a full oracle on its own, separate from the scoreboard: every read beat must carry the address-derived word for its own address, a beat answered with ERROR must report SLVERR and no other beat may, and a write must report SLVERR exactly when one of its beats was. 64 requests a run on 5 seeds, all failed=0. A run is 493 to 576 AHB beats with 56 to 78 injected errors, 166 to 191 wait states and 44 to 60 SLVERR responses, split 20/44 to 32/32 between reads and writes and 14/34/7 to 20/38/13 between FIXED, INCR and WRAP. The two independent counts agree exactly on all five seeds: the beats the sequence planned equal the AHB transfers the scoreboard matched (537, 493, 576, 515, 546) and the requests equal the AXI completions it matched (64), with zero mismatches, so the bridge issued exactly the predicted beats and every one of them matched the prediction. The run also has to be varied to pass: it fails if a direction, a burst type, an injected error, a wait state, a SLVERR or an OKAY never appeared. The first twelve requests walk every burst type in both directions before the random bulk starts, so those checks cannot flake on an unlucky seed. Deliberately kept out of the traffic, with reasons: sparse strobes and unaligned narrow writes are the negative cases of BRG_SIZ_006, narrow sizes are used only where the build supports them, and AXI4_WR_AW_BEFORE_W deadlocks this DUT. The test also runs only on the C_DPHASE_TIMEOUT=0 build and refuses to elaborate on a watchdog build: a random wait could be abandoned by the watchdog, and the scoreboard only tolerates that for a request the test declared in advance, which a random policy cannot do. Regression 24 extends it to the narrow build and to all five C_DPHASE_TIMEOUT builds, 35 runs in all, 0 failures. On the narrow build the size is drawn per request, so 34 to 44 of the 64 requests are narrow and 23 to 30 of them start at a byte lane inside the word. On a watchdog build the policy cannot simply draw a wait at random, because one that tripped the watchdog would not have been declared; ordinary requests are capped four cycles below the threshold and every eighth request after the seeded head is a deliberate timeout instead, all of its beats answered OKAY so SLVERR can only mean the watchdog, declared with expect_timeout so the watchdog is required to fire. 7 of them a run on every build, and the run fails if a watchdog build never trips it. The two independent counts still close on every build: the beats the sequence planned equal the AHB transfers the scoreboard matched plus the ones it recorded as cancelled, for example 558 = 551 + 7 on the 16-cycle build and 512 = 505 + 7 on the 256-cycle one, with one cancelled beat per timeout. Across all 35 runs a run is 476 to 624 beats and 40 to 70 SLVERR responses.</t>
         </is>
@@ -4275,7 +4332,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="2"/>
@@ -5362,27 +5419,27 @@
     <row r="30" ht="28.8" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Planned timeout coverage</t>
+          <t>Build matrix + bridge_timeout_boundary_test (no covergroup built)</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>cp_timeout_cfg / cp_ready_offset</t>
+          <t>C_DPHASE_TIMEOUT per vopt image; AHB wait swept around each threshold</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>0,16,32,64,128,256; before/on/after</t>
+          <t>0, 16, 32, 64, 128, 256 (one image each); wait = threshold-3 .. threshold+8</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Timeout configuration and threshold boundary</t>
+          <t>Timeout configuration and threshold boundary. The planned cp_timeout_cfg / cp_ready_offset pair was never built and is not going to be: C_DPHASE_TIMEOUT is a build-time generic, so a coverpoint on it samples a constant and only re-records which image is running. The matrix does that directly - optimize_timeout builds one image per supported value and TIMEOUT_TEST_LIST runs four tests on every one, 100 runs, with the default build covering 0. The boundary dimension is covered by a stronger mechanism than coverage: bridge_timeout_boundary_test sweeps the wait from threshold-3 to threshold+8 and measures the smallest wait the watchdog actually terminates, so a threshold off by one fails the test instead of merely leaving a bin unhit (BRG_TMO_003).</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>All six images run; boundary measured per image</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -5392,34 +5449,34 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Superseded</t>
         </is>
       </c>
     </row>
     <row r="31" ht="28.8" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Planned arbitration coverage</t>
+          <t>bridge_read_priority_test in-test observer (no covergroup built)</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>cp_simultaneous / cp_first_grant</t>
+          <t>per-pair contention count; direction of the first AHB transfer</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>contended; read_first</t>
+          <t>contended (required on every pair); read_first (required on every pair)</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Simultaneous AXI read/write and selected first AHB request</t>
+          <t>Simultaneous AXI read/write and selected first AHB request. The planned cp_simultaneous / cp_first_grant pair was never built and is not needed: the test carries an observer that counts the cycles where the write is asking on AWVALID or WVALID and the read on ARVALID with neither accepted, and requires contended=17 and read_first=17 over the 17 pairs. That is a check, not a report - a pair that failed to collide, or that granted the write first, fails the test, whereas an uncovered bin would only have been noticed by someone reading the coverage report. Replacing it with a covergroup would be a downgrade (BRG_ARB_001, BRG_ARB_002).</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>contended = read_first = pair count, every seed</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -5429,34 +5486,34 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Superseded</t>
         </is>
       </c>
     </row>
     <row r="32" ht="28.8" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Planned parameter coverage</t>
+          <t>Build matrix (no covergroup built)</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>cp_data_width / cp_addr_width / cp_narrow_cfg</t>
+          <t>BRIDGE_DATA_WIDTH per compilation; C_S_AXI_SUPPORTS_NARROW_BURST per vopt image</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>32/64; 32..64; off/on</t>
+          <t>data width 32, 64; narrow off, on - all four combinations</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Supported bridge configuration matrix</t>
+          <t>Supported bridge data-width and narrow configuration matrix. The planned cp_data_width / cp_narrow_cfg coverpoints were never built: both are fixed at compile or elaboration time, so they would sample a constant. The matrix exercises all four combinations directly - work (32-bit) and work64 (64-bit) are separate compilations because the widths come from package parameters, and each is vopt'd twice, narrow off and on. bridge_parameter_test runs on all four and the profile grows with the bus (32n0 run=12, 32n1 run=18, 64n0 run=12, 64n1 run=26); PARAM_TEST_LIST runs the eight-test compliance subset on both 64-bit images, 80 runs, reporting scoreboard figures identical to 32-bit (BRG_CFG_001, BRG_CFG_002).</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>100% approved matrix</t>
+          <t>All four data-width/narrow builds run the compliance subset</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -5466,76 +5523,76 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Superseded</t>
         </is>
       </c>
     </row>
     <row r="33" ht="28.8" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>axi4_mst_coverage.cg_control</t>
+          <t>Not built</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>cp_dir, cp_burst, cp_size, cp_len, cp_lock, cp_id, cp_cache, cp_prot; cx_dir_burst, cx_dir_size, cx_dir_len</t>
+          <t>BRIDGE_ADDR_WIDTH per compilation</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>lock normal/unsupported; len single..max; id zero/nonzero; 10 legal AxCACHE (reserved are illegal_bins); all AxPROT</t>
+          <t>address width 32 (run); 33 to 64 (never run)</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>AXI agent control coverage. cp_lock.unsupported is reached only by bridge_unsupported_feature_test. cp_len.very_long (AxLEN 64-254) is reached by the INCR128 case in bridge_burst_matrix_test. Regression 7: 100%.</t>
+          <t>Supported bridge address-width range. This is the one dimension of the configuration matrix that is genuinely untested, not superseded. PG177 allows C_S_AXI_ADDR_WIDTH = C_M_AHB_ADDR_WIDTH anywhere from 32 to 64 and BRG_CFG_004 carries that requirement, but every run in the regression uses 32: BRIDGE_ADDR_WIDTH defaults to 32 in axi4_types.sv and ahb_types.sv and the Makefile never overrides it. A width above 32 appears only in the negative elaboration cases (addr_width_mismatch, addr_width_too_small), which prove the guards reject illegal widths but run no traffic. This row makes the gap visible on the coverage sheet instead of leaving it buried. Remedy is small and the hook exists: BRIDGE_ADDR_WIDTH is ifndef-guarded, so a 64-bit-address build is one more compilation into its own library, the same shape as compile_wide/optimize_wide, plus the compliance subset run on it.</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>100% legal bins</t>
+          <t>Open gap - not attempted</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>BRG_BST_001 to BRG_BST_011, BRG_UNS_001</t>
-        </is>
-      </c>
-      <c r="G33" s="6" t="inlineStr">
-        <is>
-          <t>Implemented</t>
+          <t>BRG_CFG_004</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>Not Started</t>
         </is>
       </c>
     </row>
     <row r="34" ht="28.8" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>axi4_mst_coverage.cg_address</t>
+          <t>axi4_mst_coverage.cg_control</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>cp_lane, cp_aligned</t>
+          <t>cp_dir, cp_burst, cp_size, cp_len, cp_lock, cp_id, cp_cache, cp_prot; cx_dir_burst, cx_dir_size, cx_dir_len</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>lanes 0-3; aligned, unaligned</t>
+          <t>lock normal/unsupported; len single..max; id zero/nonzero; 10 legal AxCACHE (reserved are illegal_bins); all AxPROT</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Address lane and alignment. The address-region coverpoint was removed: the bridge does not remap addresses and PG177 defines no address map.</t>
+          <t>AXI agent control coverage. cp_lock.unsupported is reached only by bridge_unsupported_feature_test. cp_len.very_long (AxLEN 64-254) is reached by the INCR128 case in bridge_burst_matrix_test. Regression 7: 100%.</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>100% legal bins</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>BRG_SIZ_005</t>
+          <t>BRG_BST_001 to BRG_BST_011, BRG_UNS_001</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
@@ -5547,22 +5604,22 @@
     <row r="35" ht="28.8" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>axi4_mst_coverage.cg_response</t>
+          <t>axi4_mst_coverage.cg_address</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>cp_dir, cp_resp, cx_dir_resp</t>
+          <t>cp_lane, cp_aligned</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>okay, slverr; EXOKAY/DECERR are illegal_bins</t>
+          <t>lanes 0-3; aligned, unaligned</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>AXI responses seen by the master. EXOKAY/DECERR are illegal_bins: sampling them fails the run.</t>
+          <t>Address lane and alignment. The address-region coverpoint was removed: the bridge does not remap addresses and PG177 defines no address map.</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -5572,7 +5629,7 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>BRG_RSP_001, BRG_RSP_002, BRG_UNS_003</t>
+          <t>BRG_SIZ_005</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
@@ -5584,22 +5641,22 @@
     <row r="36" ht="28.8" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>axi4_mst_coverage.cg_write_strobe</t>
+          <t>axi4_mst_coverage.cg_response</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>cp_strb</t>
+          <t>cp_dir, cp_resp, cx_dir_resp</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>full, zero, partial</t>
+          <t>okay, slverr; EXOKAY/DECERR are illegal_bins</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Write strobe shape per beat</t>
+          <t>AXI responses seen by the master. EXOKAY/DECERR are illegal_bins: sampling them fails the run.</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -5609,7 +5666,7 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>BRG_SIZ_004</t>
+          <t>BRG_RSP_001, BRG_RSP_002, BRG_UNS_003</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
@@ -5621,32 +5678,32 @@
     <row r="37" ht="28.8" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>ahb_slv_coverage.cg_transfer</t>
+          <t>axi4_mst_coverage.cg_write_strobe</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>cp_dir, cp_trans, cp_burst, cp_size, cp_resp, cp_wait, cp_lock, cp_prot, cp_lane; cx_dir_burst, cx_dir_size, cx_burst_resp</t>
+          <t>cp_strb</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>nonseq/seq; all HBURST; wait 0, 1-3, 4-15, 16+; lock normal/unsupported; HPROT 0000-0111 (HPROT[3]=1 is ignore_bins)</t>
+          <t>full, zero, partial</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Completed AHB transfer coverage. cp_lock.unsupported (HMASTLOCK=1) is reached only by bridge_unsupported_feature_test; HPROT values other than 0001 only by bridge_protection_mapping_test. ERROR and wait-state bins need the P0 wait/ERROR test.</t>
+          <t>Write strobe shape per beat</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>100% legal bins</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>BRG_BST_001 to BRG_BST_010, BRG_WAI_001</t>
+          <t>BRG_SIZ_004</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
@@ -5658,35 +5715,72 @@
     <row r="38" ht="28.8" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>ahb_slv_coverage.cg_transfer</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>cp_dir, cp_trans, cp_burst, cp_size, cp_resp, cp_wait, cp_lock, cp_prot, cp_lane; cx_dir_burst, cx_dir_size, cx_burst_resp</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>nonseq/seq; all HBURST; wait 0, 1-3, 4-15, 16+; lock normal/unsupported; HPROT 0000-0111 (HPROT[3]=1 is ignore_bins)</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>Completed AHB transfer coverage. cp_lock.unsupported (HMASTLOCK=1) is reached only by bridge_unsupported_feature_test; HPROT values other than 0001 only by bridge_protection_mapping_test. ERROR and wait-state bins need the P0 wait/ERROR test.</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>100% legal bins</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>BRG_BST_001 to BRG_BST_010, BRG_WAI_001</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
           <t>ahb_slv_coverage.cg_bus_trans</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>cp_trans</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>idle, busy, nonseq, seq</t>
         </is>
       </c>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="D39" s="4" t="inlineStr">
         <is>
           <t>HTRANS sampled whenever HREADY is high. The RTL inserts BUSY between burst beats.</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F38" s="4" t="inlineStr">
+      <c r="F39" s="4" t="inlineStr">
         <is>
           <t>BRG_BST_002 to BRG_BST_010</t>
         </is>
       </c>
-      <c r="G38" s="6" t="inlineStr">
+      <c r="G39" s="6" t="inlineStr">
         <is>
           <t>Implemented</t>
         </is>
@@ -8441,22 +8535,22 @@
     <row r="25" ht="28.8" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>bridge_illegal_parameter_test</t>
+          <t>bridge_illegal_param_top</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Compile/elaboration matrix</t>
+          <t>none; elaboration harness, not a UVM test</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Proves unsupported width/timeout combinations fail clearly</t>
+          <t>Instantiates the bridge on its own, with no ports connected and no stimulus, so the only thing a build can be judged on is whether the configuration guards in axi_ahblite_bridge stop it. Nine cases, each its own compilation with one illegal parameter from a define and the rest legal. Every case has to fail; one that elaborates and runs to completion is the finding, because it means the bridge accepts a configuration PG177 does not support and would then misbehave quietly.</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Unequal widths; illegal data/address widths; illegal timeout</t>
+          <t>Run by 'make illegal_param_check', deliberately outside regress: a set of cases that all have to fail cannot share a pass criterion with one that all have to pass. A case counts as rejected whichever stage catches it, since some illegal widths are refused by the tool before the guards run. Result: 9 rejected, 0 accepted, each by its own guard</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -8466,7 +8560,7 @@
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Implemented</t>
         </is>
       </c>
     </row>
@@ -8601,7 +8695,7 @@
     <row r="30" ht="28.8" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>bridge_vhdl_equivalence_test</t>
+          <t>bridge_reference_equivalence_test</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -8611,12 +8705,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Applies identical stimulus to translated SV and original VHDL and compares behavior</t>
+          <t>Would have applied identical stimulus to the translated SV and the reference design and compared behavior; not built</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Approved simulator/version matrix</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -8626,7 +8720,7 @@
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Excluded</t>
         </is>
       </c>
     </row>
